--- a/GearSage-client/rate/excel/soft_lure_detail.xlsx
+++ b/GearSage-client/rate/excel/soft_lure_detail.xlsx
@@ -32,7 +32,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
   <fonts count="1">
@@ -456,11 +460,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
+      <c r="A2" t="str">
+        <v>LFD10026</v>
+      </c>
+      <c r="B2" t="str">
+        <v>LF1002</v>
       </c>
       <c r="C2" t="str">
         <v>竞技T尾2代</v>
@@ -512,11 +516,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>3</v>
+      <c r="A3" t="str">
+        <v>LFD10027</v>
+      </c>
+      <c r="B3" t="str">
+        <v>LF1002</v>
       </c>
       <c r="C3" t="str">
         <v>竞技T尾2代</v>
@@ -568,11 +572,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>LFD10028</v>
+      </c>
+      <c r="B4" t="str">
+        <v>LF1002</v>
       </c>
       <c r="C4" t="str">
         <v>竞技T尾2代</v>
@@ -624,11 +628,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
+      <c r="A5" t="str">
+        <v>LFD10029</v>
+      </c>
+      <c r="B5" t="str">
+        <v>LF1002</v>
       </c>
       <c r="C5" t="str">
         <v>竞技T尾2代</v>
@@ -680,11 +684,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
+      <c r="A6" t="str">
+        <v>LFD10030</v>
+      </c>
+      <c r="B6" t="str">
+        <v>LF1002</v>
       </c>
       <c r="C6" t="str">
         <v>竞技T尾2代</v>
@@ -736,11 +740,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>4</v>
+      <c r="A7" t="str">
+        <v>LFD10031</v>
+      </c>
+      <c r="B7" t="str">
+        <v>LF1003</v>
       </c>
       <c r="C7" t="str">
         <v>竞技T尾</v>
@@ -792,11 +796,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>4</v>
+      <c r="A8" t="str">
+        <v>LFD10032</v>
+      </c>
+      <c r="B8" t="str">
+        <v>LF1003</v>
       </c>
       <c r="C8" t="str">
         <v>竞技T尾</v>
@@ -848,11 +852,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>4</v>
+      <c r="A9" t="str">
+        <v>LFD10033</v>
+      </c>
+      <c r="B9" t="str">
+        <v>LF1003</v>
       </c>
       <c r="C9" t="str">
         <v>竞技T尾</v>
@@ -904,11 +908,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>4</v>
+      <c r="A10" t="str">
+        <v>LFD10034</v>
+      </c>
+      <c r="B10" t="str">
+        <v>LF1003</v>
       </c>
       <c r="C10" t="str">
         <v>竞技T尾</v>
@@ -960,11 +964,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>4</v>
+      <c r="A11" t="str">
+        <v>LFD10035</v>
+      </c>
+      <c r="B11" t="str">
+        <v>LF1003</v>
       </c>
       <c r="C11" t="str">
         <v>竞技T尾</v>
@@ -8447,6 +8451,18 @@
       <c r="M144" t="str">
         <v/>
       </c>
+      <c r="N144" t="str">
+        <v/>
+      </c>
+      <c r="O144" t="str">
+        <v/>
+      </c>
+      <c r="P144" t="str">
+        <v/>
+      </c>
+      <c r="Q144" t="str">
+        <v/>
+      </c>
       <c r="R144" t="str">
         <v/>
       </c>
@@ -8491,6 +8507,18 @@
       <c r="M145" t="str">
         <v/>
       </c>
+      <c r="N145" t="str">
+        <v/>
+      </c>
+      <c r="O145" t="str">
+        <v/>
+      </c>
+      <c r="P145" t="str">
+        <v/>
+      </c>
+      <c r="Q145" t="str">
+        <v/>
+      </c>
       <c r="R145" t="str">
         <v/>
       </c>
@@ -8535,6 +8563,18 @@
       <c r="M146" t="str">
         <v/>
       </c>
+      <c r="N146" t="str">
+        <v/>
+      </c>
+      <c r="O146" t="str">
+        <v/>
+      </c>
+      <c r="P146" t="str">
+        <v/>
+      </c>
+      <c r="Q146" t="str">
+        <v/>
+      </c>
       <c r="R146" t="str">
         <v/>
       </c>
@@ -8579,6 +8619,18 @@
       <c r="M147" t="str">
         <v/>
       </c>
+      <c r="N147" t="str">
+        <v/>
+      </c>
+      <c r="O147" t="str">
+        <v/>
+      </c>
+      <c r="P147" t="str">
+        <v/>
+      </c>
+      <c r="Q147" t="str">
+        <v/>
+      </c>
       <c r="R147" t="str">
         <v/>
       </c>
@@ -8623,6 +8675,18 @@
       <c r="M148" t="str">
         <v/>
       </c>
+      <c r="N148" t="str">
+        <v/>
+      </c>
+      <c r="O148" t="str">
+        <v/>
+      </c>
+      <c r="P148" t="str">
+        <v/>
+      </c>
+      <c r="Q148" t="str">
+        <v/>
+      </c>
       <c r="R148" t="str">
         <v/>
       </c>
@@ -8667,6 +8731,18 @@
       <c r="M149" t="str">
         <v/>
       </c>
+      <c r="N149" t="str">
+        <v/>
+      </c>
+      <c r="O149" t="str">
+        <v/>
+      </c>
+      <c r="P149" t="str">
+        <v/>
+      </c>
+      <c r="Q149" t="str">
+        <v/>
+      </c>
       <c r="R149" t="str">
         <v/>
       </c>
@@ -8711,6 +8787,18 @@
       <c r="M150" t="str">
         <v/>
       </c>
+      <c r="N150" t="str">
+        <v/>
+      </c>
+      <c r="O150" t="str">
+        <v/>
+      </c>
+      <c r="P150" t="str">
+        <v/>
+      </c>
+      <c r="Q150" t="str">
+        <v/>
+      </c>
       <c r="R150" t="str">
         <v/>
       </c>
@@ -8755,6 +8843,18 @@
       <c r="M151" t="str">
         <v/>
       </c>
+      <c r="N151" t="str">
+        <v/>
+      </c>
+      <c r="O151" t="str">
+        <v/>
+      </c>
+      <c r="P151" t="str">
+        <v/>
+      </c>
+      <c r="Q151" t="str">
+        <v/>
+      </c>
       <c r="R151" t="str">
         <v/>
       </c>
@@ -8799,6 +8899,18 @@
       <c r="M152" t="str">
         <v/>
       </c>
+      <c r="N152" t="str">
+        <v/>
+      </c>
+      <c r="O152" t="str">
+        <v/>
+      </c>
+      <c r="P152" t="str">
+        <v/>
+      </c>
+      <c r="Q152" t="str">
+        <v/>
+      </c>
       <c r="R152" t="str">
         <v/>
       </c>
@@ -8843,6 +8955,18 @@
       <c r="M153" t="str">
         <v/>
       </c>
+      <c r="N153" t="str">
+        <v/>
+      </c>
+      <c r="O153" t="str">
+        <v/>
+      </c>
+      <c r="P153" t="str">
+        <v/>
+      </c>
+      <c r="Q153" t="str">
+        <v/>
+      </c>
       <c r="R153" t="str">
         <v/>
       </c>
@@ -8887,6 +9011,18 @@
       <c r="M154" t="str">
         <v/>
       </c>
+      <c r="N154" t="str">
+        <v/>
+      </c>
+      <c r="O154" t="str">
+        <v/>
+      </c>
+      <c r="P154" t="str">
+        <v/>
+      </c>
+      <c r="Q154" t="str">
+        <v/>
+      </c>
       <c r="R154" t="str">
         <v/>
       </c>
@@ -8931,6 +9067,18 @@
       <c r="M155" t="str">
         <v/>
       </c>
+      <c r="N155" t="str">
+        <v/>
+      </c>
+      <c r="O155" t="str">
+        <v/>
+      </c>
+      <c r="P155" t="str">
+        <v/>
+      </c>
+      <c r="Q155" t="str">
+        <v/>
+      </c>
       <c r="R155" t="str">
         <v/>
       </c>
@@ -8975,6 +9123,18 @@
       <c r="M156" t="str">
         <v/>
       </c>
+      <c r="N156" t="str">
+        <v/>
+      </c>
+      <c r="O156" t="str">
+        <v/>
+      </c>
+      <c r="P156" t="str">
+        <v/>
+      </c>
+      <c r="Q156" t="str">
+        <v/>
+      </c>
       <c r="R156" t="str">
         <v/>
       </c>
@@ -9019,6 +9179,18 @@
       <c r="M157" t="str">
         <v/>
       </c>
+      <c r="N157" t="str">
+        <v/>
+      </c>
+      <c r="O157" t="str">
+        <v/>
+      </c>
+      <c r="P157" t="str">
+        <v/>
+      </c>
+      <c r="Q157" t="str">
+        <v/>
+      </c>
       <c r="R157" t="str">
         <v/>
       </c>
@@ -9063,6 +9235,18 @@
       <c r="M158" t="str">
         <v/>
       </c>
+      <c r="N158" t="str">
+        <v/>
+      </c>
+      <c r="O158" t="str">
+        <v/>
+      </c>
+      <c r="P158" t="str">
+        <v/>
+      </c>
+      <c r="Q158" t="str">
+        <v/>
+      </c>
       <c r="R158" t="str">
         <v/>
       </c>
@@ -9107,6 +9291,18 @@
       <c r="M159" t="str">
         <v/>
       </c>
+      <c r="N159" t="str">
+        <v/>
+      </c>
+      <c r="O159" t="str">
+        <v/>
+      </c>
+      <c r="P159" t="str">
+        <v/>
+      </c>
+      <c r="Q159" t="str">
+        <v/>
+      </c>
       <c r="R159" t="str">
         <v/>
       </c>
@@ -9151,6 +9347,18 @@
       <c r="M160" t="str">
         <v/>
       </c>
+      <c r="N160" t="str">
+        <v/>
+      </c>
+      <c r="O160" t="str">
+        <v/>
+      </c>
+      <c r="P160" t="str">
+        <v/>
+      </c>
+      <c r="Q160" t="str">
+        <v/>
+      </c>
       <c r="R160" t="str">
         <v/>
       </c>
@@ -9195,6 +9403,18 @@
       <c r="M161" t="str">
         <v/>
       </c>
+      <c r="N161" t="str">
+        <v/>
+      </c>
+      <c r="O161" t="str">
+        <v/>
+      </c>
+      <c r="P161" t="str">
+        <v/>
+      </c>
+      <c r="Q161" t="str">
+        <v/>
+      </c>
       <c r="R161" t="str">
         <v/>
       </c>
@@ -9239,6 +9459,18 @@
       <c r="M162" t="str">
         <v/>
       </c>
+      <c r="N162" t="str">
+        <v/>
+      </c>
+      <c r="O162" t="str">
+        <v/>
+      </c>
+      <c r="P162" t="str">
+        <v/>
+      </c>
+      <c r="Q162" t="str">
+        <v/>
+      </c>
       <c r="R162" t="str">
         <v/>
       </c>
@@ -9283,6 +9515,18 @@
       <c r="M163" t="str">
         <v/>
       </c>
+      <c r="N163" t="str">
+        <v/>
+      </c>
+      <c r="O163" t="str">
+        <v/>
+      </c>
+      <c r="P163" t="str">
+        <v/>
+      </c>
+      <c r="Q163" t="str">
+        <v/>
+      </c>
       <c r="R163" t="str">
         <v/>
       </c>
@@ -9327,6 +9571,18 @@
       <c r="M164" t="str">
         <v/>
       </c>
+      <c r="N164" t="str">
+        <v/>
+      </c>
+      <c r="O164" t="str">
+        <v/>
+      </c>
+      <c r="P164" t="str">
+        <v/>
+      </c>
+      <c r="Q164" t="str">
+        <v/>
+      </c>
       <c r="R164" t="str">
         <v/>
       </c>
@@ -9371,6 +9627,18 @@
       <c r="M165" t="str">
         <v/>
       </c>
+      <c r="N165" t="str">
+        <v/>
+      </c>
+      <c r="O165" t="str">
+        <v/>
+      </c>
+      <c r="P165" t="str">
+        <v/>
+      </c>
+      <c r="Q165" t="str">
+        <v/>
+      </c>
       <c r="R165" t="str">
         <v/>
       </c>
@@ -9415,6 +9683,18 @@
       <c r="M166" t="str">
         <v/>
       </c>
+      <c r="N166" t="str">
+        <v/>
+      </c>
+      <c r="O166" t="str">
+        <v/>
+      </c>
+      <c r="P166" t="str">
+        <v/>
+      </c>
+      <c r="Q166" t="str">
+        <v/>
+      </c>
       <c r="R166" t="str">
         <v/>
       </c>
@@ -9459,6 +9739,18 @@
       <c r="M167" t="str">
         <v/>
       </c>
+      <c r="N167" t="str">
+        <v/>
+      </c>
+      <c r="O167" t="str">
+        <v/>
+      </c>
+      <c r="P167" t="str">
+        <v/>
+      </c>
+      <c r="Q167" t="str">
+        <v/>
+      </c>
       <c r="R167" t="str">
         <v/>
       </c>
@@ -9503,6 +9795,18 @@
       <c r="M168" t="str">
         <v/>
       </c>
+      <c r="N168" t="str">
+        <v/>
+      </c>
+      <c r="O168" t="str">
+        <v/>
+      </c>
+      <c r="P168" t="str">
+        <v/>
+      </c>
+      <c r="Q168" t="str">
+        <v/>
+      </c>
       <c r="R168" t="str">
         <v/>
       </c>
@@ -9547,6 +9851,18 @@
       <c r="M169" t="str">
         <v/>
       </c>
+      <c r="N169" t="str">
+        <v/>
+      </c>
+      <c r="O169" t="str">
+        <v/>
+      </c>
+      <c r="P169" t="str">
+        <v/>
+      </c>
+      <c r="Q169" t="str">
+        <v/>
+      </c>
       <c r="R169" t="str">
         <v/>
       </c>
@@ -9591,6 +9907,18 @@
       <c r="M170" t="str">
         <v/>
       </c>
+      <c r="N170" t="str">
+        <v/>
+      </c>
+      <c r="O170" t="str">
+        <v/>
+      </c>
+      <c r="P170" t="str">
+        <v/>
+      </c>
+      <c r="Q170" t="str">
+        <v/>
+      </c>
       <c r="R170" t="str">
         <v/>
       </c>
@@ -9635,6 +9963,18 @@
       <c r="M171" t="str">
         <v/>
       </c>
+      <c r="N171" t="str">
+        <v/>
+      </c>
+      <c r="O171" t="str">
+        <v/>
+      </c>
+      <c r="P171" t="str">
+        <v/>
+      </c>
+      <c r="Q171" t="str">
+        <v/>
+      </c>
       <c r="R171" t="str">
         <v/>
       </c>
@@ -9679,6 +10019,18 @@
       <c r="M172" t="str">
         <v/>
       </c>
+      <c r="N172" t="str">
+        <v/>
+      </c>
+      <c r="O172" t="str">
+        <v/>
+      </c>
+      <c r="P172" t="str">
+        <v/>
+      </c>
+      <c r="Q172" t="str">
+        <v/>
+      </c>
       <c r="R172" t="str">
         <v/>
       </c>
@@ -9723,6 +10075,18 @@
       <c r="M173" t="str">
         <v/>
       </c>
+      <c r="N173" t="str">
+        <v/>
+      </c>
+      <c r="O173" t="str">
+        <v/>
+      </c>
+      <c r="P173" t="str">
+        <v/>
+      </c>
+      <c r="Q173" t="str">
+        <v/>
+      </c>
       <c r="R173" t="str">
         <v/>
       </c>
@@ -9767,6 +10131,18 @@
       <c r="M174" t="str">
         <v/>
       </c>
+      <c r="N174" t="str">
+        <v/>
+      </c>
+      <c r="O174" t="str">
+        <v/>
+      </c>
+      <c r="P174" t="str">
+        <v/>
+      </c>
+      <c r="Q174" t="str">
+        <v/>
+      </c>
       <c r="R174" t="str">
         <v/>
       </c>
@@ -9811,6 +10187,18 @@
       <c r="M175" t="str">
         <v/>
       </c>
+      <c r="N175" t="str">
+        <v/>
+      </c>
+      <c r="O175" t="str">
+        <v/>
+      </c>
+      <c r="P175" t="str">
+        <v/>
+      </c>
+      <c r="Q175" t="str">
+        <v/>
+      </c>
       <c r="R175" t="str">
         <v/>
       </c>
@@ -9855,6 +10243,18 @@
       <c r="M176" t="str">
         <v/>
       </c>
+      <c r="N176" t="str">
+        <v/>
+      </c>
+      <c r="O176" t="str">
+        <v/>
+      </c>
+      <c r="P176" t="str">
+        <v/>
+      </c>
+      <c r="Q176" t="str">
+        <v/>
+      </c>
       <c r="R176" t="str">
         <v/>
       </c>
@@ -9899,6 +10299,18 @@
       <c r="M177" t="str">
         <v/>
       </c>
+      <c r="N177" t="str">
+        <v/>
+      </c>
+      <c r="O177" t="str">
+        <v/>
+      </c>
+      <c r="P177" t="str">
+        <v/>
+      </c>
+      <c r="Q177" t="str">
+        <v/>
+      </c>
       <c r="R177" t="str">
         <v/>
       </c>
@@ -9943,6 +10355,18 @@
       <c r="M178" t="str">
         <v/>
       </c>
+      <c r="N178" t="str">
+        <v/>
+      </c>
+      <c r="O178" t="str">
+        <v/>
+      </c>
+      <c r="P178" t="str">
+        <v/>
+      </c>
+      <c r="Q178" t="str">
+        <v/>
+      </c>
       <c r="R178" t="str">
         <v/>
       </c>
@@ -9987,6 +10411,18 @@
       <c r="M179" t="str">
         <v/>
       </c>
+      <c r="N179" t="str">
+        <v/>
+      </c>
+      <c r="O179" t="str">
+        <v/>
+      </c>
+      <c r="P179" t="str">
+        <v/>
+      </c>
+      <c r="Q179" t="str">
+        <v/>
+      </c>
       <c r="R179" t="str">
         <v/>
       </c>
@@ -10031,6 +10467,18 @@
       <c r="M180" t="str">
         <v/>
       </c>
+      <c r="N180" t="str">
+        <v/>
+      </c>
+      <c r="O180" t="str">
+        <v/>
+      </c>
+      <c r="P180" t="str">
+        <v/>
+      </c>
+      <c r="Q180" t="str">
+        <v/>
+      </c>
       <c r="R180" t="str">
         <v/>
       </c>
@@ -10075,6 +10523,18 @@
       <c r="M181" t="str">
         <v/>
       </c>
+      <c r="N181" t="str">
+        <v/>
+      </c>
+      <c r="O181" t="str">
+        <v/>
+      </c>
+      <c r="P181" t="str">
+        <v/>
+      </c>
+      <c r="Q181" t="str">
+        <v/>
+      </c>
       <c r="R181" t="str">
         <v/>
       </c>
@@ -10119,6 +10579,18 @@
       <c r="M182" t="str">
         <v/>
       </c>
+      <c r="N182" t="str">
+        <v/>
+      </c>
+      <c r="O182" t="str">
+        <v/>
+      </c>
+      <c r="P182" t="str">
+        <v/>
+      </c>
+      <c r="Q182" t="str">
+        <v/>
+      </c>
       <c r="R182" t="str">
         <v/>
       </c>
@@ -10163,6 +10635,18 @@
       <c r="M183" t="str">
         <v/>
       </c>
+      <c r="N183" t="str">
+        <v/>
+      </c>
+      <c r="O183" t="str">
+        <v/>
+      </c>
+      <c r="P183" t="str">
+        <v/>
+      </c>
+      <c r="Q183" t="str">
+        <v/>
+      </c>
       <c r="R183" t="str">
         <v/>
       </c>
@@ -10207,6 +10691,18 @@
       <c r="M184" t="str">
         <v/>
       </c>
+      <c r="N184" t="str">
+        <v/>
+      </c>
+      <c r="O184" t="str">
+        <v/>
+      </c>
+      <c r="P184" t="str">
+        <v/>
+      </c>
+      <c r="Q184" t="str">
+        <v/>
+      </c>
       <c r="R184" t="str">
         <v/>
       </c>
@@ -10251,6 +10747,18 @@
       <c r="M185" t="str">
         <v/>
       </c>
+      <c r="N185" t="str">
+        <v/>
+      </c>
+      <c r="O185" t="str">
+        <v/>
+      </c>
+      <c r="P185" t="str">
+        <v/>
+      </c>
+      <c r="Q185" t="str">
+        <v/>
+      </c>
       <c r="R185" t="str">
         <v/>
       </c>
@@ -10295,6 +10803,18 @@
       <c r="M186" t="str">
         <v/>
       </c>
+      <c r="N186" t="str">
+        <v/>
+      </c>
+      <c r="O186" t="str">
+        <v/>
+      </c>
+      <c r="P186" t="str">
+        <v/>
+      </c>
+      <c r="Q186" t="str">
+        <v/>
+      </c>
       <c r="R186" t="str">
         <v/>
       </c>
@@ -10339,6 +10859,18 @@
       <c r="M187" t="str">
         <v/>
       </c>
+      <c r="N187" t="str">
+        <v/>
+      </c>
+      <c r="O187" t="str">
+        <v/>
+      </c>
+      <c r="P187" t="str">
+        <v/>
+      </c>
+      <c r="Q187" t="str">
+        <v/>
+      </c>
       <c r="R187" t="str">
         <v/>
       </c>
@@ -10383,6 +10915,18 @@
       <c r="M188" t="str">
         <v/>
       </c>
+      <c r="N188" t="str">
+        <v/>
+      </c>
+      <c r="O188" t="str">
+        <v/>
+      </c>
+      <c r="P188" t="str">
+        <v/>
+      </c>
+      <c r="Q188" t="str">
+        <v/>
+      </c>
       <c r="R188" t="str">
         <v/>
       </c>
@@ -10427,6 +10971,18 @@
       <c r="M189" t="str">
         <v/>
       </c>
+      <c r="N189" t="str">
+        <v/>
+      </c>
+      <c r="O189" t="str">
+        <v/>
+      </c>
+      <c r="P189" t="str">
+        <v/>
+      </c>
+      <c r="Q189" t="str">
+        <v/>
+      </c>
       <c r="R189" t="str">
         <v/>
       </c>
@@ -10471,6 +11027,18 @@
       <c r="M190" t="str">
         <v/>
       </c>
+      <c r="N190" t="str">
+        <v/>
+      </c>
+      <c r="O190" t="str">
+        <v/>
+      </c>
+      <c r="P190" t="str">
+        <v/>
+      </c>
+      <c r="Q190" t="str">
+        <v/>
+      </c>
       <c r="R190" t="str">
         <v/>
       </c>
@@ -10515,6 +11083,18 @@
       <c r="M191" t="str">
         <v/>
       </c>
+      <c r="N191" t="str">
+        <v/>
+      </c>
+      <c r="O191" t="str">
+        <v/>
+      </c>
+      <c r="P191" t="str">
+        <v/>
+      </c>
+      <c r="Q191" t="str">
+        <v/>
+      </c>
       <c r="R191" t="str">
         <v/>
       </c>
@@ -10559,6 +11139,18 @@
       <c r="M192" t="str">
         <v/>
       </c>
+      <c r="N192" t="str">
+        <v/>
+      </c>
+      <c r="O192" t="str">
+        <v/>
+      </c>
+      <c r="P192" t="str">
+        <v/>
+      </c>
+      <c r="Q192" t="str">
+        <v/>
+      </c>
       <c r="R192" t="str">
         <v>10</v>
       </c>
@@ -10603,6 +11195,18 @@
       <c r="M193" t="str">
         <v/>
       </c>
+      <c r="N193" t="str">
+        <v/>
+      </c>
+      <c r="O193" t="str">
+        <v/>
+      </c>
+      <c r="P193" t="str">
+        <v/>
+      </c>
+      <c r="Q193" t="str">
+        <v/>
+      </c>
       <c r="R193" t="str">
         <v>8</v>
       </c>
@@ -10647,6 +11251,18 @@
       <c r="M194" t="str">
         <v/>
       </c>
+      <c r="N194" t="str">
+        <v/>
+      </c>
+      <c r="O194" t="str">
+        <v/>
+      </c>
+      <c r="P194" t="str">
+        <v/>
+      </c>
+      <c r="Q194" t="str">
+        <v/>
+      </c>
       <c r="R194" t="str">
         <v>5</v>
       </c>
@@ -10691,6 +11307,18 @@
       <c r="M195" t="str">
         <v/>
       </c>
+      <c r="N195" t="str">
+        <v/>
+      </c>
+      <c r="O195" t="str">
+        <v/>
+      </c>
+      <c r="P195" t="str">
+        <v/>
+      </c>
+      <c r="Q195" t="str">
+        <v/>
+      </c>
       <c r="R195" t="str">
         <v>5</v>
       </c>
@@ -10735,6 +11363,18 @@
       <c r="M196" t="str">
         <v/>
       </c>
+      <c r="N196" t="str">
+        <v/>
+      </c>
+      <c r="O196" t="str">
+        <v/>
+      </c>
+      <c r="P196" t="str">
+        <v/>
+      </c>
+      <c r="Q196" t="str">
+        <v/>
+      </c>
       <c r="R196" t="str">
         <v>5</v>
       </c>
@@ -10779,6 +11419,18 @@
       <c r="M197" t="str">
         <v/>
       </c>
+      <c r="N197" t="str">
+        <v/>
+      </c>
+      <c r="O197" t="str">
+        <v/>
+      </c>
+      <c r="P197" t="str">
+        <v/>
+      </c>
+      <c r="Q197" t="str">
+        <v/>
+      </c>
       <c r="R197" t="str">
         <v>5</v>
       </c>
@@ -10823,6 +11475,18 @@
       <c r="M198" t="str">
         <v/>
       </c>
+      <c r="N198" t="str">
+        <v/>
+      </c>
+      <c r="O198" t="str">
+        <v/>
+      </c>
+      <c r="P198" t="str">
+        <v/>
+      </c>
+      <c r="Q198" t="str">
+        <v/>
+      </c>
       <c r="R198" t="str">
         <v>5</v>
       </c>
@@ -10867,6 +11531,18 @@
       <c r="M199" t="str">
         <v/>
       </c>
+      <c r="N199" t="str">
+        <v/>
+      </c>
+      <c r="O199" t="str">
+        <v/>
+      </c>
+      <c r="P199" t="str">
+        <v/>
+      </c>
+      <c r="Q199" t="str">
+        <v/>
+      </c>
       <c r="R199" t="str">
         <v>5</v>
       </c>
@@ -10911,6 +11587,18 @@
       <c r="M200" t="str">
         <v/>
       </c>
+      <c r="N200" t="str">
+        <v/>
+      </c>
+      <c r="O200" t="str">
+        <v/>
+      </c>
+      <c r="P200" t="str">
+        <v/>
+      </c>
+      <c r="Q200" t="str">
+        <v/>
+      </c>
       <c r="R200" t="str">
         <v>5</v>
       </c>
@@ -10955,6 +11643,18 @@
       <c r="M201" t="str">
         <v/>
       </c>
+      <c r="N201" t="str">
+        <v/>
+      </c>
+      <c r="O201" t="str">
+        <v/>
+      </c>
+      <c r="P201" t="str">
+        <v/>
+      </c>
+      <c r="Q201" t="str">
+        <v/>
+      </c>
       <c r="R201" t="str">
         <v>5</v>
       </c>
@@ -10999,6 +11699,18 @@
       <c r="M202" t="str">
         <v/>
       </c>
+      <c r="N202" t="str">
+        <v/>
+      </c>
+      <c r="O202" t="str">
+        <v/>
+      </c>
+      <c r="P202" t="str">
+        <v/>
+      </c>
+      <c r="Q202" t="str">
+        <v/>
+      </c>
       <c r="R202" t="str">
         <v>5</v>
       </c>
@@ -11043,6 +11755,18 @@
       <c r="M203" t="str">
         <v/>
       </c>
+      <c r="N203" t="str">
+        <v/>
+      </c>
+      <c r="O203" t="str">
+        <v/>
+      </c>
+      <c r="P203" t="str">
+        <v/>
+      </c>
+      <c r="Q203" t="str">
+        <v/>
+      </c>
       <c r="R203" t="str">
         <v>5</v>
       </c>
@@ -11087,6 +11811,18 @@
       <c r="M204" t="str">
         <v/>
       </c>
+      <c r="N204" t="str">
+        <v/>
+      </c>
+      <c r="O204" t="str">
+        <v/>
+      </c>
+      <c r="P204" t="str">
+        <v/>
+      </c>
+      <c r="Q204" t="str">
+        <v/>
+      </c>
       <c r="R204" t="str">
         <v>5</v>
       </c>
@@ -11131,6 +11867,18 @@
       <c r="M205" t="str">
         <v/>
       </c>
+      <c r="N205" t="str">
+        <v/>
+      </c>
+      <c r="O205" t="str">
+        <v/>
+      </c>
+      <c r="P205" t="str">
+        <v/>
+      </c>
+      <c r="Q205" t="str">
+        <v/>
+      </c>
       <c r="R205" t="str">
         <v>6</v>
       </c>
@@ -11175,6 +11923,18 @@
       <c r="M206" t="str">
         <v/>
       </c>
+      <c r="N206" t="str">
+        <v/>
+      </c>
+      <c r="O206" t="str">
+        <v/>
+      </c>
+      <c r="P206" t="str">
+        <v/>
+      </c>
+      <c r="Q206" t="str">
+        <v/>
+      </c>
       <c r="R206" t="str">
         <v>6</v>
       </c>
@@ -11219,6 +11979,18 @@
       <c r="M207" t="str">
         <v/>
       </c>
+      <c r="N207" t="str">
+        <v/>
+      </c>
+      <c r="O207" t="str">
+        <v/>
+      </c>
+      <c r="P207" t="str">
+        <v/>
+      </c>
+      <c r="Q207" t="str">
+        <v/>
+      </c>
       <c r="R207" t="str">
         <v>6</v>
       </c>
@@ -11263,6 +12035,18 @@
       <c r="M208" t="str">
         <v/>
       </c>
+      <c r="N208" t="str">
+        <v/>
+      </c>
+      <c r="O208" t="str">
+        <v/>
+      </c>
+      <c r="P208" t="str">
+        <v/>
+      </c>
+      <c r="Q208" t="str">
+        <v/>
+      </c>
       <c r="R208" t="str">
         <v>6</v>
       </c>
@@ -11307,6 +12091,18 @@
       <c r="M209" t="str">
         <v/>
       </c>
+      <c r="N209" t="str">
+        <v/>
+      </c>
+      <c r="O209" t="str">
+        <v/>
+      </c>
+      <c r="P209" t="str">
+        <v/>
+      </c>
+      <c r="Q209" t="str">
+        <v/>
+      </c>
       <c r="R209" t="str">
         <v>6</v>
       </c>
@@ -11351,6 +12147,18 @@
       <c r="M210" t="str">
         <v/>
       </c>
+      <c r="N210" t="str">
+        <v/>
+      </c>
+      <c r="O210" t="str">
+        <v/>
+      </c>
+      <c r="P210" t="str">
+        <v/>
+      </c>
+      <c r="Q210" t="str">
+        <v/>
+      </c>
       <c r="R210" t="str">
         <v>6</v>
       </c>
@@ -11395,6 +12203,18 @@
       <c r="M211" t="str">
         <v/>
       </c>
+      <c r="N211" t="str">
+        <v/>
+      </c>
+      <c r="O211" t="str">
+        <v/>
+      </c>
+      <c r="P211" t="str">
+        <v/>
+      </c>
+      <c r="Q211" t="str">
+        <v/>
+      </c>
       <c r="R211" t="str">
         <v>6</v>
       </c>
@@ -11439,6 +12259,18 @@
       <c r="M212" t="str">
         <v/>
       </c>
+      <c r="N212" t="str">
+        <v/>
+      </c>
+      <c r="O212" t="str">
+        <v/>
+      </c>
+      <c r="P212" t="str">
+        <v/>
+      </c>
+      <c r="Q212" t="str">
+        <v/>
+      </c>
       <c r="R212" t="str">
         <v>6</v>
       </c>
@@ -11483,6 +12315,18 @@
       <c r="M213" t="str">
         <v/>
       </c>
+      <c r="N213" t="str">
+        <v/>
+      </c>
+      <c r="O213" t="str">
+        <v/>
+      </c>
+      <c r="P213" t="str">
+        <v/>
+      </c>
+      <c r="Q213" t="str">
+        <v/>
+      </c>
       <c r="R213" t="str">
         <v>6</v>
       </c>
@@ -11527,6 +12371,18 @@
       <c r="M214" t="str">
         <v/>
       </c>
+      <c r="N214" t="str">
+        <v/>
+      </c>
+      <c r="O214" t="str">
+        <v/>
+      </c>
+      <c r="P214" t="str">
+        <v/>
+      </c>
+      <c r="Q214" t="str">
+        <v/>
+      </c>
       <c r="R214" t="str">
         <v>6</v>
       </c>
@@ -11571,6 +12427,18 @@
       <c r="M215" t="str">
         <v/>
       </c>
+      <c r="N215" t="str">
+        <v/>
+      </c>
+      <c r="O215" t="str">
+        <v/>
+      </c>
+      <c r="P215" t="str">
+        <v/>
+      </c>
+      <c r="Q215" t="str">
+        <v/>
+      </c>
       <c r="R215" t="str">
         <v>6</v>
       </c>
@@ -11615,6 +12483,18 @@
       <c r="M216" t="str">
         <v/>
       </c>
+      <c r="N216" t="str">
+        <v/>
+      </c>
+      <c r="O216" t="str">
+        <v/>
+      </c>
+      <c r="P216" t="str">
+        <v/>
+      </c>
+      <c r="Q216" t="str">
+        <v/>
+      </c>
       <c r="R216" t="str">
         <v>2</v>
       </c>
@@ -11659,6 +12539,18 @@
       <c r="M217" t="str">
         <v/>
       </c>
+      <c r="N217" t="str">
+        <v/>
+      </c>
+      <c r="O217" t="str">
+        <v/>
+      </c>
+      <c r="P217" t="str">
+        <v/>
+      </c>
+      <c r="Q217" t="str">
+        <v/>
+      </c>
       <c r="R217" t="str">
         <v>2</v>
       </c>
@@ -11703,6 +12595,18 @@
       <c r="M218" t="str">
         <v/>
       </c>
+      <c r="N218" t="str">
+        <v/>
+      </c>
+      <c r="O218" t="str">
+        <v/>
+      </c>
+      <c r="P218" t="str">
+        <v/>
+      </c>
+      <c r="Q218" t="str">
+        <v/>
+      </c>
       <c r="R218" t="str">
         <v>2</v>
       </c>
@@ -11747,6 +12651,18 @@
       <c r="M219" t="str">
         <v/>
       </c>
+      <c r="N219" t="str">
+        <v/>
+      </c>
+      <c r="O219" t="str">
+        <v/>
+      </c>
+      <c r="P219" t="str">
+        <v/>
+      </c>
+      <c r="Q219" t="str">
+        <v/>
+      </c>
       <c r="R219" t="str">
         <v>2</v>
       </c>
@@ -11791,6 +12707,18 @@
       <c r="M220" t="str">
         <v/>
       </c>
+      <c r="N220" t="str">
+        <v/>
+      </c>
+      <c r="O220" t="str">
+        <v/>
+      </c>
+      <c r="P220" t="str">
+        <v/>
+      </c>
+      <c r="Q220" t="str">
+        <v/>
+      </c>
       <c r="R220" t="str">
         <v>2</v>
       </c>
@@ -11835,6 +12763,18 @@
       <c r="M221" t="str">
         <v/>
       </c>
+      <c r="N221" t="str">
+        <v/>
+      </c>
+      <c r="O221" t="str">
+        <v/>
+      </c>
+      <c r="P221" t="str">
+        <v/>
+      </c>
+      <c r="Q221" t="str">
+        <v/>
+      </c>
       <c r="R221" t="str">
         <v>2</v>
       </c>
@@ -11879,6 +12819,18 @@
       <c r="M222" t="str">
         <v/>
       </c>
+      <c r="N222" t="str">
+        <v/>
+      </c>
+      <c r="O222" t="str">
+        <v/>
+      </c>
+      <c r="P222" t="str">
+        <v/>
+      </c>
+      <c r="Q222" t="str">
+        <v/>
+      </c>
       <c r="R222" t="str">
         <v>12</v>
       </c>
@@ -11923,6 +12875,18 @@
       <c r="M223" t="str">
         <v/>
       </c>
+      <c r="N223" t="str">
+        <v/>
+      </c>
+      <c r="O223" t="str">
+        <v/>
+      </c>
+      <c r="P223" t="str">
+        <v/>
+      </c>
+      <c r="Q223" t="str">
+        <v/>
+      </c>
       <c r="R223" t="str">
         <v>10</v>
       </c>
@@ -11967,6 +12931,18 @@
       <c r="M224" t="str">
         <v/>
       </c>
+      <c r="N224" t="str">
+        <v/>
+      </c>
+      <c r="O224" t="str">
+        <v/>
+      </c>
+      <c r="P224" t="str">
+        <v/>
+      </c>
+      <c r="Q224" t="str">
+        <v/>
+      </c>
       <c r="R224" t="str">
         <v>10</v>
       </c>
@@ -12011,6 +12987,18 @@
       <c r="M225" t="str">
         <v/>
       </c>
+      <c r="N225" t="str">
+        <v/>
+      </c>
+      <c r="O225" t="str">
+        <v/>
+      </c>
+      <c r="P225" t="str">
+        <v/>
+      </c>
+      <c r="Q225" t="str">
+        <v/>
+      </c>
       <c r="R225" t="str">
         <v>10</v>
       </c>
@@ -12055,6 +13043,18 @@
       <c r="M226" t="str">
         <v/>
       </c>
+      <c r="N226" t="str">
+        <v/>
+      </c>
+      <c r="O226" t="str">
+        <v/>
+      </c>
+      <c r="P226" t="str">
+        <v/>
+      </c>
+      <c r="Q226" t="str">
+        <v/>
+      </c>
       <c r="R226" t="str">
         <v>10</v>
       </c>
@@ -12099,6 +13099,18 @@
       <c r="M227" t="str">
         <v/>
       </c>
+      <c r="N227" t="str">
+        <v/>
+      </c>
+      <c r="O227" t="str">
+        <v/>
+      </c>
+      <c r="P227" t="str">
+        <v/>
+      </c>
+      <c r="Q227" t="str">
+        <v/>
+      </c>
       <c r="R227" t="str">
         <v>6</v>
       </c>
@@ -12143,6 +13155,18 @@
       <c r="M228" t="str">
         <v/>
       </c>
+      <c r="N228" t="str">
+        <v/>
+      </c>
+      <c r="O228" t="str">
+        <v/>
+      </c>
+      <c r="P228" t="str">
+        <v/>
+      </c>
+      <c r="Q228" t="str">
+        <v/>
+      </c>
       <c r="R228" t="str">
         <v>10</v>
       </c>
@@ -12187,6 +13211,18 @@
       <c r="M229" t="str">
         <v/>
       </c>
+      <c r="N229" t="str">
+        <v/>
+      </c>
+      <c r="O229" t="str">
+        <v/>
+      </c>
+      <c r="P229" t="str">
+        <v/>
+      </c>
+      <c r="Q229" t="str">
+        <v/>
+      </c>
       <c r="R229" t="str">
         <v>10</v>
       </c>
@@ -12231,6 +13267,18 @@
       <c r="M230" t="str">
         <v/>
       </c>
+      <c r="N230" t="str">
+        <v/>
+      </c>
+      <c r="O230" t="str">
+        <v/>
+      </c>
+      <c r="P230" t="str">
+        <v/>
+      </c>
+      <c r="Q230" t="str">
+        <v/>
+      </c>
       <c r="R230" t="str">
         <v>10</v>
       </c>
@@ -12275,6 +13323,18 @@
       <c r="M231" t="str">
         <v/>
       </c>
+      <c r="N231" t="str">
+        <v/>
+      </c>
+      <c r="O231" t="str">
+        <v/>
+      </c>
+      <c r="P231" t="str">
+        <v/>
+      </c>
+      <c r="Q231" t="str">
+        <v/>
+      </c>
       <c r="R231" t="str">
         <v>10</v>
       </c>
@@ -12319,6 +13379,18 @@
       <c r="M232" t="str">
         <v/>
       </c>
+      <c r="N232" t="str">
+        <v/>
+      </c>
+      <c r="O232" t="str">
+        <v/>
+      </c>
+      <c r="P232" t="str">
+        <v/>
+      </c>
+      <c r="Q232" t="str">
+        <v/>
+      </c>
       <c r="R232" t="str">
         <v>10</v>
       </c>
@@ -12363,6 +13435,18 @@
       <c r="M233" t="str">
         <v/>
       </c>
+      <c r="N233" t="str">
+        <v/>
+      </c>
+      <c r="O233" t="str">
+        <v/>
+      </c>
+      <c r="P233" t="str">
+        <v/>
+      </c>
+      <c r="Q233" t="str">
+        <v/>
+      </c>
       <c r="R233" t="str">
         <v>10</v>
       </c>
@@ -12407,6 +13491,18 @@
       <c r="M234" t="str">
         <v/>
       </c>
+      <c r="N234" t="str">
+        <v/>
+      </c>
+      <c r="O234" t="str">
+        <v/>
+      </c>
+      <c r="P234" t="str">
+        <v/>
+      </c>
+      <c r="Q234" t="str">
+        <v/>
+      </c>
       <c r="R234" t="str">
         <v>10</v>
       </c>
@@ -12451,6 +13547,18 @@
       <c r="M235" t="str">
         <v/>
       </c>
+      <c r="N235" t="str">
+        <v/>
+      </c>
+      <c r="O235" t="str">
+        <v/>
+      </c>
+      <c r="P235" t="str">
+        <v/>
+      </c>
+      <c r="Q235" t="str">
+        <v/>
+      </c>
       <c r="R235" t="str">
         <v>10</v>
       </c>
@@ -12495,6 +13603,18 @@
       <c r="M236" t="str">
         <v/>
       </c>
+      <c r="N236" t="str">
+        <v/>
+      </c>
+      <c r="O236" t="str">
+        <v/>
+      </c>
+      <c r="P236" t="str">
+        <v/>
+      </c>
+      <c r="Q236" t="str">
+        <v/>
+      </c>
       <c r="R236" t="str">
         <v>10</v>
       </c>
@@ -12539,6 +13659,18 @@
       <c r="M237" t="str">
         <v/>
       </c>
+      <c r="N237" t="str">
+        <v/>
+      </c>
+      <c r="O237" t="str">
+        <v/>
+      </c>
+      <c r="P237" t="str">
+        <v/>
+      </c>
+      <c r="Q237" t="str">
+        <v/>
+      </c>
       <c r="R237" t="str">
         <v>10</v>
       </c>
@@ -12583,6 +13715,18 @@
       <c r="M238" t="str">
         <v/>
       </c>
+      <c r="N238" t="str">
+        <v/>
+      </c>
+      <c r="O238" t="str">
+        <v/>
+      </c>
+      <c r="P238" t="str">
+        <v/>
+      </c>
+      <c r="Q238" t="str">
+        <v/>
+      </c>
       <c r="R238" t="str">
         <v>7</v>
       </c>
@@ -12627,6 +13771,18 @@
       <c r="M239" t="str">
         <v/>
       </c>
+      <c r="N239" t="str">
+        <v/>
+      </c>
+      <c r="O239" t="str">
+        <v/>
+      </c>
+      <c r="P239" t="str">
+        <v/>
+      </c>
+      <c r="Q239" t="str">
+        <v/>
+      </c>
       <c r="R239" t="str">
         <v>10</v>
       </c>
@@ -12671,6 +13827,18 @@
       <c r="M240" t="str">
         <v/>
       </c>
+      <c r="N240" t="str">
+        <v/>
+      </c>
+      <c r="O240" t="str">
+        <v/>
+      </c>
+      <c r="P240" t="str">
+        <v/>
+      </c>
+      <c r="Q240" t="str">
+        <v/>
+      </c>
       <c r="R240" t="str">
         <v>10</v>
       </c>
@@ -12715,6 +13883,18 @@
       <c r="M241" t="str">
         <v/>
       </c>
+      <c r="N241" t="str">
+        <v/>
+      </c>
+      <c r="O241" t="str">
+        <v/>
+      </c>
+      <c r="P241" t="str">
+        <v/>
+      </c>
+      <c r="Q241" t="str">
+        <v/>
+      </c>
       <c r="R241" t="str">
         <v>10</v>
       </c>
@@ -12759,6 +13939,18 @@
       <c r="M242" t="str">
         <v/>
       </c>
+      <c r="N242" t="str">
+        <v/>
+      </c>
+      <c r="O242" t="str">
+        <v/>
+      </c>
+      <c r="P242" t="str">
+        <v/>
+      </c>
+      <c r="Q242" t="str">
+        <v/>
+      </c>
       <c r="R242" t="str">
         <v>10</v>
       </c>
@@ -12803,6 +13995,18 @@
       <c r="M243" t="str">
         <v/>
       </c>
+      <c r="N243" t="str">
+        <v/>
+      </c>
+      <c r="O243" t="str">
+        <v/>
+      </c>
+      <c r="P243" t="str">
+        <v/>
+      </c>
+      <c r="Q243" t="str">
+        <v/>
+      </c>
       <c r="R243" t="str">
         <v>10</v>
       </c>
@@ -12847,6 +14051,18 @@
       <c r="M244" t="str">
         <v/>
       </c>
+      <c r="N244" t="str">
+        <v/>
+      </c>
+      <c r="O244" t="str">
+        <v/>
+      </c>
+      <c r="P244" t="str">
+        <v/>
+      </c>
+      <c r="Q244" t="str">
+        <v/>
+      </c>
       <c r="R244" t="str">
         <v>10</v>
       </c>
@@ -12891,6 +14107,18 @@
       <c r="M245" t="str">
         <v/>
       </c>
+      <c r="N245" t="str">
+        <v/>
+      </c>
+      <c r="O245" t="str">
+        <v/>
+      </c>
+      <c r="P245" t="str">
+        <v/>
+      </c>
+      <c r="Q245" t="str">
+        <v/>
+      </c>
       <c r="R245" t="str">
         <v>8</v>
       </c>
@@ -12935,6 +14163,18 @@
       <c r="M246" t="str">
         <v/>
       </c>
+      <c r="N246" t="str">
+        <v/>
+      </c>
+      <c r="O246" t="str">
+        <v/>
+      </c>
+      <c r="P246" t="str">
+        <v/>
+      </c>
+      <c r="Q246" t="str">
+        <v/>
+      </c>
       <c r="R246" t="str">
         <v>8</v>
       </c>
@@ -12979,6 +14219,18 @@
       <c r="M247" t="str">
         <v/>
       </c>
+      <c r="N247" t="str">
+        <v/>
+      </c>
+      <c r="O247" t="str">
+        <v/>
+      </c>
+      <c r="P247" t="str">
+        <v/>
+      </c>
+      <c r="Q247" t="str">
+        <v/>
+      </c>
       <c r="R247" t="str">
         <v>8</v>
       </c>
@@ -13023,6 +14275,18 @@
       <c r="M248" t="str">
         <v/>
       </c>
+      <c r="N248" t="str">
+        <v/>
+      </c>
+      <c r="O248" t="str">
+        <v/>
+      </c>
+      <c r="P248" t="str">
+        <v/>
+      </c>
+      <c r="Q248" t="str">
+        <v/>
+      </c>
       <c r="R248" t="str">
         <v>8</v>
       </c>
@@ -13067,6 +14331,18 @@
       <c r="M249" t="str">
         <v/>
       </c>
+      <c r="N249" t="str">
+        <v/>
+      </c>
+      <c r="O249" t="str">
+        <v/>
+      </c>
+      <c r="P249" t="str">
+        <v/>
+      </c>
+      <c r="Q249" t="str">
+        <v/>
+      </c>
       <c r="R249" t="str">
         <v>8</v>
       </c>
@@ -13111,6 +14387,18 @@
       <c r="M250" t="str">
         <v/>
       </c>
+      <c r="N250" t="str">
+        <v/>
+      </c>
+      <c r="O250" t="str">
+        <v/>
+      </c>
+      <c r="P250" t="str">
+        <v/>
+      </c>
+      <c r="Q250" t="str">
+        <v/>
+      </c>
       <c r="R250" t="str">
         <v>8</v>
       </c>
@@ -13155,6 +14443,18 @@
       <c r="M251" t="str">
         <v/>
       </c>
+      <c r="N251" t="str">
+        <v/>
+      </c>
+      <c r="O251" t="str">
+        <v/>
+      </c>
+      <c r="P251" t="str">
+        <v/>
+      </c>
+      <c r="Q251" t="str">
+        <v/>
+      </c>
       <c r="R251" t="str">
         <v>7</v>
       </c>
@@ -13199,6 +14499,18 @@
       <c r="M252" t="str">
         <v/>
       </c>
+      <c r="N252" t="str">
+        <v/>
+      </c>
+      <c r="O252" t="str">
+        <v/>
+      </c>
+      <c r="P252" t="str">
+        <v/>
+      </c>
+      <c r="Q252" t="str">
+        <v/>
+      </c>
       <c r="R252" t="str">
         <v>7</v>
       </c>
@@ -13243,6 +14555,18 @@
       <c r="M253" t="str">
         <v/>
       </c>
+      <c r="N253" t="str">
+        <v/>
+      </c>
+      <c r="O253" t="str">
+        <v/>
+      </c>
+      <c r="P253" t="str">
+        <v/>
+      </c>
+      <c r="Q253" t="str">
+        <v/>
+      </c>
       <c r="R253" t="str">
         <v>7</v>
       </c>
@@ -13287,6 +14611,18 @@
       <c r="M254" t="str">
         <v/>
       </c>
+      <c r="N254" t="str">
+        <v/>
+      </c>
+      <c r="O254" t="str">
+        <v/>
+      </c>
+      <c r="P254" t="str">
+        <v/>
+      </c>
+      <c r="Q254" t="str">
+        <v/>
+      </c>
       <c r="R254" t="str">
         <v>7</v>
       </c>
@@ -13331,6 +14667,18 @@
       <c r="M255" t="str">
         <v/>
       </c>
+      <c r="N255" t="str">
+        <v/>
+      </c>
+      <c r="O255" t="str">
+        <v/>
+      </c>
+      <c r="P255" t="str">
+        <v/>
+      </c>
+      <c r="Q255" t="str">
+        <v/>
+      </c>
       <c r="R255" t="str">
         <v>7</v>
       </c>
@@ -13375,6 +14723,18 @@
       <c r="M256" t="str">
         <v/>
       </c>
+      <c r="N256" t="str">
+        <v/>
+      </c>
+      <c r="O256" t="str">
+        <v/>
+      </c>
+      <c r="P256" t="str">
+        <v/>
+      </c>
+      <c r="Q256" t="str">
+        <v/>
+      </c>
       <c r="R256" t="str">
         <v>7</v>
       </c>
@@ -13419,6 +14779,18 @@
       <c r="M257" t="str">
         <v/>
       </c>
+      <c r="N257" t="str">
+        <v/>
+      </c>
+      <c r="O257" t="str">
+        <v/>
+      </c>
+      <c r="P257" t="str">
+        <v/>
+      </c>
+      <c r="Q257" t="str">
+        <v/>
+      </c>
       <c r="R257" t="str">
         <v/>
       </c>
@@ -13463,6 +14835,18 @@
       <c r="M258" t="str">
         <v/>
       </c>
+      <c r="N258" t="str">
+        <v/>
+      </c>
+      <c r="O258" t="str">
+        <v/>
+      </c>
+      <c r="P258" t="str">
+        <v/>
+      </c>
+      <c r="Q258" t="str">
+        <v/>
+      </c>
       <c r="R258" t="str">
         <v/>
       </c>
@@ -13507,6 +14891,18 @@
       <c r="M259" t="str">
         <v/>
       </c>
+      <c r="N259" t="str">
+        <v/>
+      </c>
+      <c r="O259" t="str">
+        <v/>
+      </c>
+      <c r="P259" t="str">
+        <v/>
+      </c>
+      <c r="Q259" t="str">
+        <v/>
+      </c>
       <c r="R259" t="str">
         <v/>
       </c>
@@ -13551,6 +14947,18 @@
       <c r="M260" t="str">
         <v/>
       </c>
+      <c r="N260" t="str">
+        <v/>
+      </c>
+      <c r="O260" t="str">
+        <v/>
+      </c>
+      <c r="P260" t="str">
+        <v/>
+      </c>
+      <c r="Q260" t="str">
+        <v/>
+      </c>
       <c r="R260" t="str">
         <v/>
       </c>
@@ -13595,6 +15003,18 @@
       <c r="M261" t="str">
         <v/>
       </c>
+      <c r="N261" t="str">
+        <v/>
+      </c>
+      <c r="O261" t="str">
+        <v/>
+      </c>
+      <c r="P261" t="str">
+        <v/>
+      </c>
+      <c r="Q261" t="str">
+        <v/>
+      </c>
       <c r="R261" t="str">
         <v/>
       </c>
@@ -13639,6 +15059,18 @@
       <c r="M262" t="str">
         <v/>
       </c>
+      <c r="N262" t="str">
+        <v/>
+      </c>
+      <c r="O262" t="str">
+        <v/>
+      </c>
+      <c r="P262" t="str">
+        <v/>
+      </c>
+      <c r="Q262" t="str">
+        <v/>
+      </c>
       <c r="R262" t="str">
         <v/>
       </c>
@@ -13683,6 +15115,18 @@
       <c r="M263" t="str">
         <v/>
       </c>
+      <c r="N263" t="str">
+        <v/>
+      </c>
+      <c r="O263" t="str">
+        <v/>
+      </c>
+      <c r="P263" t="str">
+        <v/>
+      </c>
+      <c r="Q263" t="str">
+        <v/>
+      </c>
       <c r="R263" t="str">
         <v/>
       </c>
@@ -13727,6 +15171,18 @@
       <c r="M264" t="str">
         <v/>
       </c>
+      <c r="N264" t="str">
+        <v/>
+      </c>
+      <c r="O264" t="str">
+        <v/>
+      </c>
+      <c r="P264" t="str">
+        <v/>
+      </c>
+      <c r="Q264" t="str">
+        <v/>
+      </c>
       <c r="R264" t="str">
         <v/>
       </c>
@@ -13771,6 +15227,18 @@
       <c r="M265" t="str">
         <v/>
       </c>
+      <c r="N265" t="str">
+        <v/>
+      </c>
+      <c r="O265" t="str">
+        <v/>
+      </c>
+      <c r="P265" t="str">
+        <v/>
+      </c>
+      <c r="Q265" t="str">
+        <v/>
+      </c>
       <c r="R265" t="str">
         <v/>
       </c>
@@ -13815,6 +15283,18 @@
       <c r="M266" t="str">
         <v/>
       </c>
+      <c r="N266" t="str">
+        <v/>
+      </c>
+      <c r="O266" t="str">
+        <v/>
+      </c>
+      <c r="P266" t="str">
+        <v/>
+      </c>
+      <c r="Q266" t="str">
+        <v/>
+      </c>
       <c r="R266" t="str">
         <v/>
       </c>
@@ -13859,6 +15339,18 @@
       <c r="M267" t="str">
         <v/>
       </c>
+      <c r="N267" t="str">
+        <v/>
+      </c>
+      <c r="O267" t="str">
+        <v/>
+      </c>
+      <c r="P267" t="str">
+        <v/>
+      </c>
+      <c r="Q267" t="str">
+        <v/>
+      </c>
       <c r="R267" t="str">
         <v/>
       </c>
@@ -13903,6 +15395,18 @@
       <c r="M268" t="str">
         <v/>
       </c>
+      <c r="N268" t="str">
+        <v/>
+      </c>
+      <c r="O268" t="str">
+        <v/>
+      </c>
+      <c r="P268" t="str">
+        <v/>
+      </c>
+      <c r="Q268" t="str">
+        <v/>
+      </c>
       <c r="R268" t="str">
         <v/>
       </c>
@@ -13947,6 +15451,18 @@
       <c r="M269" t="str">
         <v/>
       </c>
+      <c r="N269" t="str">
+        <v/>
+      </c>
+      <c r="O269" t="str">
+        <v/>
+      </c>
+      <c r="P269" t="str">
+        <v/>
+      </c>
+      <c r="Q269" t="str">
+        <v/>
+      </c>
       <c r="R269" t="str">
         <v/>
       </c>
@@ -13991,6 +15507,18 @@
       <c r="M270" t="str">
         <v/>
       </c>
+      <c r="N270" t="str">
+        <v/>
+      </c>
+      <c r="O270" t="str">
+        <v/>
+      </c>
+      <c r="P270" t="str">
+        <v/>
+      </c>
+      <c r="Q270" t="str">
+        <v/>
+      </c>
       <c r="R270" t="str">
         <v/>
       </c>
@@ -14035,6 +15563,18 @@
       <c r="M271" t="str">
         <v/>
       </c>
+      <c r="N271" t="str">
+        <v/>
+      </c>
+      <c r="O271" t="str">
+        <v/>
+      </c>
+      <c r="P271" t="str">
+        <v/>
+      </c>
+      <c r="Q271" t="str">
+        <v/>
+      </c>
       <c r="R271" t="str">
         <v/>
       </c>
@@ -14079,6 +15619,18 @@
       <c r="M272" t="str">
         <v/>
       </c>
+      <c r="N272" t="str">
+        <v/>
+      </c>
+      <c r="O272" t="str">
+        <v/>
+      </c>
+      <c r="P272" t="str">
+        <v/>
+      </c>
+      <c r="Q272" t="str">
+        <v/>
+      </c>
       <c r="R272" t="str">
         <v/>
       </c>
@@ -14123,6 +15675,18 @@
       <c r="M273" t="str">
         <v/>
       </c>
+      <c r="N273" t="str">
+        <v/>
+      </c>
+      <c r="O273" t="str">
+        <v/>
+      </c>
+      <c r="P273" t="str">
+        <v/>
+      </c>
+      <c r="Q273" t="str">
+        <v/>
+      </c>
       <c r="R273" t="str">
         <v/>
       </c>
@@ -14167,6 +15731,18 @@
       <c r="M274" t="str">
         <v/>
       </c>
+      <c r="N274" t="str">
+        <v/>
+      </c>
+      <c r="O274" t="str">
+        <v/>
+      </c>
+      <c r="P274" t="str">
+        <v/>
+      </c>
+      <c r="Q274" t="str">
+        <v/>
+      </c>
       <c r="R274" t="str">
         <v/>
       </c>
@@ -14211,6 +15787,18 @@
       <c r="M275" t="str">
         <v/>
       </c>
+      <c r="N275" t="str">
+        <v/>
+      </c>
+      <c r="O275" t="str">
+        <v/>
+      </c>
+      <c r="P275" t="str">
+        <v/>
+      </c>
+      <c r="Q275" t="str">
+        <v/>
+      </c>
       <c r="R275" t="str">
         <v/>
       </c>
@@ -14255,6 +15843,18 @@
       <c r="M276" t="str">
         <v/>
       </c>
+      <c r="N276" t="str">
+        <v/>
+      </c>
+      <c r="O276" t="str">
+        <v/>
+      </c>
+      <c r="P276" t="str">
+        <v/>
+      </c>
+      <c r="Q276" t="str">
+        <v/>
+      </c>
       <c r="R276" t="str">
         <v/>
       </c>
@@ -14299,6 +15899,18 @@
       <c r="M277" t="str">
         <v/>
       </c>
+      <c r="N277" t="str">
+        <v/>
+      </c>
+      <c r="O277" t="str">
+        <v/>
+      </c>
+      <c r="P277" t="str">
+        <v/>
+      </c>
+      <c r="Q277" t="str">
+        <v/>
+      </c>
       <c r="R277" t="str">
         <v/>
       </c>
@@ -14343,6 +15955,18 @@
       <c r="M278" t="str">
         <v/>
       </c>
+      <c r="N278" t="str">
+        <v/>
+      </c>
+      <c r="O278" t="str">
+        <v/>
+      </c>
+      <c r="P278" t="str">
+        <v/>
+      </c>
+      <c r="Q278" t="str">
+        <v/>
+      </c>
       <c r="R278" t="str">
         <v/>
       </c>
@@ -14387,6 +16011,18 @@
       <c r="M279" t="str">
         <v/>
       </c>
+      <c r="N279" t="str">
+        <v/>
+      </c>
+      <c r="O279" t="str">
+        <v/>
+      </c>
+      <c r="P279" t="str">
+        <v/>
+      </c>
+      <c r="Q279" t="str">
+        <v/>
+      </c>
       <c r="R279" t="str">
         <v/>
       </c>
@@ -14431,6 +16067,18 @@
       <c r="M280" t="str">
         <v/>
       </c>
+      <c r="N280" t="str">
+        <v/>
+      </c>
+      <c r="O280" t="str">
+        <v/>
+      </c>
+      <c r="P280" t="str">
+        <v/>
+      </c>
+      <c r="Q280" t="str">
+        <v/>
+      </c>
       <c r="R280" t="str">
         <v/>
       </c>
@@ -14475,6 +16123,18 @@
       <c r="M281" t="str">
         <v/>
       </c>
+      <c r="N281" t="str">
+        <v/>
+      </c>
+      <c r="O281" t="str">
+        <v/>
+      </c>
+      <c r="P281" t="str">
+        <v/>
+      </c>
+      <c r="Q281" t="str">
+        <v/>
+      </c>
       <c r="R281" t="str">
         <v/>
       </c>
@@ -14519,6 +16179,18 @@
       <c r="M282" t="str">
         <v/>
       </c>
+      <c r="N282" t="str">
+        <v/>
+      </c>
+      <c r="O282" t="str">
+        <v/>
+      </c>
+      <c r="P282" t="str">
+        <v/>
+      </c>
+      <c r="Q282" t="str">
+        <v/>
+      </c>
       <c r="R282" t="str">
         <v/>
       </c>
@@ -14563,6 +16235,18 @@
       <c r="M283" t="str">
         <v/>
       </c>
+      <c r="N283" t="str">
+        <v/>
+      </c>
+      <c r="O283" t="str">
+        <v/>
+      </c>
+      <c r="P283" t="str">
+        <v/>
+      </c>
+      <c r="Q283" t="str">
+        <v/>
+      </c>
       <c r="R283" t="str">
         <v/>
       </c>
@@ -14607,6 +16291,18 @@
       <c r="M284" t="str">
         <v/>
       </c>
+      <c r="N284" t="str">
+        <v/>
+      </c>
+      <c r="O284" t="str">
+        <v/>
+      </c>
+      <c r="P284" t="str">
+        <v/>
+      </c>
+      <c r="Q284" t="str">
+        <v/>
+      </c>
       <c r="R284" t="str">
         <v/>
       </c>
@@ -14649,6 +16345,18 @@
         <v>4550133657009</v>
       </c>
       <c r="M285" t="str">
+        <v/>
+      </c>
+      <c r="N285" t="str">
+        <v/>
+      </c>
+      <c r="O285" t="str">
+        <v/>
+      </c>
+      <c r="P285" t="str">
+        <v/>
+      </c>
+      <c r="Q285" t="str">
         <v/>
       </c>
       <c r="R285" t="str">

--- a/GearSage-client/rate/excel/soft_lure_detail.xlsx
+++ b/GearSage-client/rate/excel/soft_lure_detail.xlsx
@@ -32,11 +32,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
   </numFmts>
   <fonts count="1">

--- a/GearSage-client/rate/excel/soft_lure_detail.xlsx
+++ b/GearSage-client/rate/excel/soft_lure_detail.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R285"/>
+  <dimension ref="A1:R305"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -16359,9 +16359,1129 @@
         <v/>
       </c>
     </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>KLD10000</v>
+      </c>
+      <c r="B286" t="str">
+        <v>KL1000</v>
+      </c>
+      <c r="C286" t="str">
+        <v>スイングベイト2.8"</v>
+      </c>
+      <c r="D286" t="str">
+        <v/>
+      </c>
+      <c r="E286" t="str">
+        <v/>
+      </c>
+      <c r="F286" t="str">
+        <v/>
+      </c>
+      <c r="G286" t="str">
+        <v/>
+      </c>
+      <c r="H286" t="str">
+        <v/>
+      </c>
+      <c r="I286" t="str">
+        <v>2026-04-10T05:00:09.333Z</v>
+      </c>
+      <c r="J286" t="str">
+        <v>2026-04-10T05:00:09.333Z</v>
+      </c>
+      <c r="K286" t="str">
+        <v/>
+      </c>
+      <c r="L286" t="str">
+        <v/>
+      </c>
+      <c r="M286" t="str">
+        <v/>
+      </c>
+      <c r="N286" t="str">
+        <v/>
+      </c>
+      <c r="O286" t="str">
+        <v/>
+      </c>
+      <c r="P286" t="str">
+        <v/>
+      </c>
+      <c r="Q286" t="str">
+        <v/>
+      </c>
+      <c r="R286" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>KLD10001</v>
+      </c>
+      <c r="B287" t="str">
+        <v>KL1001</v>
+      </c>
+      <c r="C287" t="str">
+        <v>スイングインパクト</v>
+      </c>
+      <c r="D287" t="str">
+        <v/>
+      </c>
+      <c r="E287" t="str">
+        <v/>
+      </c>
+      <c r="F287" t="str">
+        <v/>
+      </c>
+      <c r="G287" t="str">
+        <v/>
+      </c>
+      <c r="H287" t="str">
+        <v/>
+      </c>
+      <c r="I287" t="str">
+        <v>2026-04-10T05:00:16.169Z</v>
+      </c>
+      <c r="J287" t="str">
+        <v>2026-04-10T05:00:16.169Z</v>
+      </c>
+      <c r="K287" t="str">
+        <v/>
+      </c>
+      <c r="L287" t="str">
+        <v/>
+      </c>
+      <c r="M287" t="str">
+        <v/>
+      </c>
+      <c r="N287" t="str">
+        <v/>
+      </c>
+      <c r="O287" t="str">
+        <v/>
+      </c>
+      <c r="P287" t="str">
+        <v/>
+      </c>
+      <c r="Q287" t="str">
+        <v/>
+      </c>
+      <c r="R287" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>KLD10002</v>
+      </c>
+      <c r="B288" t="str">
+        <v>KL1002</v>
+      </c>
+      <c r="C288" t="str">
+        <v>スイングインパクトファット</v>
+      </c>
+      <c r="D288" t="str">
+        <v/>
+      </c>
+      <c r="E288" t="str">
+        <v/>
+      </c>
+      <c r="F288" t="str">
+        <v/>
+      </c>
+      <c r="G288" t="str">
+        <v/>
+      </c>
+      <c r="H288" t="str">
+        <v/>
+      </c>
+      <c r="I288" t="str">
+        <v>2026-04-10T05:00:26.223Z</v>
+      </c>
+      <c r="J288" t="str">
+        <v>2026-04-10T05:00:26.223Z</v>
+      </c>
+      <c r="K288" t="str">
+        <v/>
+      </c>
+      <c r="L288" t="str">
+        <v/>
+      </c>
+      <c r="M288" t="str">
+        <v/>
+      </c>
+      <c r="N288" t="str">
+        <v/>
+      </c>
+      <c r="O288" t="str">
+        <v/>
+      </c>
+      <c r="P288" t="str">
+        <v/>
+      </c>
+      <c r="Q288" t="str">
+        <v/>
+      </c>
+      <c r="R288" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>KLD10003</v>
+      </c>
+      <c r="B289" t="str">
+        <v>KL1003</v>
+      </c>
+      <c r="C289" t="str">
+        <v>イージーシャイナー</v>
+      </c>
+      <c r="D289" t="str">
+        <v/>
+      </c>
+      <c r="E289" t="str">
+        <v/>
+      </c>
+      <c r="F289" t="str">
+        <v/>
+      </c>
+      <c r="G289" t="str">
+        <v/>
+      </c>
+      <c r="H289" t="str">
+        <v/>
+      </c>
+      <c r="I289" t="str">
+        <v>2026-04-10T05:00:31.150Z</v>
+      </c>
+      <c r="J289" t="str">
+        <v>2026-04-10T05:00:31.150Z</v>
+      </c>
+      <c r="K289" t="str">
+        <v/>
+      </c>
+      <c r="L289" t="str">
+        <v/>
+      </c>
+      <c r="M289" t="str">
+        <v/>
+      </c>
+      <c r="N289" t="str">
+        <v/>
+      </c>
+      <c r="O289" t="str">
+        <v/>
+      </c>
+      <c r="P289" t="str">
+        <v/>
+      </c>
+      <c r="Q289" t="str">
+        <v/>
+      </c>
+      <c r="R289" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>KLD10004</v>
+      </c>
+      <c r="B290" t="str">
+        <v>KL1004</v>
+      </c>
+      <c r="C290" t="str">
+        <v>グライドカマロン3.5"</v>
+      </c>
+      <c r="D290" t="str">
+        <v/>
+      </c>
+      <c r="E290" t="str">
+        <v/>
+      </c>
+      <c r="F290" t="str">
+        <v/>
+      </c>
+      <c r="G290" t="str">
+        <v/>
+      </c>
+      <c r="H290" t="str">
+        <v/>
+      </c>
+      <c r="I290" t="str">
+        <v>2026-04-10T05:00:32.478Z</v>
+      </c>
+      <c r="J290" t="str">
+        <v>2026-04-10T05:00:32.478Z</v>
+      </c>
+      <c r="K290" t="str">
+        <v/>
+      </c>
+      <c r="L290" t="str">
+        <v/>
+      </c>
+      <c r="M290" t="str">
+        <v/>
+      </c>
+      <c r="N290" t="str">
+        <v/>
+      </c>
+      <c r="O290" t="str">
+        <v/>
+      </c>
+      <c r="P290" t="str">
+        <v/>
+      </c>
+      <c r="Q290" t="str">
+        <v/>
+      </c>
+      <c r="R290" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>KLD10005</v>
+      </c>
+      <c r="B291" t="str">
+        <v>KL1005</v>
+      </c>
+      <c r="C291" t="str">
+        <v>フラッパーグラブ4"</v>
+      </c>
+      <c r="D291" t="str">
+        <v/>
+      </c>
+      <c r="E291" t="str">
+        <v/>
+      </c>
+      <c r="F291" t="str">
+        <v/>
+      </c>
+      <c r="G291" t="str">
+        <v/>
+      </c>
+      <c r="H291" t="str">
+        <v/>
+      </c>
+      <c r="I291" t="str">
+        <v>2026-04-10T05:00:33.726Z</v>
+      </c>
+      <c r="J291" t="str">
+        <v>2026-04-10T05:00:33.726Z</v>
+      </c>
+      <c r="K291" t="str">
+        <v/>
+      </c>
+      <c r="L291" t="str">
+        <v/>
+      </c>
+      <c r="M291" t="str">
+        <v/>
+      </c>
+      <c r="N291" t="str">
+        <v/>
+      </c>
+      <c r="O291" t="str">
+        <v/>
+      </c>
+      <c r="P291" t="str">
+        <v/>
+      </c>
+      <c r="Q291" t="str">
+        <v/>
+      </c>
+      <c r="R291" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>KLD10006</v>
+      </c>
+      <c r="B292" t="str">
+        <v>KL1006</v>
+      </c>
+      <c r="C292" t="str">
+        <v>ハイパースパイダー</v>
+      </c>
+      <c r="D292" t="str">
+        <v/>
+      </c>
+      <c r="E292" t="str">
+        <v/>
+      </c>
+      <c r="F292" t="str">
+        <v/>
+      </c>
+      <c r="G292" t="str">
+        <v/>
+      </c>
+      <c r="H292" t="str">
+        <v/>
+      </c>
+      <c r="I292" t="str">
+        <v>2026-04-10T05:00:35.359Z</v>
+      </c>
+      <c r="J292" t="str">
+        <v>2026-04-10T05:00:35.359Z</v>
+      </c>
+      <c r="K292" t="str">
+        <v/>
+      </c>
+      <c r="L292" t="str">
+        <v/>
+      </c>
+      <c r="M292" t="str">
+        <v/>
+      </c>
+      <c r="N292" t="str">
+        <v/>
+      </c>
+      <c r="O292" t="str">
+        <v/>
+      </c>
+      <c r="P292" t="str">
+        <v/>
+      </c>
+      <c r="Q292" t="str">
+        <v/>
+      </c>
+      <c r="R292" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>KLD10007</v>
+      </c>
+      <c r="B293" t="str">
+        <v>KL1007</v>
+      </c>
+      <c r="C293" t="str">
+        <v>パドリンビーバー</v>
+      </c>
+      <c r="D293" t="str">
+        <v/>
+      </c>
+      <c r="E293" t="str">
+        <v/>
+      </c>
+      <c r="F293" t="str">
+        <v/>
+      </c>
+      <c r="G293" t="str">
+        <v/>
+      </c>
+      <c r="H293" t="str">
+        <v/>
+      </c>
+      <c r="I293" t="str">
+        <v>2026-04-10T05:00:37.011Z</v>
+      </c>
+      <c r="J293" t="str">
+        <v>2026-04-10T05:00:37.011Z</v>
+      </c>
+      <c r="K293" t="str">
+        <v/>
+      </c>
+      <c r="L293" t="str">
+        <v/>
+      </c>
+      <c r="M293" t="str">
+        <v/>
+      </c>
+      <c r="N293" t="str">
+        <v/>
+      </c>
+      <c r="O293" t="str">
+        <v/>
+      </c>
+      <c r="P293" t="str">
+        <v/>
+      </c>
+      <c r="Q293" t="str">
+        <v/>
+      </c>
+      <c r="R293" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>KLD10008</v>
+      </c>
+      <c r="B294" t="str">
+        <v>KL1008</v>
+      </c>
+      <c r="C294" t="str">
+        <v>ネコカマロン</v>
+      </c>
+      <c r="D294" t="str">
+        <v/>
+      </c>
+      <c r="E294" t="str">
+        <v/>
+      </c>
+      <c r="F294" t="str">
+        <v/>
+      </c>
+      <c r="G294" t="str">
+        <v/>
+      </c>
+      <c r="H294" t="str">
+        <v/>
+      </c>
+      <c r="I294" t="str">
+        <v>2026-04-10T05:00:38.559Z</v>
+      </c>
+      <c r="J294" t="str">
+        <v>2026-04-10T05:00:38.559Z</v>
+      </c>
+      <c r="K294" t="str">
+        <v/>
+      </c>
+      <c r="L294" t="str">
+        <v/>
+      </c>
+      <c r="M294" t="str">
+        <v/>
+      </c>
+      <c r="N294" t="str">
+        <v/>
+      </c>
+      <c r="O294" t="str">
+        <v/>
+      </c>
+      <c r="P294" t="str">
+        <v/>
+      </c>
+      <c r="Q294" t="str">
+        <v/>
+      </c>
+      <c r="R294" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>KLD10009</v>
+      </c>
+      <c r="B295" t="str">
+        <v>KL1009</v>
+      </c>
+      <c r="C295" t="str">
+        <v>フレックスチャンク</v>
+      </c>
+      <c r="D295" t="str">
+        <v/>
+      </c>
+      <c r="E295" t="str">
+        <v/>
+      </c>
+      <c r="F295" t="str">
+        <v/>
+      </c>
+      <c r="G295" t="str">
+        <v/>
+      </c>
+      <c r="H295" t="str">
+        <v/>
+      </c>
+      <c r="I295" t="str">
+        <v>2026-04-10T05:00:40.270Z</v>
+      </c>
+      <c r="J295" t="str">
+        <v>2026-04-10T05:00:40.270Z</v>
+      </c>
+      <c r="K295" t="str">
+        <v/>
+      </c>
+      <c r="L295" t="str">
+        <v/>
+      </c>
+      <c r="M295" t="str">
+        <v/>
+      </c>
+      <c r="N295" t="str">
+        <v/>
+      </c>
+      <c r="O295" t="str">
+        <v/>
+      </c>
+      <c r="P295" t="str">
+        <v/>
+      </c>
+      <c r="Q295" t="str">
+        <v/>
+      </c>
+      <c r="R295" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>KLD10010</v>
+      </c>
+      <c r="B296" t="str">
+        <v>KL1010</v>
+      </c>
+      <c r="C296" t="str">
+        <v>Easy Shaker</v>
+      </c>
+      <c r="D296" t="str">
+        <v/>
+      </c>
+      <c r="E296" t="str">
+        <v/>
+      </c>
+      <c r="F296" t="str">
+        <v/>
+      </c>
+      <c r="G296" t="str">
+        <v/>
+      </c>
+      <c r="H296" t="str">
+        <v/>
+      </c>
+      <c r="I296" t="str">
+        <v>2026-04-10T05:00:42.551Z</v>
+      </c>
+      <c r="J296" t="str">
+        <v>2026-04-10T05:00:42.551Z</v>
+      </c>
+      <c r="K296" t="str">
+        <v/>
+      </c>
+      <c r="L296" t="str">
+        <v/>
+      </c>
+      <c r="M296" t="str">
+        <v/>
+      </c>
+      <c r="N296" t="str">
+        <v/>
+      </c>
+      <c r="O296" t="str">
+        <v/>
+      </c>
+      <c r="P296" t="str">
+        <v/>
+      </c>
+      <c r="Q296" t="str">
+        <v/>
+      </c>
+      <c r="R296" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>KLD10011</v>
+      </c>
+      <c r="B297" t="str">
+        <v>KL1011</v>
+      </c>
+      <c r="C297" t="str">
+        <v>カスタムリーチ</v>
+      </c>
+      <c r="D297" t="str">
+        <v/>
+      </c>
+      <c r="E297" t="str">
+        <v/>
+      </c>
+      <c r="F297" t="str">
+        <v/>
+      </c>
+      <c r="G297" t="str">
+        <v/>
+      </c>
+      <c r="H297" t="str">
+        <v/>
+      </c>
+      <c r="I297" t="str">
+        <v>2026-04-10T05:00:45.695Z</v>
+      </c>
+      <c r="J297" t="str">
+        <v>2026-04-10T05:00:45.695Z</v>
+      </c>
+      <c r="K297" t="str">
+        <v/>
+      </c>
+      <c r="L297" t="str">
+        <v/>
+      </c>
+      <c r="M297" t="str">
+        <v/>
+      </c>
+      <c r="N297" t="str">
+        <v/>
+      </c>
+      <c r="O297" t="str">
+        <v/>
+      </c>
+      <c r="P297" t="str">
+        <v/>
+      </c>
+      <c r="Q297" t="str">
+        <v/>
+      </c>
+      <c r="R297" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>KLD10012</v>
+      </c>
+      <c r="B298" t="str">
+        <v>KL1012</v>
+      </c>
+      <c r="C298" t="str">
+        <v>ノイジーフラッパー</v>
+      </c>
+      <c r="D298" t="str">
+        <v/>
+      </c>
+      <c r="E298" t="str">
+        <v/>
+      </c>
+      <c r="F298" t="str">
+        <v/>
+      </c>
+      <c r="G298" t="str">
+        <v/>
+      </c>
+      <c r="H298" t="str">
+        <v/>
+      </c>
+      <c r="I298" t="str">
+        <v>2026-04-10T05:00:49.253Z</v>
+      </c>
+      <c r="J298" t="str">
+        <v>2026-04-10T05:00:49.253Z</v>
+      </c>
+      <c r="K298" t="str">
+        <v/>
+      </c>
+      <c r="L298" t="str">
+        <v/>
+      </c>
+      <c r="M298" t="str">
+        <v/>
+      </c>
+      <c r="N298" t="str">
+        <v/>
+      </c>
+      <c r="O298" t="str">
+        <v/>
+      </c>
+      <c r="P298" t="str">
+        <v/>
+      </c>
+      <c r="Q298" t="str">
+        <v/>
+      </c>
+      <c r="R298" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>KLD10013</v>
+      </c>
+      <c r="B299" t="str">
+        <v>KL1013</v>
+      </c>
+      <c r="C299" t="str">
+        <v>クレイジーフラッパー</v>
+      </c>
+      <c r="D299" t="str">
+        <v/>
+      </c>
+      <c r="E299" t="str">
+        <v/>
+      </c>
+      <c r="F299" t="str">
+        <v/>
+      </c>
+      <c r="G299" t="str">
+        <v/>
+      </c>
+      <c r="H299" t="str">
+        <v/>
+      </c>
+      <c r="I299" t="str">
+        <v>2026-04-10T05:00:52.359Z</v>
+      </c>
+      <c r="J299" t="str">
+        <v>2026-04-10T05:00:52.359Z</v>
+      </c>
+      <c r="K299" t="str">
+        <v/>
+      </c>
+      <c r="L299" t="str">
+        <v/>
+      </c>
+      <c r="M299" t="str">
+        <v/>
+      </c>
+      <c r="N299" t="str">
+        <v/>
+      </c>
+      <c r="O299" t="str">
+        <v/>
+      </c>
+      <c r="P299" t="str">
+        <v/>
+      </c>
+      <c r="Q299" t="str">
+        <v/>
+      </c>
+      <c r="R299" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>KLD10014</v>
+      </c>
+      <c r="B300" t="str">
+        <v>KL1014</v>
+      </c>
+      <c r="C300" t="str">
+        <v>セクシーインパクト</v>
+      </c>
+      <c r="D300" t="str">
+        <v/>
+      </c>
+      <c r="E300" t="str">
+        <v/>
+      </c>
+      <c r="F300" t="str">
+        <v/>
+      </c>
+      <c r="G300" t="str">
+        <v/>
+      </c>
+      <c r="H300" t="str">
+        <v/>
+      </c>
+      <c r="I300" t="str">
+        <v>2026-04-10T05:01:05.353Z</v>
+      </c>
+      <c r="J300" t="str">
+        <v>2026-04-10T05:01:05.353Z</v>
+      </c>
+      <c r="K300" t="str">
+        <v/>
+      </c>
+      <c r="L300" t="str">
+        <v/>
+      </c>
+      <c r="M300" t="str">
+        <v/>
+      </c>
+      <c r="N300" t="str">
+        <v/>
+      </c>
+      <c r="O300" t="str">
+        <v/>
+      </c>
+      <c r="P300" t="str">
+        <v/>
+      </c>
+      <c r="Q300" t="str">
+        <v/>
+      </c>
+      <c r="R300" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>KLD10015</v>
+      </c>
+      <c r="B301" t="str">
+        <v>KL1015</v>
+      </c>
+      <c r="C301" t="str">
+        <v>リトルスパイダー</v>
+      </c>
+      <c r="D301" t="str">
+        <v/>
+      </c>
+      <c r="E301" t="str">
+        <v/>
+      </c>
+      <c r="F301" t="str">
+        <v/>
+      </c>
+      <c r="G301" t="str">
+        <v/>
+      </c>
+      <c r="H301" t="str">
+        <v/>
+      </c>
+      <c r="I301" t="str">
+        <v>2026-04-10T05:01:10.963Z</v>
+      </c>
+      <c r="J301" t="str">
+        <v>2026-04-10T05:01:10.963Z</v>
+      </c>
+      <c r="K301" t="str">
+        <v/>
+      </c>
+      <c r="L301" t="str">
+        <v/>
+      </c>
+      <c r="M301" t="str">
+        <v/>
+      </c>
+      <c r="N301" t="str">
+        <v/>
+      </c>
+      <c r="O301" t="str">
+        <v/>
+      </c>
+      <c r="P301" t="str">
+        <v/>
+      </c>
+      <c r="Q301" t="str">
+        <v/>
+      </c>
+      <c r="R301" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>KLD10016</v>
+      </c>
+      <c r="B302" t="str">
+        <v>KL1016</v>
+      </c>
+      <c r="C302" t="str">
+        <v>シャッドインパクト</v>
+      </c>
+      <c r="D302" t="str">
+        <v/>
+      </c>
+      <c r="E302" t="str">
+        <v/>
+      </c>
+      <c r="F302" t="str">
+        <v/>
+      </c>
+      <c r="G302" t="str">
+        <v/>
+      </c>
+      <c r="H302" t="str">
+        <v/>
+      </c>
+      <c r="I302" t="str">
+        <v>2026-04-10T05:01:20.888Z</v>
+      </c>
+      <c r="J302" t="str">
+        <v>2026-04-10T05:01:20.888Z</v>
+      </c>
+      <c r="K302" t="str">
+        <v/>
+      </c>
+      <c r="L302" t="str">
+        <v/>
+      </c>
+      <c r="M302" t="str">
+        <v/>
+      </c>
+      <c r="N302" t="str">
+        <v/>
+      </c>
+      <c r="O302" t="str">
+        <v/>
+      </c>
+      <c r="P302" t="str">
+        <v/>
+      </c>
+      <c r="Q302" t="str">
+        <v/>
+      </c>
+      <c r="R302" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>KLD10017</v>
+      </c>
+      <c r="B303" t="str">
+        <v>KL1017</v>
+      </c>
+      <c r="C303" t="str">
+        <v>ソルティ・コアチューブ</v>
+      </c>
+      <c r="D303" t="str">
+        <v/>
+      </c>
+      <c r="E303" t="str">
+        <v/>
+      </c>
+      <c r="F303" t="str">
+        <v/>
+      </c>
+      <c r="G303" t="str">
+        <v/>
+      </c>
+      <c r="H303" t="str">
+        <v/>
+      </c>
+      <c r="I303" t="str">
+        <v>2026-04-10T05:01:24.581Z</v>
+      </c>
+      <c r="J303" t="str">
+        <v>2026-04-10T05:01:24.581Z</v>
+      </c>
+      <c r="K303" t="str">
+        <v/>
+      </c>
+      <c r="L303" t="str">
+        <v/>
+      </c>
+      <c r="M303" t="str">
+        <v/>
+      </c>
+      <c r="N303" t="str">
+        <v/>
+      </c>
+      <c r="O303" t="str">
+        <v/>
+      </c>
+      <c r="P303" t="str">
+        <v/>
+      </c>
+      <c r="Q303" t="str">
+        <v/>
+      </c>
+      <c r="R303" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>KLD10018</v>
+      </c>
+      <c r="B304" t="str">
+        <v>KL1018</v>
+      </c>
+      <c r="C304" t="str">
+        <v>マッドワグ</v>
+      </c>
+      <c r="D304" t="str">
+        <v/>
+      </c>
+      <c r="E304" t="str">
+        <v/>
+      </c>
+      <c r="F304" t="str">
+        <v/>
+      </c>
+      <c r="G304" t="str">
+        <v/>
+      </c>
+      <c r="H304" t="str">
+        <v/>
+      </c>
+      <c r="I304" t="str">
+        <v>2026-04-10T05:01:30.282Z</v>
+      </c>
+      <c r="J304" t="str">
+        <v>2026-04-10T05:01:30.282Z</v>
+      </c>
+      <c r="K304" t="str">
+        <v/>
+      </c>
+      <c r="L304" t="str">
+        <v/>
+      </c>
+      <c r="M304" t="str">
+        <v/>
+      </c>
+      <c r="N304" t="str">
+        <v/>
+      </c>
+      <c r="O304" t="str">
+        <v/>
+      </c>
+      <c r="P304" t="str">
+        <v/>
+      </c>
+      <c r="Q304" t="str">
+        <v/>
+      </c>
+      <c r="R304" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>KLD10019</v>
+      </c>
+      <c r="B305" t="str">
+        <v>KL1019</v>
+      </c>
+      <c r="C305" t="str">
+        <v>ライブインパクト</v>
+      </c>
+      <c r="D305" t="str">
+        <v/>
+      </c>
+      <c r="E305" t="str">
+        <v/>
+      </c>
+      <c r="F305" t="str">
+        <v/>
+      </c>
+      <c r="G305" t="str">
+        <v/>
+      </c>
+      <c r="H305" t="str">
+        <v/>
+      </c>
+      <c r="I305" t="str">
+        <v>2026-04-10T05:01:35.219Z</v>
+      </c>
+      <c r="J305" t="str">
+        <v>2026-04-10T05:01:35.219Z</v>
+      </c>
+      <c r="K305" t="str">
+        <v/>
+      </c>
+      <c r="L305" t="str">
+        <v/>
+      </c>
+      <c r="M305" t="str">
+        <v/>
+      </c>
+      <c r="N305" t="str">
+        <v/>
+      </c>
+      <c r="O305" t="str">
+        <v/>
+      </c>
+      <c r="P305" t="str">
+        <v/>
+      </c>
+      <c r="Q305" t="str">
+        <v/>
+      </c>
+      <c r="R305" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R285"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R305"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/GearSage-client/rate/excel/soft_lure_detail.xlsx
+++ b/GearSage-client/rate/excel/soft_lure_detail.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R305"/>
+  <dimension ref="A1:R355"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -16367,16 +16367,16 @@
         <v>KL1000</v>
       </c>
       <c r="C286" t="str">
-        <v>スイングベイト2.8"</v>
+        <v>ジグヘッドリグ</v>
       </c>
       <c r="D286" t="str">
-        <v/>
+        <v>1/32oz</v>
       </c>
       <c r="E286" t="str">
         <v/>
       </c>
       <c r="F286" t="str">
-        <v/>
+        <v>ジグヘッドリグ</v>
       </c>
       <c r="G286" t="str">
         <v/>
@@ -16385,10 +16385,10 @@
         <v/>
       </c>
       <c r="I286" t="str">
-        <v>2026-04-10T05:00:09.333Z</v>
+        <v>2026-04-10T05:39:11.615Z</v>
       </c>
       <c r="J286" t="str">
-        <v>2026-04-10T05:00:09.333Z</v>
+        <v>2026-04-10T05:39:11.615Z</v>
       </c>
       <c r="K286" t="str">
         <v/>
@@ -16423,28 +16423,28 @@
         <v>KL1001</v>
       </c>
       <c r="C287" t="str">
-        <v>スイングインパクト</v>
+        <v>2"</v>
       </c>
       <c r="D287" t="str">
-        <v/>
+        <v>0.9g</v>
       </c>
       <c r="E287" t="str">
         <v/>
       </c>
       <c r="F287" t="str">
-        <v/>
+        <v>2"</v>
       </c>
       <c r="G287" t="str">
         <v/>
       </c>
       <c r="H287" t="str">
-        <v/>
+        <v>620</v>
       </c>
       <c r="I287" t="str">
-        <v>2026-04-10T05:00:16.169Z</v>
+        <v>2026-04-10T05:39:18.540Z</v>
       </c>
       <c r="J287" t="str">
-        <v>2026-04-10T05:00:16.169Z</v>
+        <v>2026-04-10T05:39:18.540Z</v>
       </c>
       <c r="K287" t="str">
         <v/>
@@ -16468,7 +16468,7 @@
         <v/>
       </c>
       <c r="R287" t="str">
-        <v/>
+        <v>12</v>
       </c>
     </row>
     <row r="288">
@@ -16476,31 +16476,31 @@
         <v>KLD10002</v>
       </c>
       <c r="B288" t="str">
-        <v>KL1002</v>
+        <v>KL1001</v>
       </c>
       <c r="C288" t="str">
-        <v>スイングインパクトファット</v>
+        <v>2.5"</v>
       </c>
       <c r="D288" t="str">
-        <v/>
+        <v>1.3g</v>
       </c>
       <c r="E288" t="str">
         <v/>
       </c>
       <c r="F288" t="str">
-        <v/>
+        <v>2.5"</v>
       </c>
       <c r="G288" t="str">
         <v/>
       </c>
       <c r="H288" t="str">
-        <v/>
+        <v>620</v>
       </c>
       <c r="I288" t="str">
-        <v>2026-04-10T05:00:26.223Z</v>
+        <v>2026-04-10T05:39:18.540Z</v>
       </c>
       <c r="J288" t="str">
-        <v>2026-04-10T05:00:26.223Z</v>
+        <v>2026-04-10T05:39:18.540Z</v>
       </c>
       <c r="K288" t="str">
         <v/>
@@ -16524,7 +16524,7 @@
         <v/>
       </c>
       <c r="R288" t="str">
-        <v/>
+        <v>10</v>
       </c>
     </row>
     <row r="289">
@@ -16532,31 +16532,31 @@
         <v>KLD10003</v>
       </c>
       <c r="B289" t="str">
-        <v>KL1003</v>
+        <v>KL1001</v>
       </c>
       <c r="C289" t="str">
-        <v>イージーシャイナー</v>
+        <v>3"</v>
       </c>
       <c r="D289" t="str">
-        <v/>
+        <v>2.0g</v>
       </c>
       <c r="E289" t="str">
         <v/>
       </c>
       <c r="F289" t="str">
-        <v/>
+        <v>3"</v>
       </c>
       <c r="G289" t="str">
         <v/>
       </c>
       <c r="H289" t="str">
-        <v/>
+        <v>620</v>
       </c>
       <c r="I289" t="str">
-        <v>2026-04-10T05:00:31.150Z</v>
+        <v>2026-04-10T05:39:18.540Z</v>
       </c>
       <c r="J289" t="str">
-        <v>2026-04-10T05:00:31.150Z</v>
+        <v>2026-04-10T05:39:18.540Z</v>
       </c>
       <c r="K289" t="str">
         <v/>
@@ -16580,7 +16580,7 @@
         <v/>
       </c>
       <c r="R289" t="str">
-        <v/>
+        <v>10</v>
       </c>
     </row>
     <row r="290">
@@ -16588,31 +16588,31 @@
         <v>KLD10004</v>
       </c>
       <c r="B290" t="str">
-        <v>KL1004</v>
+        <v>KL1001</v>
       </c>
       <c r="C290" t="str">
-        <v>グライドカマロン3.5"</v>
+        <v>3.5"</v>
       </c>
       <c r="D290" t="str">
-        <v/>
+        <v>3.2g</v>
       </c>
       <c r="E290" t="str">
         <v/>
       </c>
       <c r="F290" t="str">
-        <v/>
+        <v>3.5"</v>
       </c>
       <c r="G290" t="str">
         <v/>
       </c>
       <c r="H290" t="str">
-        <v/>
+        <v>740</v>
       </c>
       <c r="I290" t="str">
-        <v>2026-04-10T05:00:32.478Z</v>
+        <v>2026-04-10T05:39:18.540Z</v>
       </c>
       <c r="J290" t="str">
-        <v>2026-04-10T05:00:32.478Z</v>
+        <v>2026-04-10T05:39:18.540Z</v>
       </c>
       <c r="K290" t="str">
         <v/>
@@ -16636,7 +16636,7 @@
         <v/>
       </c>
       <c r="R290" t="str">
-        <v/>
+        <v>8</v>
       </c>
     </row>
     <row r="291">
@@ -16644,31 +16644,31 @@
         <v>KLD10005</v>
       </c>
       <c r="B291" t="str">
-        <v>KL1005</v>
+        <v>KL1001</v>
       </c>
       <c r="C291" t="str">
-        <v>フラッパーグラブ4"</v>
+        <v>4"</v>
       </c>
       <c r="D291" t="str">
-        <v/>
+        <v>4.6g</v>
       </c>
       <c r="E291" t="str">
         <v/>
       </c>
       <c r="F291" t="str">
-        <v/>
+        <v>4"</v>
       </c>
       <c r="G291" t="str">
         <v/>
       </c>
       <c r="H291" t="str">
-        <v/>
+        <v>740</v>
       </c>
       <c r="I291" t="str">
-        <v>2026-04-10T05:00:33.726Z</v>
+        <v>2026-04-10T05:39:18.540Z</v>
       </c>
       <c r="J291" t="str">
-        <v>2026-04-10T05:00:33.726Z</v>
+        <v>2026-04-10T05:39:18.540Z</v>
       </c>
       <c r="K291" t="str">
         <v/>
@@ -16692,7 +16692,7 @@
         <v/>
       </c>
       <c r="R291" t="str">
-        <v/>
+        <v>8</v>
       </c>
     </row>
     <row r="292">
@@ -16700,31 +16700,31 @@
         <v>KLD10006</v>
       </c>
       <c r="B292" t="str">
-        <v>KL1006</v>
+        <v>KL1001</v>
       </c>
       <c r="C292" t="str">
-        <v>ハイパースパイダー</v>
+        <v>4.5"</v>
       </c>
       <c r="D292" t="str">
-        <v/>
+        <v>9.0g</v>
       </c>
       <c r="E292" t="str">
         <v/>
       </c>
       <c r="F292" t="str">
-        <v/>
+        <v>4.5"</v>
       </c>
       <c r="G292" t="str">
         <v/>
       </c>
       <c r="H292" t="str">
-        <v/>
+        <v>740</v>
       </c>
       <c r="I292" t="str">
-        <v>2026-04-10T05:00:35.359Z</v>
+        <v>2026-04-10T05:39:18.540Z</v>
       </c>
       <c r="J292" t="str">
-        <v>2026-04-10T05:00:35.359Z</v>
+        <v>2026-04-10T05:39:18.540Z</v>
       </c>
       <c r="K292" t="str">
         <v/>
@@ -16748,7 +16748,7 @@
         <v/>
       </c>
       <c r="R292" t="str">
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="293">
@@ -16756,31 +16756,31 @@
         <v>KLD10007</v>
       </c>
       <c r="B293" t="str">
-        <v>KL1007</v>
+        <v>KL1002</v>
       </c>
       <c r="C293" t="str">
-        <v>パドリンビーバー</v>
+        <v>2.8"</v>
       </c>
       <c r="D293" t="str">
-        <v/>
+        <v>3.5g</v>
       </c>
       <c r="E293" t="str">
         <v/>
       </c>
       <c r="F293" t="str">
-        <v/>
+        <v>2.8"</v>
       </c>
       <c r="G293" t="str">
         <v/>
       </c>
       <c r="H293" t="str">
-        <v/>
+        <v>740</v>
       </c>
       <c r="I293" t="str">
-        <v>2026-04-10T05:00:37.011Z</v>
+        <v>2026-04-10T05:39:27.448Z</v>
       </c>
       <c r="J293" t="str">
-        <v>2026-04-10T05:00:37.011Z</v>
+        <v>2026-04-10T05:39:27.448Z</v>
       </c>
       <c r="K293" t="str">
         <v/>
@@ -16804,7 +16804,7 @@
         <v/>
       </c>
       <c r="R293" t="str">
-        <v/>
+        <v>8</v>
       </c>
     </row>
     <row r="294">
@@ -16812,31 +16812,31 @@
         <v>KLD10008</v>
       </c>
       <c r="B294" t="str">
-        <v>KL1008</v>
+        <v>KL1002</v>
       </c>
       <c r="C294" t="str">
-        <v>ネコカマロン</v>
+        <v>3.3"</v>
       </c>
       <c r="D294" t="str">
-        <v/>
+        <v>5.6g</v>
       </c>
       <c r="E294" t="str">
         <v/>
       </c>
       <c r="F294" t="str">
-        <v/>
+        <v>3.3"</v>
       </c>
       <c r="G294" t="str">
         <v/>
       </c>
       <c r="H294" t="str">
-        <v/>
+        <v>740</v>
       </c>
       <c r="I294" t="str">
-        <v>2026-04-10T05:00:38.559Z</v>
+        <v>2026-04-10T05:39:27.448Z</v>
       </c>
       <c r="J294" t="str">
-        <v>2026-04-10T05:00:38.559Z</v>
+        <v>2026-04-10T05:39:27.448Z</v>
       </c>
       <c r="K294" t="str">
         <v/>
@@ -16860,7 +16860,7 @@
         <v/>
       </c>
       <c r="R294" t="str">
-        <v/>
+        <v>7</v>
       </c>
     </row>
     <row r="295">
@@ -16868,31 +16868,31 @@
         <v>KLD10009</v>
       </c>
       <c r="B295" t="str">
-        <v>KL1009</v>
+        <v>KL1002</v>
       </c>
       <c r="C295" t="str">
-        <v>フレックスチャンク</v>
+        <v>3.8"</v>
       </c>
       <c r="D295" t="str">
-        <v/>
+        <v>8.5g</v>
       </c>
       <c r="E295" t="str">
         <v/>
       </c>
       <c r="F295" t="str">
-        <v/>
+        <v>3.8"</v>
       </c>
       <c r="G295" t="str">
         <v/>
       </c>
       <c r="H295" t="str">
-        <v/>
+        <v>740</v>
       </c>
       <c r="I295" t="str">
-        <v>2026-04-10T05:00:40.270Z</v>
+        <v>2026-04-10T05:39:27.448Z</v>
       </c>
       <c r="J295" t="str">
-        <v>2026-04-10T05:00:40.270Z</v>
+        <v>2026-04-10T05:39:27.448Z</v>
       </c>
       <c r="K295" t="str">
         <v/>
@@ -16916,7 +16916,7 @@
         <v/>
       </c>
       <c r="R295" t="str">
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="296">
@@ -16924,31 +16924,31 @@
         <v>KLD10010</v>
       </c>
       <c r="B296" t="str">
-        <v>KL1010</v>
+        <v>KL1002</v>
       </c>
       <c r="C296" t="str">
-        <v>Easy Shaker</v>
+        <v>4.3"</v>
       </c>
       <c r="D296" t="str">
-        <v/>
+        <v>10.3g</v>
       </c>
       <c r="E296" t="str">
         <v/>
       </c>
       <c r="F296" t="str">
-        <v/>
+        <v>4.3"</v>
       </c>
       <c r="G296" t="str">
         <v/>
       </c>
       <c r="H296" t="str">
-        <v/>
+        <v>860</v>
       </c>
       <c r="I296" t="str">
-        <v>2026-04-10T05:00:42.551Z</v>
+        <v>2026-04-10T05:39:27.448Z</v>
       </c>
       <c r="J296" t="str">
-        <v>2026-04-10T05:00:42.551Z</v>
+        <v>2026-04-10T05:39:27.448Z</v>
       </c>
       <c r="K296" t="str">
         <v/>
@@ -16972,7 +16972,7 @@
         <v/>
       </c>
       <c r="R296" t="str">
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="297">
@@ -16980,31 +16980,31 @@
         <v>KLD10011</v>
       </c>
       <c r="B297" t="str">
-        <v>KL1011</v>
+        <v>KL1002</v>
       </c>
       <c r="C297" t="str">
-        <v>カスタムリーチ</v>
+        <v>4.8"</v>
       </c>
       <c r="D297" t="str">
-        <v/>
+        <v>12.8g</v>
       </c>
       <c r="E297" t="str">
         <v/>
       </c>
       <c r="F297" t="str">
-        <v/>
+        <v>4.8"</v>
       </c>
       <c r="G297" t="str">
         <v/>
       </c>
       <c r="H297" t="str">
-        <v/>
+        <v>860</v>
       </c>
       <c r="I297" t="str">
-        <v>2026-04-10T05:00:45.695Z</v>
+        <v>2026-04-10T05:39:27.448Z</v>
       </c>
       <c r="J297" t="str">
-        <v>2026-04-10T05:00:45.695Z</v>
+        <v>2026-04-10T05:39:27.448Z</v>
       </c>
       <c r="K297" t="str">
         <v/>
@@ -17028,7 +17028,7 @@
         <v/>
       </c>
       <c r="R297" t="str">
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="298">
@@ -17036,31 +17036,31 @@
         <v>KLD10012</v>
       </c>
       <c r="B298" t="str">
-        <v>KL1012</v>
+        <v>KL1002</v>
       </c>
       <c r="C298" t="str">
-        <v>ノイジーフラッパー</v>
+        <v>5.8"</v>
       </c>
       <c r="D298" t="str">
-        <v/>
+        <v>22.8g</v>
       </c>
       <c r="E298" t="str">
         <v/>
       </c>
       <c r="F298" t="str">
-        <v/>
+        <v>5.8"</v>
       </c>
       <c r="G298" t="str">
         <v/>
       </c>
       <c r="H298" t="str">
-        <v/>
+        <v>860</v>
       </c>
       <c r="I298" t="str">
-        <v>2026-04-10T05:00:49.253Z</v>
+        <v>2026-04-10T05:39:27.448Z</v>
       </c>
       <c r="J298" t="str">
-        <v>2026-04-10T05:00:49.253Z</v>
+        <v>2026-04-10T05:39:27.448Z</v>
       </c>
       <c r="K298" t="str">
         <v/>
@@ -17084,7 +17084,7 @@
         <v/>
       </c>
       <c r="R298" t="str">
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="299">
@@ -17092,31 +17092,31 @@
         <v>KLD10013</v>
       </c>
       <c r="B299" t="str">
-        <v>KL1013</v>
+        <v>KL1002</v>
       </c>
       <c r="C299" t="str">
-        <v>クレイジーフラッパー</v>
+        <v>6.8"</v>
       </c>
       <c r="D299" t="str">
-        <v/>
+        <v>36.5g</v>
       </c>
       <c r="E299" t="str">
         <v/>
       </c>
       <c r="F299" t="str">
-        <v/>
+        <v>6.8"</v>
       </c>
       <c r="G299" t="str">
         <v/>
       </c>
       <c r="H299" t="str">
-        <v/>
+        <v>1080</v>
       </c>
       <c r="I299" t="str">
-        <v>2026-04-10T05:00:52.359Z</v>
+        <v>2026-04-10T05:39:27.448Z</v>
       </c>
       <c r="J299" t="str">
-        <v>2026-04-10T05:00:52.359Z</v>
+        <v>2026-04-10T05:39:27.448Z</v>
       </c>
       <c r="K299" t="str">
         <v/>
@@ -17140,7 +17140,7 @@
         <v/>
       </c>
       <c r="R299" t="str">
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="300">
@@ -17148,31 +17148,31 @@
         <v>KLD10014</v>
       </c>
       <c r="B300" t="str">
-        <v>KL1014</v>
+        <v>KL1002</v>
       </c>
       <c r="C300" t="str">
-        <v>セクシーインパクト</v>
+        <v>7.8"</v>
       </c>
       <c r="D300" t="str">
-        <v/>
+        <v>54.2g</v>
       </c>
       <c r="E300" t="str">
         <v/>
       </c>
       <c r="F300" t="str">
-        <v/>
+        <v>7.8"</v>
       </c>
       <c r="G300" t="str">
         <v/>
       </c>
       <c r="H300" t="str">
-        <v/>
+        <v>1080</v>
       </c>
       <c r="I300" t="str">
-        <v>2026-04-10T05:01:05.353Z</v>
+        <v>2026-04-10T05:39:27.448Z</v>
       </c>
       <c r="J300" t="str">
-        <v>2026-04-10T05:01:05.353Z</v>
+        <v>2026-04-10T05:39:27.448Z</v>
       </c>
       <c r="K300" t="str">
         <v/>
@@ -17196,7 +17196,7 @@
         <v/>
       </c>
       <c r="R300" t="str">
-        <v/>
+        <v>2</v>
       </c>
     </row>
     <row r="301">
@@ -17204,31 +17204,31 @@
         <v>KLD10015</v>
       </c>
       <c r="B301" t="str">
-        <v>KL1015</v>
+        <v>KL1003</v>
       </c>
       <c r="C301" t="str">
-        <v>リトルスパイダー</v>
+        <v>2"</v>
       </c>
       <c r="D301" t="str">
-        <v/>
+        <v>1.0 g</v>
       </c>
       <c r="E301" t="str">
         <v/>
       </c>
       <c r="F301" t="str">
-        <v/>
+        <v>2"</v>
       </c>
       <c r="G301" t="str">
         <v/>
       </c>
       <c r="H301" t="str">
-        <v/>
+        <v>740</v>
       </c>
       <c r="I301" t="str">
-        <v>2026-04-10T05:01:10.963Z</v>
+        <v>2026-04-10T05:39:32.312Z</v>
       </c>
       <c r="J301" t="str">
-        <v>2026-04-10T05:01:10.963Z</v>
+        <v>2026-04-10T05:39:32.312Z</v>
       </c>
       <c r="K301" t="str">
         <v/>
@@ -17252,7 +17252,7 @@
         <v/>
       </c>
       <c r="R301" t="str">
-        <v/>
+        <v>12</v>
       </c>
     </row>
     <row r="302">
@@ -17260,31 +17260,31 @@
         <v>KLD10016</v>
       </c>
       <c r="B302" t="str">
-        <v>KL1016</v>
+        <v>KL1003</v>
       </c>
       <c r="C302" t="str">
-        <v>シャッドインパクト</v>
+        <v>3"</v>
       </c>
       <c r="D302" t="str">
-        <v/>
+        <v>2.2 g</v>
       </c>
       <c r="E302" t="str">
         <v/>
       </c>
       <c r="F302" t="str">
-        <v/>
+        <v>3"</v>
       </c>
       <c r="G302" t="str">
         <v/>
       </c>
       <c r="H302" t="str">
-        <v/>
+        <v>740</v>
       </c>
       <c r="I302" t="str">
-        <v>2026-04-10T05:01:20.888Z</v>
+        <v>2026-04-10T05:39:32.312Z</v>
       </c>
       <c r="J302" t="str">
-        <v>2026-04-10T05:01:20.888Z</v>
+        <v>2026-04-10T05:39:32.312Z</v>
       </c>
       <c r="K302" t="str">
         <v/>
@@ -17308,7 +17308,7 @@
         <v/>
       </c>
       <c r="R302" t="str">
-        <v/>
+        <v>10</v>
       </c>
     </row>
     <row r="303">
@@ -17316,31 +17316,31 @@
         <v>KLD10017</v>
       </c>
       <c r="B303" t="str">
-        <v>KL1017</v>
+        <v>KL1003</v>
       </c>
       <c r="C303" t="str">
-        <v>ソルティ・コアチューブ</v>
+        <v>3.5"</v>
       </c>
       <c r="D303" t="str">
-        <v/>
+        <v>3.9 g</v>
       </c>
       <c r="E303" t="str">
         <v/>
       </c>
       <c r="F303" t="str">
-        <v/>
+        <v>3.5"</v>
       </c>
       <c r="G303" t="str">
         <v/>
       </c>
       <c r="H303" t="str">
-        <v/>
+        <v>740</v>
       </c>
       <c r="I303" t="str">
-        <v>2026-04-10T05:01:24.581Z</v>
+        <v>2026-04-10T05:39:32.312Z</v>
       </c>
       <c r="J303" t="str">
-        <v>2026-04-10T05:01:24.581Z</v>
+        <v>2026-04-10T05:39:32.312Z</v>
       </c>
       <c r="K303" t="str">
         <v/>
@@ -17364,7 +17364,7 @@
         <v/>
       </c>
       <c r="R303" t="str">
-        <v/>
+        <v>7</v>
       </c>
     </row>
     <row r="304">
@@ -17372,31 +17372,31 @@
         <v>KLD10018</v>
       </c>
       <c r="B304" t="str">
-        <v>KL1018</v>
+        <v>KL1003</v>
       </c>
       <c r="C304" t="str">
-        <v>マッドワグ</v>
+        <v>4"</v>
       </c>
       <c r="D304" t="str">
-        <v/>
+        <v>5.5 g</v>
       </c>
       <c r="E304" t="str">
         <v/>
       </c>
       <c r="F304" t="str">
-        <v/>
+        <v>4"</v>
       </c>
       <c r="G304" t="str">
         <v/>
       </c>
       <c r="H304" t="str">
-        <v/>
+        <v>740</v>
       </c>
       <c r="I304" t="str">
-        <v>2026-04-10T05:01:30.282Z</v>
+        <v>2026-04-10T05:39:32.312Z</v>
       </c>
       <c r="J304" t="str">
-        <v>2026-04-10T05:01:30.282Z</v>
+        <v>2026-04-10T05:39:32.312Z</v>
       </c>
       <c r="K304" t="str">
         <v/>
@@ -17420,7 +17420,7 @@
         <v/>
       </c>
       <c r="R304" t="str">
-        <v/>
+        <v>7</v>
       </c>
     </row>
     <row r="305">
@@ -17428,60 +17428,2860 @@
         <v>KLD10019</v>
       </c>
       <c r="B305" t="str">
+        <v>KL1003</v>
+      </c>
+      <c r="C305" t="str">
+        <v>4.5"</v>
+      </c>
+      <c r="D305" t="str">
+        <v>7.4 g</v>
+      </c>
+      <c r="E305" t="str">
+        <v/>
+      </c>
+      <c r="F305" t="str">
+        <v>4.5"</v>
+      </c>
+      <c r="G305" t="str">
+        <v/>
+      </c>
+      <c r="H305" t="str">
+        <v>740</v>
+      </c>
+      <c r="I305" t="str">
+        <v>2026-04-10T05:39:32.312Z</v>
+      </c>
+      <c r="J305" t="str">
+        <v>2026-04-10T05:39:32.312Z</v>
+      </c>
+      <c r="K305" t="str">
+        <v/>
+      </c>
+      <c r="L305" t="str">
+        <v/>
+      </c>
+      <c r="M305" t="str">
+        <v/>
+      </c>
+      <c r="N305" t="str">
+        <v/>
+      </c>
+      <c r="O305" t="str">
+        <v/>
+      </c>
+      <c r="P305" t="str">
+        <v/>
+      </c>
+      <c r="Q305" t="str">
+        <v/>
+      </c>
+      <c r="R305" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="str">
+        <v>KLD10020</v>
+      </c>
+      <c r="B306" t="str">
+        <v>KL1003</v>
+      </c>
+      <c r="C306" t="str">
+        <v>5"</v>
+      </c>
+      <c r="D306" t="str">
+        <v>10.4 g</v>
+      </c>
+      <c r="E306" t="str">
+        <v/>
+      </c>
+      <c r="F306" t="str">
+        <v>5"</v>
+      </c>
+      <c r="G306" t="str">
+        <v/>
+      </c>
+      <c r="H306" t="str">
+        <v>840</v>
+      </c>
+      <c r="I306" t="str">
+        <v>2026-04-10T05:39:32.312Z</v>
+      </c>
+      <c r="J306" t="str">
+        <v>2026-04-10T05:39:32.312Z</v>
+      </c>
+      <c r="K306" t="str">
+        <v/>
+      </c>
+      <c r="L306" t="str">
+        <v/>
+      </c>
+      <c r="M306" t="str">
+        <v/>
+      </c>
+      <c r="N306" t="str">
+        <v/>
+      </c>
+      <c r="O306" t="str">
+        <v/>
+      </c>
+      <c r="P306" t="str">
+        <v/>
+      </c>
+      <c r="Q306" t="str">
+        <v/>
+      </c>
+      <c r="R306" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>KLD10021</v>
+      </c>
+      <c r="B307" t="str">
+        <v>KL1003</v>
+      </c>
+      <c r="C307" t="str">
+        <v>8"</v>
+      </c>
+      <c r="D307" t="str">
+        <v>43 g</v>
+      </c>
+      <c r="E307" t="str">
+        <v/>
+      </c>
+      <c r="F307" t="str">
+        <v>8"</v>
+      </c>
+      <c r="G307" t="str">
+        <v/>
+      </c>
+      <c r="H307" t="str">
+        <v>1080</v>
+      </c>
+      <c r="I307" t="str">
+        <v>2026-04-10T05:39:32.312Z</v>
+      </c>
+      <c r="J307" t="str">
+        <v>2026-04-10T05:39:32.312Z</v>
+      </c>
+      <c r="K307" t="str">
+        <v/>
+      </c>
+      <c r="L307" t="str">
+        <v/>
+      </c>
+      <c r="M307" t="str">
+        <v/>
+      </c>
+      <c r="N307" t="str">
+        <v/>
+      </c>
+      <c r="O307" t="str">
+        <v/>
+      </c>
+      <c r="P307" t="str">
+        <v/>
+      </c>
+      <c r="Q307" t="str">
+        <v/>
+      </c>
+      <c r="R307" t="str">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>KLD10022</v>
+      </c>
+      <c r="B308" t="str">
+        <v>KL1004</v>
+      </c>
+      <c r="C308" t="str">
+        <v>グライドカマロン3.5"</v>
+      </c>
+      <c r="D308" t="str">
+        <v/>
+      </c>
+      <c r="E308" t="str">
+        <v/>
+      </c>
+      <c r="F308" t="str">
+        <v/>
+      </c>
+      <c r="G308" t="str">
+        <v/>
+      </c>
+      <c r="H308" t="str">
+        <v/>
+      </c>
+      <c r="I308" t="str">
+        <v>2026-04-10T05:39:33.792Z</v>
+      </c>
+      <c r="J308" t="str">
+        <v>2026-04-10T05:39:33.792Z</v>
+      </c>
+      <c r="K308" t="str">
+        <v/>
+      </c>
+      <c r="L308" t="str">
+        <v/>
+      </c>
+      <c r="M308" t="str">
+        <v/>
+      </c>
+      <c r="N308" t="str">
+        <v/>
+      </c>
+      <c r="O308" t="str">
+        <v/>
+      </c>
+      <c r="P308" t="str">
+        <v/>
+      </c>
+      <c r="Q308" t="str">
+        <v/>
+      </c>
+      <c r="R308" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="str">
+        <v>KLD10023</v>
+      </c>
+      <c r="B309" t="str">
+        <v>KL1005</v>
+      </c>
+      <c r="C309" t="str">
+        <v>4"</v>
+      </c>
+      <c r="D309" t="str">
+        <v/>
+      </c>
+      <c r="E309" t="str">
+        <v/>
+      </c>
+      <c r="F309" t="str">
+        <v>4"</v>
+      </c>
+      <c r="G309" t="str">
+        <v/>
+      </c>
+      <c r="H309" t="str">
+        <v/>
+      </c>
+      <c r="I309" t="str">
+        <v>2026-04-10T05:39:35.679Z</v>
+      </c>
+      <c r="J309" t="str">
+        <v>2026-04-10T05:39:35.679Z</v>
+      </c>
+      <c r="K309" t="str">
+        <v/>
+      </c>
+      <c r="L309" t="str">
+        <v/>
+      </c>
+      <c r="M309" t="str">
+        <v/>
+      </c>
+      <c r="N309" t="str">
+        <v/>
+      </c>
+      <c r="O309" t="str">
+        <v/>
+      </c>
+      <c r="P309" t="str">
+        <v/>
+      </c>
+      <c r="Q309" t="str">
+        <v/>
+      </c>
+      <c r="R309" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="str">
+        <v>KLD10024</v>
+      </c>
+      <c r="B310" t="str">
+        <v>KL1006</v>
+      </c>
+      <c r="C310" t="str">
+        <v>3.2"</v>
+      </c>
+      <c r="D310" t="str">
+        <v>約5g</v>
+      </c>
+      <c r="E310" t="str">
+        <v/>
+      </c>
+      <c r="F310" t="str">
+        <v>3.2"</v>
+      </c>
+      <c r="G310" t="str">
+        <v/>
+      </c>
+      <c r="H310" t="str">
+        <v/>
+      </c>
+      <c r="I310" t="str">
+        <v>2026-04-10T05:39:37.181Z</v>
+      </c>
+      <c r="J310" t="str">
+        <v>2026-04-10T05:39:37.181Z</v>
+      </c>
+      <c r="K310" t="str">
+        <v/>
+      </c>
+      <c r="L310" t="str">
+        <v/>
+      </c>
+      <c r="M310" t="str">
+        <v/>
+      </c>
+      <c r="N310" t="str">
+        <v/>
+      </c>
+      <c r="O310" t="str">
+        <v/>
+      </c>
+      <c r="P310" t="str">
+        <v/>
+      </c>
+      <c r="Q310" t="str">
+        <v/>
+      </c>
+      <c r="R310" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="str">
+        <v>KLD10025</v>
+      </c>
+      <c r="B311" t="str">
+        <v>KL1007</v>
+      </c>
+      <c r="C311" t="str">
+        <v>3.5"</v>
+      </c>
+      <c r="D311" t="str">
+        <v/>
+      </c>
+      <c r="E311" t="str">
+        <v/>
+      </c>
+      <c r="F311" t="str">
+        <v>3.5"</v>
+      </c>
+      <c r="G311" t="str">
+        <v/>
+      </c>
+      <c r="H311" t="str">
+        <v/>
+      </c>
+      <c r="I311" t="str">
+        <v>2026-04-10T05:39:39.295Z</v>
+      </c>
+      <c r="J311" t="str">
+        <v>2026-04-10T05:39:39.295Z</v>
+      </c>
+      <c r="K311" t="str">
+        <v/>
+      </c>
+      <c r="L311" t="str">
+        <v/>
+      </c>
+      <c r="M311" t="str">
+        <v/>
+      </c>
+      <c r="N311" t="str">
+        <v/>
+      </c>
+      <c r="O311" t="str">
+        <v/>
+      </c>
+      <c r="P311" t="str">
+        <v/>
+      </c>
+      <c r="Q311" t="str">
+        <v/>
+      </c>
+      <c r="R311" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="str">
+        <v>KLD10026</v>
+      </c>
+      <c r="B312" t="str">
+        <v>KL1008</v>
+      </c>
+      <c r="C312" t="str">
+        <v>5.5"</v>
+      </c>
+      <c r="D312" t="str">
+        <v>約7.4g</v>
+      </c>
+      <c r="E312" t="str">
+        <v/>
+      </c>
+      <c r="F312" t="str">
+        <v>5.5"</v>
+      </c>
+      <c r="G312" t="str">
+        <v/>
+      </c>
+      <c r="H312" t="str">
+        <v/>
+      </c>
+      <c r="I312" t="str">
+        <v>2026-04-10T05:39:40.991Z</v>
+      </c>
+      <c r="J312" t="str">
+        <v>2026-04-10T05:39:40.991Z</v>
+      </c>
+      <c r="K312" t="str">
+        <v/>
+      </c>
+      <c r="L312" t="str">
+        <v/>
+      </c>
+      <c r="M312" t="str">
+        <v/>
+      </c>
+      <c r="N312" t="str">
+        <v/>
+      </c>
+      <c r="O312" t="str">
+        <v/>
+      </c>
+      <c r="P312" t="str">
+        <v/>
+      </c>
+      <c r="Q312" t="str">
+        <v/>
+      </c>
+      <c r="R312" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="str">
+        <v>KLD10027</v>
+      </c>
+      <c r="B313" t="str">
+        <v>KL1009</v>
+      </c>
+      <c r="C313" t="str">
+        <v>Small</v>
+      </c>
+      <c r="D313" t="str">
+        <v>約1.7g</v>
+      </c>
+      <c r="E313" t="str">
+        <v/>
+      </c>
+      <c r="F313" t="str">
+        <v>Small</v>
+      </c>
+      <c r="G313" t="str">
+        <v/>
+      </c>
+      <c r="H313" t="str">
+        <v>620</v>
+      </c>
+      <c r="I313" t="str">
+        <v>2026-04-10T05:39:42.698Z</v>
+      </c>
+      <c r="J313" t="str">
+        <v>2026-04-10T05:39:42.698Z</v>
+      </c>
+      <c r="K313" t="str">
+        <v/>
+      </c>
+      <c r="L313" t="str">
+        <v/>
+      </c>
+      <c r="M313" t="str">
+        <v/>
+      </c>
+      <c r="N313" t="str">
+        <v/>
+      </c>
+      <c r="O313" t="str">
+        <v/>
+      </c>
+      <c r="P313" t="str">
+        <v/>
+      </c>
+      <c r="Q313" t="str">
+        <v/>
+      </c>
+      <c r="R313" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="str">
+        <v>KLD10028</v>
+      </c>
+      <c r="B314" t="str">
+        <v>KL1009</v>
+      </c>
+      <c r="C314" t="str">
+        <v>Small-Medium</v>
+      </c>
+      <c r="D314" t="str">
+        <v>約3.3g</v>
+      </c>
+      <c r="E314" t="str">
+        <v/>
+      </c>
+      <c r="F314" t="str">
+        <v>Small-Medium</v>
+      </c>
+      <c r="G314" t="str">
+        <v/>
+      </c>
+      <c r="H314" t="str">
+        <v>620</v>
+      </c>
+      <c r="I314" t="str">
+        <v>2026-04-10T05:39:42.698Z</v>
+      </c>
+      <c r="J314" t="str">
+        <v>2026-04-10T05:39:42.698Z</v>
+      </c>
+      <c r="K314" t="str">
+        <v/>
+      </c>
+      <c r="L314" t="str">
+        <v/>
+      </c>
+      <c r="M314" t="str">
+        <v/>
+      </c>
+      <c r="N314" t="str">
+        <v/>
+      </c>
+      <c r="O314" t="str">
+        <v/>
+      </c>
+      <c r="P314" t="str">
+        <v/>
+      </c>
+      <c r="Q314" t="str">
+        <v/>
+      </c>
+      <c r="R314" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v>KLD10029</v>
+      </c>
+      <c r="B315" t="str">
+        <v>KL1009</v>
+      </c>
+      <c r="C315" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="D315" t="str">
+        <v>6.5g</v>
+      </c>
+      <c r="E315" t="str">
+        <v/>
+      </c>
+      <c r="F315" t="str">
+        <v>Medium</v>
+      </c>
+      <c r="G315" t="str">
+        <v/>
+      </c>
+      <c r="H315" t="str">
+        <v>620</v>
+      </c>
+      <c r="I315" t="str">
+        <v>2026-04-10T05:39:42.698Z</v>
+      </c>
+      <c r="J315" t="str">
+        <v>2026-04-10T05:39:42.698Z</v>
+      </c>
+      <c r="K315" t="str">
+        <v/>
+      </c>
+      <c r="L315" t="str">
+        <v/>
+      </c>
+      <c r="M315" t="str">
+        <v/>
+      </c>
+      <c r="N315" t="str">
+        <v/>
+      </c>
+      <c r="O315" t="str">
+        <v/>
+      </c>
+      <c r="P315" t="str">
+        <v/>
+      </c>
+      <c r="Q315" t="str">
+        <v/>
+      </c>
+      <c r="R315" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>KLD10030</v>
+      </c>
+      <c r="B316" t="str">
+        <v>KL1009</v>
+      </c>
+      <c r="C316" t="str">
+        <v>Medium-Large</v>
+      </c>
+      <c r="D316" t="str">
+        <v>約8.4g</v>
+      </c>
+      <c r="E316" t="str">
+        <v/>
+      </c>
+      <c r="F316" t="str">
+        <v>Medium-Large</v>
+      </c>
+      <c r="G316" t="str">
+        <v/>
+      </c>
+      <c r="H316" t="str">
+        <v>670</v>
+      </c>
+      <c r="I316" t="str">
+        <v>2026-04-10T05:39:42.698Z</v>
+      </c>
+      <c r="J316" t="str">
+        <v>2026-04-10T05:39:42.698Z</v>
+      </c>
+      <c r="K316" t="str">
+        <v/>
+      </c>
+      <c r="L316" t="str">
+        <v/>
+      </c>
+      <c r="M316" t="str">
+        <v/>
+      </c>
+      <c r="N316" t="str">
+        <v/>
+      </c>
+      <c r="O316" t="str">
+        <v/>
+      </c>
+      <c r="P316" t="str">
+        <v/>
+      </c>
+      <c r="Q316" t="str">
+        <v/>
+      </c>
+      <c r="R316" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>KLD10031</v>
+      </c>
+      <c r="B317" t="str">
+        <v>KL1009</v>
+      </c>
+      <c r="C317" t="str">
+        <v>Large</v>
+      </c>
+      <c r="D317" t="str">
+        <v>約13.5g</v>
+      </c>
+      <c r="E317" t="str">
+        <v/>
+      </c>
+      <c r="F317" t="str">
+        <v>Large</v>
+      </c>
+      <c r="G317" t="str">
+        <v/>
+      </c>
+      <c r="H317" t="str">
+        <v>740</v>
+      </c>
+      <c r="I317" t="str">
+        <v>2026-04-10T05:39:42.698Z</v>
+      </c>
+      <c r="J317" t="str">
+        <v>2026-04-10T05:39:42.698Z</v>
+      </c>
+      <c r="K317" t="str">
+        <v/>
+      </c>
+      <c r="L317" t="str">
+        <v/>
+      </c>
+      <c r="M317" t="str">
+        <v/>
+      </c>
+      <c r="N317" t="str">
+        <v/>
+      </c>
+      <c r="O317" t="str">
+        <v/>
+      </c>
+      <c r="P317" t="str">
+        <v/>
+      </c>
+      <c r="Q317" t="str">
+        <v/>
+      </c>
+      <c r="R317" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>KLD10032</v>
+      </c>
+      <c r="B318" t="str">
+        <v>KL1010</v>
+      </c>
+      <c r="C318" t="str">
+        <v>2"</v>
+      </c>
+      <c r="D318" t="str">
+        <v>約0.5g</v>
+      </c>
+      <c r="E318" t="str">
+        <v/>
+      </c>
+      <c r="F318" t="str">
+        <v>2"</v>
+      </c>
+      <c r="G318" t="str">
+        <v/>
+      </c>
+      <c r="H318" t="str">
+        <v>620</v>
+      </c>
+      <c r="I318" t="str">
+        <v>2026-04-10T05:39:45.196Z</v>
+      </c>
+      <c r="J318" t="str">
+        <v>2026-04-10T05:39:45.196Z</v>
+      </c>
+      <c r="K318" t="str">
+        <v/>
+      </c>
+      <c r="L318" t="str">
+        <v/>
+      </c>
+      <c r="M318" t="str">
+        <v/>
+      </c>
+      <c r="N318" t="str">
+        <v/>
+      </c>
+      <c r="O318" t="str">
+        <v/>
+      </c>
+      <c r="P318" t="str">
+        <v/>
+      </c>
+      <c r="Q318" t="str">
+        <v/>
+      </c>
+      <c r="R318" t="str">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
+        <v>KLD10033</v>
+      </c>
+      <c r="B319" t="str">
+        <v>KL1010</v>
+      </c>
+      <c r="C319" t="str">
+        <v>2.5"</v>
+      </c>
+      <c r="D319" t="str">
+        <v>約0.7g</v>
+      </c>
+      <c r="E319" t="str">
+        <v/>
+      </c>
+      <c r="F319" t="str">
+        <v>2.5"</v>
+      </c>
+      <c r="G319" t="str">
+        <v/>
+      </c>
+      <c r="H319" t="str">
+        <v>620</v>
+      </c>
+      <c r="I319" t="str">
+        <v>2026-04-10T05:39:45.196Z</v>
+      </c>
+      <c r="J319" t="str">
+        <v>2026-04-10T05:39:45.196Z</v>
+      </c>
+      <c r="K319" t="str">
+        <v/>
+      </c>
+      <c r="L319" t="str">
+        <v/>
+      </c>
+      <c r="M319" t="str">
+        <v/>
+      </c>
+      <c r="N319" t="str">
+        <v/>
+      </c>
+      <c r="O319" t="str">
+        <v/>
+      </c>
+      <c r="P319" t="str">
+        <v/>
+      </c>
+      <c r="Q319" t="str">
+        <v/>
+      </c>
+      <c r="R319" t="str">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>KLD10034</v>
+      </c>
+      <c r="B320" t="str">
+        <v>KL1010</v>
+      </c>
+      <c r="C320" t="str">
+        <v>3"</v>
+      </c>
+      <c r="D320" t="str">
+        <v>約1.2g</v>
+      </c>
+      <c r="E320" t="str">
+        <v/>
+      </c>
+      <c r="F320" t="str">
+        <v>3"</v>
+      </c>
+      <c r="G320" t="str">
+        <v/>
+      </c>
+      <c r="H320" t="str">
+        <v>620</v>
+      </c>
+      <c r="I320" t="str">
+        <v>2026-04-10T05:39:45.196Z</v>
+      </c>
+      <c r="J320" t="str">
+        <v>2026-04-10T05:39:45.196Z</v>
+      </c>
+      <c r="K320" t="str">
+        <v/>
+      </c>
+      <c r="L320" t="str">
+        <v/>
+      </c>
+      <c r="M320" t="str">
+        <v/>
+      </c>
+      <c r="N320" t="str">
+        <v/>
+      </c>
+      <c r="O320" t="str">
+        <v/>
+      </c>
+      <c r="P320" t="str">
+        <v/>
+      </c>
+      <c r="Q320" t="str">
+        <v/>
+      </c>
+      <c r="R320" t="str">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>KLD10035</v>
+      </c>
+      <c r="B321" t="str">
+        <v>KL1010</v>
+      </c>
+      <c r="C321" t="str">
+        <v>3.5"</v>
+      </c>
+      <c r="D321" t="str">
+        <v>約1.9g</v>
+      </c>
+      <c r="E321" t="str">
+        <v/>
+      </c>
+      <c r="F321" t="str">
+        <v>3.5"</v>
+      </c>
+      <c r="G321" t="str">
+        <v/>
+      </c>
+      <c r="H321" t="str">
+        <v>620</v>
+      </c>
+      <c r="I321" t="str">
+        <v>2026-04-10T05:39:45.196Z</v>
+      </c>
+      <c r="J321" t="str">
+        <v>2026-04-10T05:39:45.196Z</v>
+      </c>
+      <c r="K321" t="str">
+        <v/>
+      </c>
+      <c r="L321" t="str">
+        <v/>
+      </c>
+      <c r="M321" t="str">
+        <v/>
+      </c>
+      <c r="N321" t="str">
+        <v/>
+      </c>
+      <c r="O321" t="str">
+        <v/>
+      </c>
+      <c r="P321" t="str">
+        <v/>
+      </c>
+      <c r="Q321" t="str">
+        <v/>
+      </c>
+      <c r="R321" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>KLD10036</v>
+      </c>
+      <c r="B322" t="str">
+        <v>KL1010</v>
+      </c>
+      <c r="C322" t="str">
+        <v>4.5"</v>
+      </c>
+      <c r="D322" t="str">
+        <v>約3.3g</v>
+      </c>
+      <c r="E322" t="str">
+        <v/>
+      </c>
+      <c r="F322" t="str">
+        <v>4.5"</v>
+      </c>
+      <c r="G322" t="str">
+        <v/>
+      </c>
+      <c r="H322" t="str">
+        <v>620</v>
+      </c>
+      <c r="I322" t="str">
+        <v>2026-04-10T05:39:45.196Z</v>
+      </c>
+      <c r="J322" t="str">
+        <v>2026-04-10T05:39:45.196Z</v>
+      </c>
+      <c r="K322" t="str">
+        <v/>
+      </c>
+      <c r="L322" t="str">
+        <v/>
+      </c>
+      <c r="M322" t="str">
+        <v/>
+      </c>
+      <c r="N322" t="str">
+        <v/>
+      </c>
+      <c r="O322" t="str">
+        <v/>
+      </c>
+      <c r="P322" t="str">
+        <v/>
+      </c>
+      <c r="Q322" t="str">
+        <v/>
+      </c>
+      <c r="R322" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>KLD10037</v>
+      </c>
+      <c r="B323" t="str">
+        <v>KL1010</v>
+      </c>
+      <c r="C323" t="str">
+        <v>5.5"</v>
+      </c>
+      <c r="D323" t="str">
+        <v>約5.6g</v>
+      </c>
+      <c r="E323" t="str">
+        <v/>
+      </c>
+      <c r="F323" t="str">
+        <v>5.5"</v>
+      </c>
+      <c r="G323" t="str">
+        <v/>
+      </c>
+      <c r="H323" t="str">
+        <v>740</v>
+      </c>
+      <c r="I323" t="str">
+        <v>2026-04-10T05:39:45.196Z</v>
+      </c>
+      <c r="J323" t="str">
+        <v>2026-04-10T05:39:45.196Z</v>
+      </c>
+      <c r="K323" t="str">
+        <v/>
+      </c>
+      <c r="L323" t="str">
+        <v/>
+      </c>
+      <c r="M323" t="str">
+        <v/>
+      </c>
+      <c r="N323" t="str">
+        <v/>
+      </c>
+      <c r="O323" t="str">
+        <v/>
+      </c>
+      <c r="P323" t="str">
+        <v/>
+      </c>
+      <c r="Q323" t="str">
+        <v/>
+      </c>
+      <c r="R323" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>KLD10038</v>
+      </c>
+      <c r="B324" t="str">
+        <v>KL1011</v>
+      </c>
+      <c r="C324" t="str">
+        <v>3"</v>
+      </c>
+      <c r="D324" t="str">
+        <v>約1.3g</v>
+      </c>
+      <c r="E324" t="str">
+        <v/>
+      </c>
+      <c r="F324" t="str">
+        <v>3"</v>
+      </c>
+      <c r="G324" t="str">
+        <v/>
+      </c>
+      <c r="H324" t="str">
+        <v>740</v>
+      </c>
+      <c r="I324" t="str">
+        <v>2026-04-10T05:39:48.055Z</v>
+      </c>
+      <c r="J324" t="str">
+        <v>2026-04-10T05:39:48.055Z</v>
+      </c>
+      <c r="K324" t="str">
+        <v/>
+      </c>
+      <c r="L324" t="str">
+        <v/>
+      </c>
+      <c r="M324" t="str">
+        <v/>
+      </c>
+      <c r="N324" t="str">
+        <v/>
+      </c>
+      <c r="O324" t="str">
+        <v/>
+      </c>
+      <c r="P324" t="str">
+        <v/>
+      </c>
+      <c r="Q324" t="str">
+        <v/>
+      </c>
+      <c r="R324" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>KLD10039</v>
+      </c>
+      <c r="B325" t="str">
+        <v>KL1012</v>
+      </c>
+      <c r="C325" t="str">
+        <v>3.5"</v>
+      </c>
+      <c r="D325" t="str">
+        <v>16.3g</v>
+      </c>
+      <c r="E325" t="str">
+        <v/>
+      </c>
+      <c r="F325" t="str">
+        <v>3.5"</v>
+      </c>
+      <c r="G325" t="str">
+        <v/>
+      </c>
+      <c r="H325" t="str">
+        <v/>
+      </c>
+      <c r="I325" t="str">
+        <v>2026-04-10T05:39:51.253Z</v>
+      </c>
+      <c r="J325" t="str">
+        <v>2026-04-10T05:39:51.253Z</v>
+      </c>
+      <c r="K325" t="str">
+        <v/>
+      </c>
+      <c r="L325" t="str">
+        <v/>
+      </c>
+      <c r="M325" t="str">
+        <v/>
+      </c>
+      <c r="N325" t="str">
+        <v/>
+      </c>
+      <c r="O325" t="str">
+        <v/>
+      </c>
+      <c r="P325" t="str">
+        <v/>
+      </c>
+      <c r="Q325" t="str">
+        <v/>
+      </c>
+      <c r="R325" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>KLD10040</v>
+      </c>
+      <c r="B326" t="str">
+        <v>KL1013</v>
+      </c>
+      <c r="C326" t="str">
+        <v>2.4および2.8インチ インナートレー×2※2.4"のみインナートレーを1枚増やし</v>
+      </c>
+      <c r="D326" t="str">
+        <v/>
+      </c>
+      <c r="E326" t="str">
+        <v/>
+      </c>
+      <c r="F326" t="str">
+        <v>2.4および2.8インチ インナートレー×2※2.4"のみインナートレーを1枚増やし</v>
+      </c>
+      <c r="G326" t="str">
+        <v/>
+      </c>
+      <c r="H326" t="str">
+        <v/>
+      </c>
+      <c r="I326" t="str">
+        <v>2026-04-10T05:39:55.263Z</v>
+      </c>
+      <c r="J326" t="str">
+        <v>2026-04-10T05:39:55.263Z</v>
+      </c>
+      <c r="K326" t="str">
+        <v/>
+      </c>
+      <c r="L326" t="str">
+        <v/>
+      </c>
+      <c r="M326" t="str">
+        <v/>
+      </c>
+      <c r="N326" t="str">
+        <v/>
+      </c>
+      <c r="O326" t="str">
+        <v/>
+      </c>
+      <c r="P326" t="str">
+        <v/>
+      </c>
+      <c r="Q326" t="str">
+        <v/>
+      </c>
+      <c r="R326" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>KLD10041</v>
+      </c>
+      <c r="B327" t="str">
+        <v>KL1013</v>
+      </c>
+      <c r="C327" t="str">
+        <v>2"</v>
+      </c>
+      <c r="D327" t="str">
+        <v>約1.2g</v>
+      </c>
+      <c r="E327" t="str">
+        <v/>
+      </c>
+      <c r="F327" t="str">
+        <v>2"</v>
+      </c>
+      <c r="G327" t="str">
+        <v/>
+      </c>
+      <c r="H327" t="str">
+        <v>720</v>
+      </c>
+      <c r="I327" t="str">
+        <v>2026-04-10T05:39:55.263Z</v>
+      </c>
+      <c r="J327" t="str">
+        <v>2026-04-10T05:39:55.263Z</v>
+      </c>
+      <c r="K327" t="str">
+        <v/>
+      </c>
+      <c r="L327" t="str">
+        <v/>
+      </c>
+      <c r="M327" t="str">
+        <v/>
+      </c>
+      <c r="N327" t="str">
+        <v/>
+      </c>
+      <c r="O327" t="str">
+        <v/>
+      </c>
+      <c r="P327" t="str">
+        <v/>
+      </c>
+      <c r="Q327" t="str">
+        <v/>
+      </c>
+      <c r="R327" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>KLD10042</v>
+      </c>
+      <c r="B328" t="str">
+        <v>KL1013</v>
+      </c>
+      <c r="C328" t="str">
+        <v>2.4"</v>
+      </c>
+      <c r="D328" t="str">
+        <v>約2.1g</v>
+      </c>
+      <c r="E328" t="str">
+        <v/>
+      </c>
+      <c r="F328" t="str">
+        <v>2.4"</v>
+      </c>
+      <c r="G328" t="str">
+        <v/>
+      </c>
+      <c r="H328" t="str">
+        <v>770</v>
+      </c>
+      <c r="I328" t="str">
+        <v>2026-04-10T05:39:55.263Z</v>
+      </c>
+      <c r="J328" t="str">
+        <v>2026-04-10T05:39:55.263Z</v>
+      </c>
+      <c r="K328" t="str">
+        <v/>
+      </c>
+      <c r="L328" t="str">
+        <v/>
+      </c>
+      <c r="M328" t="str">
+        <v/>
+      </c>
+      <c r="N328" t="str">
+        <v/>
+      </c>
+      <c r="O328" t="str">
+        <v/>
+      </c>
+      <c r="P328" t="str">
+        <v/>
+      </c>
+      <c r="Q328" t="str">
+        <v/>
+      </c>
+      <c r="R328" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v>KLD10043</v>
+      </c>
+      <c r="B329" t="str">
+        <v>KL1013</v>
+      </c>
+      <c r="C329" t="str">
+        <v>2.8"</v>
+      </c>
+      <c r="D329" t="str">
+        <v>3.4g</v>
+      </c>
+      <c r="E329" t="str">
+        <v/>
+      </c>
+      <c r="F329" t="str">
+        <v>2.8"</v>
+      </c>
+      <c r="G329" t="str">
+        <v/>
+      </c>
+      <c r="H329" t="str">
+        <v>770</v>
+      </c>
+      <c r="I329" t="str">
+        <v>2026-04-10T05:39:55.263Z</v>
+      </c>
+      <c r="J329" t="str">
+        <v>2026-04-10T05:39:55.263Z</v>
+      </c>
+      <c r="K329" t="str">
+        <v/>
+      </c>
+      <c r="L329" t="str">
+        <v/>
+      </c>
+      <c r="M329" t="str">
+        <v/>
+      </c>
+      <c r="N329" t="str">
+        <v/>
+      </c>
+      <c r="O329" t="str">
+        <v/>
+      </c>
+      <c r="P329" t="str">
+        <v/>
+      </c>
+      <c r="Q329" t="str">
+        <v/>
+      </c>
+      <c r="R329" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
+        <v>KLD10044</v>
+      </c>
+      <c r="B330" t="str">
+        <v>KL1013</v>
+      </c>
+      <c r="C330" t="str">
+        <v>3.6"</v>
+      </c>
+      <c r="D330" t="str">
+        <v>6.6g</v>
+      </c>
+      <c r="E330" t="str">
+        <v/>
+      </c>
+      <c r="F330" t="str">
+        <v>3.6"</v>
+      </c>
+      <c r="G330" t="str">
+        <v/>
+      </c>
+      <c r="H330" t="str">
+        <v>820</v>
+      </c>
+      <c r="I330" t="str">
+        <v>2026-04-10T05:39:55.263Z</v>
+      </c>
+      <c r="J330" t="str">
+        <v>2026-04-10T05:39:55.263Z</v>
+      </c>
+      <c r="K330" t="str">
+        <v/>
+      </c>
+      <c r="L330" t="str">
+        <v/>
+      </c>
+      <c r="M330" t="str">
+        <v/>
+      </c>
+      <c r="N330" t="str">
+        <v/>
+      </c>
+      <c r="O330" t="str">
+        <v/>
+      </c>
+      <c r="P330" t="str">
+        <v/>
+      </c>
+      <c r="Q330" t="str">
+        <v/>
+      </c>
+      <c r="R330" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v>KLD10045</v>
+      </c>
+      <c r="B331" t="str">
+        <v>KL1013</v>
+      </c>
+      <c r="C331" t="str">
+        <v>4.4"</v>
+      </c>
+      <c r="D331" t="str">
+        <v>12.0g</v>
+      </c>
+      <c r="E331" t="str">
+        <v/>
+      </c>
+      <c r="F331" t="str">
+        <v>4.4"</v>
+      </c>
+      <c r="G331" t="str">
+        <v/>
+      </c>
+      <c r="H331" t="str">
+        <v>860</v>
+      </c>
+      <c r="I331" t="str">
+        <v>2026-04-10T05:39:55.263Z</v>
+      </c>
+      <c r="J331" t="str">
+        <v>2026-04-10T05:39:55.263Z</v>
+      </c>
+      <c r="K331" t="str">
+        <v/>
+      </c>
+      <c r="L331" t="str">
+        <v/>
+      </c>
+      <c r="M331" t="str">
+        <v/>
+      </c>
+      <c r="N331" t="str">
+        <v/>
+      </c>
+      <c r="O331" t="str">
+        <v/>
+      </c>
+      <c r="P331" t="str">
+        <v/>
+      </c>
+      <c r="Q331" t="str">
+        <v/>
+      </c>
+      <c r="R331" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
+        <v>KLD10046</v>
+      </c>
+      <c r="B332" t="str">
+        <v>KL1014</v>
+      </c>
+      <c r="C332" t="str">
+        <v>2.8"</v>
+      </c>
+      <c r="D332" t="str">
+        <v>1.5g</v>
+      </c>
+      <c r="E332" t="str">
+        <v/>
+      </c>
+      <c r="F332" t="str">
+        <v>2.8"</v>
+      </c>
+      <c r="G332" t="str">
+        <v/>
+      </c>
+      <c r="H332" t="str">
+        <v>740</v>
+      </c>
+      <c r="I332" t="str">
+        <v>2026-04-10T05:40:06.614Z</v>
+      </c>
+      <c r="J332" t="str">
+        <v>2026-04-10T05:40:06.614Z</v>
+      </c>
+      <c r="K332" t="str">
+        <v/>
+      </c>
+      <c r="L332" t="str">
+        <v/>
+      </c>
+      <c r="M332" t="str">
+        <v/>
+      </c>
+      <c r="N332" t="str">
+        <v/>
+      </c>
+      <c r="O332" t="str">
+        <v/>
+      </c>
+      <c r="P332" t="str">
+        <v/>
+      </c>
+      <c r="Q332" t="str">
+        <v/>
+      </c>
+      <c r="R332" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
+        <v>KLD10047</v>
+      </c>
+      <c r="B333" t="str">
+        <v>KL1014</v>
+      </c>
+      <c r="C333" t="str">
+        <v>3.8"</v>
+      </c>
+      <c r="D333" t="str">
+        <v>3.3g</v>
+      </c>
+      <c r="E333" t="str">
+        <v/>
+      </c>
+      <c r="F333" t="str">
+        <v>3.8"</v>
+      </c>
+      <c r="G333" t="str">
+        <v/>
+      </c>
+      <c r="H333" t="str">
+        <v>740</v>
+      </c>
+      <c r="I333" t="str">
+        <v>2026-04-10T05:40:06.614Z</v>
+      </c>
+      <c r="J333" t="str">
+        <v>2026-04-10T05:40:06.614Z</v>
+      </c>
+      <c r="K333" t="str">
+        <v/>
+      </c>
+      <c r="L333" t="str">
+        <v/>
+      </c>
+      <c r="M333" t="str">
+        <v/>
+      </c>
+      <c r="N333" t="str">
+        <v/>
+      </c>
+      <c r="O333" t="str">
+        <v/>
+      </c>
+      <c r="P333" t="str">
+        <v/>
+      </c>
+      <c r="Q333" t="str">
+        <v/>
+      </c>
+      <c r="R333" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="str">
+        <v>KLD10048</v>
+      </c>
+      <c r="B334" t="str">
+        <v>KL1014</v>
+      </c>
+      <c r="C334" t="str">
+        <v>4.8"</v>
+      </c>
+      <c r="D334" t="str">
+        <v>6.3g</v>
+      </c>
+      <c r="E334" t="str">
+        <v/>
+      </c>
+      <c r="F334" t="str">
+        <v>4.8"</v>
+      </c>
+      <c r="G334" t="str">
+        <v/>
+      </c>
+      <c r="H334" t="str">
+        <v>740</v>
+      </c>
+      <c r="I334" t="str">
+        <v>2026-04-10T05:40:06.614Z</v>
+      </c>
+      <c r="J334" t="str">
+        <v>2026-04-10T05:40:06.614Z</v>
+      </c>
+      <c r="K334" t="str">
+        <v/>
+      </c>
+      <c r="L334" t="str">
+        <v/>
+      </c>
+      <c r="M334" t="str">
+        <v/>
+      </c>
+      <c r="N334" t="str">
+        <v/>
+      </c>
+      <c r="O334" t="str">
+        <v/>
+      </c>
+      <c r="P334" t="str">
+        <v/>
+      </c>
+      <c r="Q334" t="str">
+        <v/>
+      </c>
+      <c r="R334" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="str">
+        <v>KLD10049</v>
+      </c>
+      <c r="B335" t="str">
+        <v>KL1014</v>
+      </c>
+      <c r="C335" t="str">
+        <v>5.8"</v>
+      </c>
+      <c r="D335" t="str">
+        <v>10.6g</v>
+      </c>
+      <c r="E335" t="str">
+        <v/>
+      </c>
+      <c r="F335" t="str">
+        <v>5.8"</v>
+      </c>
+      <c r="G335" t="str">
+        <v/>
+      </c>
+      <c r="H335" t="str">
+        <v>860</v>
+      </c>
+      <c r="I335" t="str">
+        <v>2026-04-10T05:40:06.614Z</v>
+      </c>
+      <c r="J335" t="str">
+        <v>2026-04-10T05:40:06.614Z</v>
+      </c>
+      <c r="K335" t="str">
+        <v/>
+      </c>
+      <c r="L335" t="str">
+        <v/>
+      </c>
+      <c r="M335" t="str">
+        <v/>
+      </c>
+      <c r="N335" t="str">
+        <v/>
+      </c>
+      <c r="O335" t="str">
+        <v/>
+      </c>
+      <c r="P335" t="str">
+        <v/>
+      </c>
+      <c r="Q335" t="str">
+        <v/>
+      </c>
+      <c r="R335" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="str">
+        <v>KLD10050</v>
+      </c>
+      <c r="B336" t="str">
+        <v>KL1015</v>
+      </c>
+      <c r="C336" t="str">
+        <v>2"</v>
+      </c>
+      <c r="D336" t="str">
+        <v>1.1g</v>
+      </c>
+      <c r="E336" t="str">
+        <v/>
+      </c>
+      <c r="F336" t="str">
+        <v>2"</v>
+      </c>
+      <c r="G336" t="str">
+        <v/>
+      </c>
+      <c r="H336" t="str">
+        <v>740</v>
+      </c>
+      <c r="I336" t="str">
+        <v>2026-04-10T05:40:13.153Z</v>
+      </c>
+      <c r="J336" t="str">
+        <v>2026-04-10T05:40:13.153Z</v>
+      </c>
+      <c r="K336" t="str">
+        <v/>
+      </c>
+      <c r="L336" t="str">
+        <v/>
+      </c>
+      <c r="M336" t="str">
+        <v/>
+      </c>
+      <c r="N336" t="str">
+        <v/>
+      </c>
+      <c r="O336" t="str">
+        <v/>
+      </c>
+      <c r="P336" t="str">
+        <v/>
+      </c>
+      <c r="Q336" t="str">
+        <v/>
+      </c>
+      <c r="R336" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="str">
+        <v>KLD10051</v>
+      </c>
+      <c r="B337" t="str">
+        <v>KL1015</v>
+      </c>
+      <c r="C337" t="str">
+        <v>3"</v>
+      </c>
+      <c r="D337" t="str">
+        <v>1.7g</v>
+      </c>
+      <c r="E337" t="str">
+        <v/>
+      </c>
+      <c r="F337" t="str">
+        <v>3"</v>
+      </c>
+      <c r="G337" t="str">
+        <v/>
+      </c>
+      <c r="H337" t="str">
+        <v>740</v>
+      </c>
+      <c r="I337" t="str">
+        <v>2026-04-10T05:40:13.153Z</v>
+      </c>
+      <c r="J337" t="str">
+        <v>2026-04-10T05:40:13.153Z</v>
+      </c>
+      <c r="K337" t="str">
+        <v/>
+      </c>
+      <c r="L337" t="str">
+        <v/>
+      </c>
+      <c r="M337" t="str">
+        <v/>
+      </c>
+      <c r="N337" t="str">
+        <v/>
+      </c>
+      <c r="O337" t="str">
+        <v/>
+      </c>
+      <c r="P337" t="str">
+        <v/>
+      </c>
+      <c r="Q337" t="str">
+        <v/>
+      </c>
+      <c r="R337" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="str">
+        <v>KLD10052</v>
+      </c>
+      <c r="B338" t="str">
+        <v>KL1015</v>
+      </c>
+      <c r="C338" t="str">
+        <v>3.5"</v>
+      </c>
+      <c r="D338" t="str">
+        <v>2.7g</v>
+      </c>
+      <c r="E338" t="str">
+        <v/>
+      </c>
+      <c r="F338" t="str">
+        <v>3.5"</v>
+      </c>
+      <c r="G338" t="str">
+        <v/>
+      </c>
+      <c r="H338" t="str">
+        <v>740</v>
+      </c>
+      <c r="I338" t="str">
+        <v>2026-04-10T05:40:13.153Z</v>
+      </c>
+      <c r="J338" t="str">
+        <v>2026-04-10T05:40:13.153Z</v>
+      </c>
+      <c r="K338" t="str">
+        <v/>
+      </c>
+      <c r="L338" t="str">
+        <v/>
+      </c>
+      <c r="M338" t="str">
+        <v/>
+      </c>
+      <c r="N338" t="str">
+        <v/>
+      </c>
+      <c r="O338" t="str">
+        <v/>
+      </c>
+      <c r="P338" t="str">
+        <v/>
+      </c>
+      <c r="Q338" t="str">
+        <v/>
+      </c>
+      <c r="R338" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="str">
+        <v>KLD10053</v>
+      </c>
+      <c r="B339" t="str">
+        <v>KL1016</v>
+      </c>
+      <c r="C339" t="str">
+        <v>2"</v>
+      </c>
+      <c r="D339" t="str">
+        <v>0.9g</v>
+      </c>
+      <c r="E339" t="str">
+        <v/>
+      </c>
+      <c r="F339" t="str">
+        <v>2"</v>
+      </c>
+      <c r="G339" t="str">
+        <v/>
+      </c>
+      <c r="H339" t="str">
+        <v>740</v>
+      </c>
+      <c r="I339" t="str">
+        <v>2026-04-10T05:40:20.195Z</v>
+      </c>
+      <c r="J339" t="str">
+        <v>2026-04-10T05:40:20.195Z</v>
+      </c>
+      <c r="K339" t="str">
+        <v/>
+      </c>
+      <c r="L339" t="str">
+        <v/>
+      </c>
+      <c r="M339" t="str">
+        <v/>
+      </c>
+      <c r="N339" t="str">
+        <v/>
+      </c>
+      <c r="O339" t="str">
+        <v/>
+      </c>
+      <c r="P339" t="str">
+        <v/>
+      </c>
+      <c r="Q339" t="str">
+        <v/>
+      </c>
+      <c r="R339" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="str">
+        <v>KLD10054</v>
+      </c>
+      <c r="B340" t="str">
+        <v>KL1016</v>
+      </c>
+      <c r="C340" t="str">
+        <v>3"</v>
+      </c>
+      <c r="D340" t="str">
+        <v>2.2g</v>
+      </c>
+      <c r="E340" t="str">
+        <v/>
+      </c>
+      <c r="F340" t="str">
+        <v>3"</v>
+      </c>
+      <c r="G340" t="str">
+        <v/>
+      </c>
+      <c r="H340" t="str">
+        <v>740</v>
+      </c>
+      <c r="I340" t="str">
+        <v>2026-04-10T05:40:20.195Z</v>
+      </c>
+      <c r="J340" t="str">
+        <v>2026-04-10T05:40:20.195Z</v>
+      </c>
+      <c r="K340" t="str">
+        <v/>
+      </c>
+      <c r="L340" t="str">
+        <v/>
+      </c>
+      <c r="M340" t="str">
+        <v/>
+      </c>
+      <c r="N340" t="str">
+        <v/>
+      </c>
+      <c r="O340" t="str">
+        <v/>
+      </c>
+      <c r="P340" t="str">
+        <v/>
+      </c>
+      <c r="Q340" t="str">
+        <v/>
+      </c>
+      <c r="R340" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="str">
+        <v>KLD10055</v>
+      </c>
+      <c r="B341" t="str">
+        <v>KL1016</v>
+      </c>
+      <c r="C341" t="str">
+        <v>4"</v>
+      </c>
+      <c r="D341" t="str">
+        <v>5.2g</v>
+      </c>
+      <c r="E341" t="str">
+        <v/>
+      </c>
+      <c r="F341" t="str">
+        <v>4"</v>
+      </c>
+      <c r="G341" t="str">
+        <v/>
+      </c>
+      <c r="H341" t="str">
+        <v>740</v>
+      </c>
+      <c r="I341" t="str">
+        <v>2026-04-10T05:40:20.195Z</v>
+      </c>
+      <c r="J341" t="str">
+        <v>2026-04-10T05:40:20.195Z</v>
+      </c>
+      <c r="K341" t="str">
+        <v/>
+      </c>
+      <c r="L341" t="str">
+        <v/>
+      </c>
+      <c r="M341" t="str">
+        <v/>
+      </c>
+      <c r="N341" t="str">
+        <v/>
+      </c>
+      <c r="O341" t="str">
+        <v/>
+      </c>
+      <c r="P341" t="str">
+        <v/>
+      </c>
+      <c r="Q341" t="str">
+        <v/>
+      </c>
+      <c r="R341" t="str">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="str">
+        <v>KLD10056</v>
+      </c>
+      <c r="B342" t="str">
+        <v>KL1016</v>
+      </c>
+      <c r="C342" t="str">
+        <v>5"</v>
+      </c>
+      <c r="D342" t="str">
+        <v>7.2g</v>
+      </c>
+      <c r="E342" t="str">
+        <v/>
+      </c>
+      <c r="F342" t="str">
+        <v>5"</v>
+      </c>
+      <c r="G342" t="str">
+        <v/>
+      </c>
+      <c r="H342" t="str">
+        <v>740</v>
+      </c>
+      <c r="I342" t="str">
+        <v>2026-04-10T05:40:20.195Z</v>
+      </c>
+      <c r="J342" t="str">
+        <v>2026-04-10T05:40:20.195Z</v>
+      </c>
+      <c r="K342" t="str">
+        <v/>
+      </c>
+      <c r="L342" t="str">
+        <v/>
+      </c>
+      <c r="M342" t="str">
+        <v/>
+      </c>
+      <c r="N342" t="str">
+        <v/>
+      </c>
+      <c r="O342" t="str">
+        <v/>
+      </c>
+      <c r="P342" t="str">
+        <v/>
+      </c>
+      <c r="Q342" t="str">
+        <v/>
+      </c>
+      <c r="R342" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
+        <v>KLD10057</v>
+      </c>
+      <c r="B343" t="str">
+        <v>KL1017</v>
+      </c>
+      <c r="C343" t="str">
+        <v>3.5"</v>
+      </c>
+      <c r="D343" t="str">
+        <v>7.8g</v>
+      </c>
+      <c r="E343" t="str">
+        <v/>
+      </c>
+      <c r="F343" t="str">
+        <v>3.5"</v>
+      </c>
+      <c r="G343" t="str">
+        <v/>
+      </c>
+      <c r="H343" t="str">
+        <v>820</v>
+      </c>
+      <c r="I343" t="str">
+        <v>2026-04-10T05:40:24.698Z</v>
+      </c>
+      <c r="J343" t="str">
+        <v>2026-04-10T05:40:24.698Z</v>
+      </c>
+      <c r="K343" t="str">
+        <v/>
+      </c>
+      <c r="L343" t="str">
+        <v/>
+      </c>
+      <c r="M343" t="str">
+        <v/>
+      </c>
+      <c r="N343" t="str">
+        <v/>
+      </c>
+      <c r="O343" t="str">
+        <v/>
+      </c>
+      <c r="P343" t="str">
+        <v/>
+      </c>
+      <c r="Q343" t="str">
+        <v/>
+      </c>
+      <c r="R343" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="str">
+        <v>KLD10058</v>
+      </c>
+      <c r="B344" t="str">
+        <v>KL1017</v>
+      </c>
+      <c r="C344" t="str">
+        <v>4.25"</v>
+      </c>
+      <c r="D344" t="str">
+        <v>14.0g</v>
+      </c>
+      <c r="E344" t="str">
+        <v/>
+      </c>
+      <c r="F344" t="str">
+        <v>4.25"</v>
+      </c>
+      <c r="G344" t="str">
+        <v/>
+      </c>
+      <c r="H344" t="str">
+        <v>960</v>
+      </c>
+      <c r="I344" t="str">
+        <v>2026-04-10T05:40:24.698Z</v>
+      </c>
+      <c r="J344" t="str">
+        <v>2026-04-10T05:40:24.698Z</v>
+      </c>
+      <c r="K344" t="str">
+        <v/>
+      </c>
+      <c r="L344" t="str">
+        <v/>
+      </c>
+      <c r="M344" t="str">
+        <v/>
+      </c>
+      <c r="N344" t="str">
+        <v/>
+      </c>
+      <c r="O344" t="str">
+        <v/>
+      </c>
+      <c r="P344" t="str">
+        <v/>
+      </c>
+      <c r="Q344" t="str">
+        <v/>
+      </c>
+      <c r="R344" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="str">
+        <v>KLD10059</v>
+      </c>
+      <c r="B345" t="str">
+        <v>KL1018</v>
+      </c>
+      <c r="C345" t="str">
+        <v>Mini 2.5"</v>
+      </c>
+      <c r="D345" t="str">
+        <v>0.6g</v>
+      </c>
+      <c r="E345" t="str">
+        <v/>
+      </c>
+      <c r="F345" t="str">
+        <v>Mini 2.5"</v>
+      </c>
+      <c r="G345" t="str">
+        <v/>
+      </c>
+      <c r="H345" t="str">
+        <v>620</v>
+      </c>
+      <c r="I345" t="str">
+        <v>2026-04-10T05:40:28.288Z</v>
+      </c>
+      <c r="J345" t="str">
+        <v>2026-04-10T05:40:28.288Z</v>
+      </c>
+      <c r="K345" t="str">
+        <v/>
+      </c>
+      <c r="L345" t="str">
+        <v/>
+      </c>
+      <c r="M345" t="str">
+        <v/>
+      </c>
+      <c r="N345" t="str">
+        <v/>
+      </c>
+      <c r="O345" t="str">
+        <v/>
+      </c>
+      <c r="P345" t="str">
+        <v/>
+      </c>
+      <c r="Q345" t="str">
+        <v/>
+      </c>
+      <c r="R345" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="str">
+        <v>KLD10060</v>
+      </c>
+      <c r="B346" t="str">
+        <v>KL1018</v>
+      </c>
+      <c r="C346" t="str">
+        <v>Mini 3.5"</v>
+      </c>
+      <c r="D346" t="str">
+        <v>1.8g</v>
+      </c>
+      <c r="E346" t="str">
+        <v/>
+      </c>
+      <c r="F346" t="str">
+        <v>Mini 3.5"</v>
+      </c>
+      <c r="G346" t="str">
+        <v/>
+      </c>
+      <c r="H346" t="str">
+        <v>620</v>
+      </c>
+      <c r="I346" t="str">
+        <v>2026-04-10T05:40:28.288Z</v>
+      </c>
+      <c r="J346" t="str">
+        <v>2026-04-10T05:40:28.288Z</v>
+      </c>
+      <c r="K346" t="str">
+        <v/>
+      </c>
+      <c r="L346" t="str">
+        <v/>
+      </c>
+      <c r="M346" t="str">
+        <v/>
+      </c>
+      <c r="N346" t="str">
+        <v/>
+      </c>
+      <c r="O346" t="str">
+        <v/>
+      </c>
+      <c r="P346" t="str">
+        <v/>
+      </c>
+      <c r="Q346" t="str">
+        <v/>
+      </c>
+      <c r="R346" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="str">
+        <v>KLD10061</v>
+      </c>
+      <c r="B347" t="str">
+        <v>KL1018</v>
+      </c>
+      <c r="C347" t="str">
+        <v>Slim 4.5"</v>
+      </c>
+      <c r="D347" t="str">
+        <v>2.9g</v>
+      </c>
+      <c r="E347" t="str">
+        <v/>
+      </c>
+      <c r="F347" t="str">
+        <v>Slim 4.5"</v>
+      </c>
+      <c r="G347" t="str">
+        <v/>
+      </c>
+      <c r="H347" t="str">
+        <v>620</v>
+      </c>
+      <c r="I347" t="str">
+        <v>2026-04-10T05:40:28.288Z</v>
+      </c>
+      <c r="J347" t="str">
+        <v>2026-04-10T05:40:28.288Z</v>
+      </c>
+      <c r="K347" t="str">
+        <v/>
+      </c>
+      <c r="L347" t="str">
+        <v/>
+      </c>
+      <c r="M347" t="str">
+        <v/>
+      </c>
+      <c r="N347" t="str">
+        <v/>
+      </c>
+      <c r="O347" t="str">
+        <v/>
+      </c>
+      <c r="P347" t="str">
+        <v/>
+      </c>
+      <c r="Q347" t="str">
+        <v/>
+      </c>
+      <c r="R347" t="str">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
+        <v>KLD10062</v>
+      </c>
+      <c r="B348" t="str">
+        <v>KL1018</v>
+      </c>
+      <c r="C348" t="str">
+        <v>Original 7"</v>
+      </c>
+      <c r="D348" t="str">
+        <v>12.3g</v>
+      </c>
+      <c r="E348" t="str">
+        <v/>
+      </c>
+      <c r="F348" t="str">
+        <v>Original 7"</v>
+      </c>
+      <c r="G348" t="str">
+        <v/>
+      </c>
+      <c r="H348" t="str">
+        <v>740</v>
+      </c>
+      <c r="I348" t="str">
+        <v>2026-04-10T05:40:28.288Z</v>
+      </c>
+      <c r="J348" t="str">
+        <v>2026-04-10T05:40:28.288Z</v>
+      </c>
+      <c r="K348" t="str">
+        <v/>
+      </c>
+      <c r="L348" t="str">
+        <v/>
+      </c>
+      <c r="M348" t="str">
+        <v/>
+      </c>
+      <c r="N348" t="str">
+        <v/>
+      </c>
+      <c r="O348" t="str">
+        <v/>
+      </c>
+      <c r="P348" t="str">
+        <v/>
+      </c>
+      <c r="Q348" t="str">
+        <v/>
+      </c>
+      <c r="R348" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>KLD10063</v>
+      </c>
+      <c r="B349" t="str">
+        <v>KL1018</v>
+      </c>
+      <c r="C349" t="str">
+        <v>Long 8"</v>
+      </c>
+      <c r="D349" t="str">
+        <v>7.7g</v>
+      </c>
+      <c r="E349" t="str">
+        <v/>
+      </c>
+      <c r="F349" t="str">
+        <v>Long 8"</v>
+      </c>
+      <c r="G349" t="str">
+        <v/>
+      </c>
+      <c r="H349" t="str">
+        <v>740</v>
+      </c>
+      <c r="I349" t="str">
+        <v>2026-04-10T05:40:28.288Z</v>
+      </c>
+      <c r="J349" t="str">
+        <v>2026-04-10T05:40:28.288Z</v>
+      </c>
+      <c r="K349" t="str">
+        <v/>
+      </c>
+      <c r="L349" t="str">
+        <v/>
+      </c>
+      <c r="M349" t="str">
+        <v/>
+      </c>
+      <c r="N349" t="str">
+        <v/>
+      </c>
+      <c r="O349" t="str">
+        <v/>
+      </c>
+      <c r="P349" t="str">
+        <v/>
+      </c>
+      <c r="Q349" t="str">
+        <v/>
+      </c>
+      <c r="R349" t="str">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>KLD10064</v>
+      </c>
+      <c r="B350" t="str">
+        <v>KL1018</v>
+      </c>
+      <c r="C350" t="str">
+        <v>Long 11"</v>
+      </c>
+      <c r="D350" t="str">
+        <v>10.9g</v>
+      </c>
+      <c r="E350" t="str">
+        <v/>
+      </c>
+      <c r="F350" t="str">
+        <v>Long 11"</v>
+      </c>
+      <c r="G350" t="str">
+        <v/>
+      </c>
+      <c r="H350" t="str">
+        <v>740</v>
+      </c>
+      <c r="I350" t="str">
+        <v>2026-04-10T05:40:28.288Z</v>
+      </c>
+      <c r="J350" t="str">
+        <v>2026-04-10T05:40:28.288Z</v>
+      </c>
+      <c r="K350" t="str">
+        <v/>
+      </c>
+      <c r="L350" t="str">
+        <v/>
+      </c>
+      <c r="M350" t="str">
+        <v/>
+      </c>
+      <c r="N350" t="str">
+        <v/>
+      </c>
+      <c r="O350" t="str">
+        <v/>
+      </c>
+      <c r="P350" t="str">
+        <v/>
+      </c>
+      <c r="Q350" t="str">
+        <v/>
+      </c>
+      <c r="R350" t="str">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>KLD10065</v>
+      </c>
+      <c r="B351" t="str">
+        <v>KL1018</v>
+      </c>
+      <c r="C351" t="str">
+        <v>ジグヘッドリグ 2.5" &amp; 3.5"</v>
+      </c>
+      <c r="D351" t="str">
+        <v/>
+      </c>
+      <c r="E351" t="str">
+        <v/>
+      </c>
+      <c r="F351" t="str">
+        <v>ジグヘッドリグ 2.5" &amp; 3.5"</v>
+      </c>
+      <c r="G351" t="str">
+        <v/>
+      </c>
+      <c r="H351" t="str">
+        <v/>
+      </c>
+      <c r="I351" t="str">
+        <v>2026-04-10T05:40:28.288Z</v>
+      </c>
+      <c r="J351" t="str">
+        <v>2026-04-10T05:40:28.288Z</v>
+      </c>
+      <c r="K351" t="str">
+        <v/>
+      </c>
+      <c r="L351" t="str">
+        <v/>
+      </c>
+      <c r="M351" t="str">
+        <v/>
+      </c>
+      <c r="N351" t="str">
+        <v/>
+      </c>
+      <c r="O351" t="str">
+        <v/>
+      </c>
+      <c r="P351" t="str">
+        <v/>
+      </c>
+      <c r="Q351" t="str">
+        <v/>
+      </c>
+      <c r="R351" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="str">
+        <v>KLD10066</v>
+      </c>
+      <c r="B352" t="str">
+        <v>KL1018</v>
+      </c>
+      <c r="C352" t="str">
+        <v>スモラバトレーラー 2.5" &amp; 3.5"</v>
+      </c>
+      <c r="D352" t="str">
+        <v/>
+      </c>
+      <c r="E352" t="str">
+        <v/>
+      </c>
+      <c r="F352" t="str">
+        <v>スモラバトレーラー 2.5" &amp; 3.5"</v>
+      </c>
+      <c r="G352" t="str">
+        <v/>
+      </c>
+      <c r="H352" t="str">
+        <v/>
+      </c>
+      <c r="I352" t="str">
+        <v>2026-04-10T05:40:28.288Z</v>
+      </c>
+      <c r="J352" t="str">
+        <v>2026-04-10T05:40:28.288Z</v>
+      </c>
+      <c r="K352" t="str">
+        <v/>
+      </c>
+      <c r="L352" t="str">
+        <v/>
+      </c>
+      <c r="M352" t="str">
+        <v/>
+      </c>
+      <c r="N352" t="str">
+        <v/>
+      </c>
+      <c r="O352" t="str">
+        <v/>
+      </c>
+      <c r="P352" t="str">
+        <v/>
+      </c>
+      <c r="Q352" t="str">
+        <v/>
+      </c>
+      <c r="R352" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="str">
+        <v>KLD10067</v>
+      </c>
+      <c r="B353" t="str">
         <v>KL1019</v>
       </c>
-      <c r="C305" t="str">
-        <v>ライブインパクト</v>
-      </c>
-      <c r="D305" t="str">
-        <v/>
-      </c>
-      <c r="E305" t="str">
-        <v/>
-      </c>
-      <c r="F305" t="str">
-        <v/>
-      </c>
-      <c r="G305" t="str">
-        <v/>
-      </c>
-      <c r="H305" t="str">
-        <v/>
-      </c>
-      <c r="I305" t="str">
-        <v>2026-04-10T05:01:35.219Z</v>
-      </c>
-      <c r="J305" t="str">
-        <v>2026-04-10T05:01:35.219Z</v>
-      </c>
-      <c r="K305" t="str">
-        <v/>
-      </c>
-      <c r="L305" t="str">
-        <v/>
-      </c>
-      <c r="M305" t="str">
-        <v/>
-      </c>
-      <c r="N305" t="str">
-        <v/>
-      </c>
-      <c r="O305" t="str">
-        <v/>
-      </c>
-      <c r="P305" t="str">
-        <v/>
-      </c>
-      <c r="Q305" t="str">
-        <v/>
-      </c>
-      <c r="R305" t="str">
-        <v/>
+      <c r="C353" t="str">
+        <v>2.5"</v>
+      </c>
+      <c r="D353" t="str">
+        <v/>
+      </c>
+      <c r="E353" t="str">
+        <v/>
+      </c>
+      <c r="F353" t="str">
+        <v>2.5"</v>
+      </c>
+      <c r="G353" t="str">
+        <v/>
+      </c>
+      <c r="H353" t="str">
+        <v/>
+      </c>
+      <c r="I353" t="str">
+        <v>2026-04-10T05:40:33.878Z</v>
+      </c>
+      <c r="J353" t="str">
+        <v>2026-04-10T05:40:33.878Z</v>
+      </c>
+      <c r="K353" t="str">
+        <v/>
+      </c>
+      <c r="L353" t="str">
+        <v/>
+      </c>
+      <c r="M353" t="str">
+        <v/>
+      </c>
+      <c r="N353" t="str">
+        <v/>
+      </c>
+      <c r="O353" t="str">
+        <v/>
+      </c>
+      <c r="P353" t="str">
+        <v/>
+      </c>
+      <c r="Q353" t="str">
+        <v/>
+      </c>
+      <c r="R353" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="str">
+        <v>KLD10068</v>
+      </c>
+      <c r="B354" t="str">
+        <v>KL1019</v>
+      </c>
+      <c r="C354" t="str">
+        <v>3"</v>
+      </c>
+      <c r="D354" t="str">
+        <v/>
+      </c>
+      <c r="E354" t="str">
+        <v/>
+      </c>
+      <c r="F354" t="str">
+        <v>3"</v>
+      </c>
+      <c r="G354" t="str">
+        <v/>
+      </c>
+      <c r="H354" t="str">
+        <v/>
+      </c>
+      <c r="I354" t="str">
+        <v>2026-04-10T05:40:33.878Z</v>
+      </c>
+      <c r="J354" t="str">
+        <v>2026-04-10T05:40:33.878Z</v>
+      </c>
+      <c r="K354" t="str">
+        <v/>
+      </c>
+      <c r="L354" t="str">
+        <v/>
+      </c>
+      <c r="M354" t="str">
+        <v/>
+      </c>
+      <c r="N354" t="str">
+        <v/>
+      </c>
+      <c r="O354" t="str">
+        <v/>
+      </c>
+      <c r="P354" t="str">
+        <v/>
+      </c>
+      <c r="Q354" t="str">
+        <v/>
+      </c>
+      <c r="R354" t="str">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="str">
+        <v>KLD10069</v>
+      </c>
+      <c r="B355" t="str">
+        <v>KL1019</v>
+      </c>
+      <c r="C355" t="str">
+        <v>4"</v>
+      </c>
+      <c r="D355" t="str">
+        <v/>
+      </c>
+      <c r="E355" t="str">
+        <v/>
+      </c>
+      <c r="F355" t="str">
+        <v>4"</v>
+      </c>
+      <c r="G355" t="str">
+        <v/>
+      </c>
+      <c r="H355" t="str">
+        <v/>
+      </c>
+      <c r="I355" t="str">
+        <v>2026-04-10T05:40:33.878Z</v>
+      </c>
+      <c r="J355" t="str">
+        <v>2026-04-10T05:40:33.878Z</v>
+      </c>
+      <c r="K355" t="str">
+        <v/>
+      </c>
+      <c r="L355" t="str">
+        <v/>
+      </c>
+      <c r="M355" t="str">
+        <v/>
+      </c>
+      <c r="N355" t="str">
+        <v/>
+      </c>
+      <c r="O355" t="str">
+        <v/>
+      </c>
+      <c r="P355" t="str">
+        <v/>
+      </c>
+      <c r="Q355" t="str">
+        <v/>
+      </c>
+      <c r="R355" t="str">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R305"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R355"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/GearSage-client/rate/excel/soft_lure_detail.xlsx
+++ b/GearSage-client/rate/excel/soft_lure_detail.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R355"/>
+  <dimension ref="A1:AA409"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -454,6 +454,33 @@
       <c r="R1" t="str">
         <v>quantity (入数)</v>
       </c>
+      <c r="S1" t="str">
+        <v>Size</v>
+      </c>
+      <c r="T1" t="str">
+        <v>Market Reference Price</v>
+      </c>
+      <c r="U1" t="str">
+        <v>Quantity</v>
+      </c>
+      <c r="V1" t="str">
+        <v>Hook</v>
+      </c>
+      <c r="W1" t="str">
+        <v>Hook Size</v>
+      </c>
+      <c r="X1" t="str">
+        <v>Ring Size</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>Material</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>Sale Price</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>Description</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -20279,9 +20306,4491 @@
         <v>10</v>
       </c>
     </row>
+    <row r="356">
+      <c r="A356" t="str">
+        <v>YAM001D001</v>
+      </c>
+      <c r="B356" t="str">
+        <v>YAM001</v>
+      </c>
+      <c r="C356" t="str">
+        <v>YAM-9SFUZ-5-297</v>
+      </c>
+      <c r="D356" t="str">
+        <v/>
+      </c>
+      <c r="E356" t="str">
+        <v/>
+      </c>
+      <c r="F356" t="str">
+        <v/>
+      </c>
+      <c r="G356" t="str">
+        <v/>
+      </c>
+      <c r="H356" t="str">
+        <v/>
+      </c>
+      <c r="I356" t="str">
+        <v>2026-04-10T10:18:14.137Z</v>
+      </c>
+      <c r="J356" t="str">
+        <v>2026-04-10T10:18:14.137Z</v>
+      </c>
+      <c r="K356" t="str">
+        <v/>
+      </c>
+      <c r="L356" t="str">
+        <v/>
+      </c>
+      <c r="M356" t="str">
+        <v/>
+      </c>
+      <c r="N356" t="str">
+        <v/>
+      </c>
+      <c r="O356" t="str">
+        <v/>
+      </c>
+      <c r="P356" t="str">
+        <v/>
+      </c>
+      <c r="Q356" t="str">
+        <v/>
+      </c>
+      <c r="R356" t="str">
+        <v/>
+      </c>
+      <c r="S356" t="str">
+        <v>4</v>
+      </c>
+      <c r="T356">
+        <v>9.99</v>
+      </c>
+      <c r="U356" t="str">
+        <v>5</v>
+      </c>
+      <c r="V356" t="str">
+        <v/>
+      </c>
+      <c r="W356" t="str">
+        <v/>
+      </c>
+      <c r="X356" t="str">
+        <v/>
+      </c>
+      <c r="Y356" t="str">
+        <v/>
+      </c>
+      <c r="Z356" t="str">
+        <v/>
+      </c>
+      <c r="AA356" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="str">
+        <v>YAM001D002</v>
+      </c>
+      <c r="B357" t="str">
+        <v>YAM001</v>
+      </c>
+      <c r="C357" t="str">
+        <v>YAM-9FUZ-4-297</v>
+      </c>
+      <c r="D357" t="str">
+        <v/>
+      </c>
+      <c r="E357" t="str">
+        <v/>
+      </c>
+      <c r="F357" t="str">
+        <v/>
+      </c>
+      <c r="G357" t="str">
+        <v/>
+      </c>
+      <c r="H357" t="str">
+        <v/>
+      </c>
+      <c r="I357" t="str">
+        <v>2026-04-10T10:18:14.137Z</v>
+      </c>
+      <c r="J357" t="str">
+        <v>2026-04-10T10:18:14.137Z</v>
+      </c>
+      <c r="K357" t="str">
+        <v/>
+      </c>
+      <c r="L357" t="str">
+        <v/>
+      </c>
+      <c r="M357" t="str">
+        <v/>
+      </c>
+      <c r="N357" t="str">
+        <v/>
+      </c>
+      <c r="O357" t="str">
+        <v/>
+      </c>
+      <c r="P357" t="str">
+        <v/>
+      </c>
+      <c r="Q357" t="str">
+        <v/>
+      </c>
+      <c r="R357" t="str">
+        <v/>
+      </c>
+      <c r="S357" t="str">
+        <v>5</v>
+      </c>
+      <c r="T357">
+        <v>9.99</v>
+      </c>
+      <c r="U357" t="str">
+        <v>4</v>
+      </c>
+      <c r="V357" t="str">
+        <v/>
+      </c>
+      <c r="W357" t="str">
+        <v/>
+      </c>
+      <c r="X357" t="str">
+        <v/>
+      </c>
+      <c r="Y357" t="str">
+        <v/>
+      </c>
+      <c r="Z357" t="str">
+        <v/>
+      </c>
+      <c r="AA357" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="str">
+        <v>YAM002D001</v>
+      </c>
+      <c r="B358" t="str">
+        <v>YAM002</v>
+      </c>
+      <c r="C358" t="str">
+        <v>YAM-FUZNUKI25-5-297</v>
+      </c>
+      <c r="D358" t="str">
+        <v/>
+      </c>
+      <c r="E358" t="str">
+        <v/>
+      </c>
+      <c r="F358" t="str">
+        <v/>
+      </c>
+      <c r="G358" t="str">
+        <v/>
+      </c>
+      <c r="H358" t="str">
+        <v/>
+      </c>
+      <c r="I358" t="str">
+        <v>2026-04-10T10:18:16.243Z</v>
+      </c>
+      <c r="J358" t="str">
+        <v>2026-04-10T10:18:16.243Z</v>
+      </c>
+      <c r="K358" t="str">
+        <v/>
+      </c>
+      <c r="L358" t="str">
+        <v/>
+      </c>
+      <c r="M358" t="str">
+        <v/>
+      </c>
+      <c r="N358" t="str">
+        <v/>
+      </c>
+      <c r="O358" t="str">
+        <v/>
+      </c>
+      <c r="P358" t="str">
+        <v/>
+      </c>
+      <c r="Q358" t="str">
+        <v/>
+      </c>
+      <c r="R358" t="str">
+        <v/>
+      </c>
+      <c r="S358" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="T358">
+        <v>9.99</v>
+      </c>
+      <c r="U358" t="str">
+        <v>5</v>
+      </c>
+      <c r="V358" t="str">
+        <v/>
+      </c>
+      <c r="W358" t="str">
+        <v/>
+      </c>
+      <c r="X358" t="str">
+        <v/>
+      </c>
+      <c r="Y358" t="str">
+        <v/>
+      </c>
+      <c r="Z358" t="str">
+        <v/>
+      </c>
+      <c r="AA358" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="str">
+        <v>YAM002D002</v>
+      </c>
+      <c r="B359" t="str">
+        <v>YAM002</v>
+      </c>
+      <c r="C359" t="str">
+        <v>YAM-FUZNUKI35-4-297</v>
+      </c>
+      <c r="D359" t="str">
+        <v/>
+      </c>
+      <c r="E359" t="str">
+        <v/>
+      </c>
+      <c r="F359" t="str">
+        <v/>
+      </c>
+      <c r="G359" t="str">
+        <v/>
+      </c>
+      <c r="H359" t="str">
+        <v/>
+      </c>
+      <c r="I359" t="str">
+        <v>2026-04-10T10:18:16.243Z</v>
+      </c>
+      <c r="J359" t="str">
+        <v>2026-04-10T10:18:16.243Z</v>
+      </c>
+      <c r="K359" t="str">
+        <v/>
+      </c>
+      <c r="L359" t="str">
+        <v/>
+      </c>
+      <c r="M359" t="str">
+        <v/>
+      </c>
+      <c r="N359" t="str">
+        <v/>
+      </c>
+      <c r="O359" t="str">
+        <v/>
+      </c>
+      <c r="P359" t="str">
+        <v/>
+      </c>
+      <c r="Q359" t="str">
+        <v/>
+      </c>
+      <c r="R359" t="str">
+        <v/>
+      </c>
+      <c r="S359" t="str">
+        <v>3.5</v>
+      </c>
+      <c r="T359">
+        <v>9.99</v>
+      </c>
+      <c r="U359" t="str">
+        <v>4</v>
+      </c>
+      <c r="V359" t="str">
+        <v/>
+      </c>
+      <c r="W359" t="str">
+        <v/>
+      </c>
+      <c r="X359" t="str">
+        <v/>
+      </c>
+      <c r="Y359" t="str">
+        <v/>
+      </c>
+      <c r="Z359" t="str">
+        <v/>
+      </c>
+      <c r="AA359" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="str">
+        <v>YAM003D001</v>
+      </c>
+      <c r="B360" t="str">
+        <v>YAM003</v>
+      </c>
+      <c r="C360" t="str">
+        <v>YAM-FUZNUT-6-297</v>
+      </c>
+      <c r="D360" t="str">
+        <v/>
+      </c>
+      <c r="E360" t="str">
+        <v/>
+      </c>
+      <c r="F360" t="str">
+        <v/>
+      </c>
+      <c r="G360" t="str">
+        <v/>
+      </c>
+      <c r="H360" t="str">
+        <v/>
+      </c>
+      <c r="I360" t="str">
+        <v>2026-04-10T10:18:18.376Z</v>
+      </c>
+      <c r="J360" t="str">
+        <v>2026-04-10T10:18:18.376Z</v>
+      </c>
+      <c r="K360" t="str">
+        <v/>
+      </c>
+      <c r="L360" t="str">
+        <v/>
+      </c>
+      <c r="M360" t="str">
+        <v/>
+      </c>
+      <c r="N360" t="str">
+        <v/>
+      </c>
+      <c r="O360" t="str">
+        <v/>
+      </c>
+      <c r="P360" t="str">
+        <v/>
+      </c>
+      <c r="Q360" t="str">
+        <v/>
+      </c>
+      <c r="R360" t="str">
+        <v/>
+      </c>
+      <c r="S360" t="str">
+        <v/>
+      </c>
+      <c r="T360">
+        <v>9.99</v>
+      </c>
+      <c r="U360" t="str">
+        <v>6</v>
+      </c>
+      <c r="V360" t="str">
+        <v/>
+      </c>
+      <c r="W360" t="str">
+        <v/>
+      </c>
+      <c r="X360" t="str">
+        <v/>
+      </c>
+      <c r="Y360" t="str">
+        <v/>
+      </c>
+      <c r="Z360" t="str">
+        <v/>
+      </c>
+      <c r="AA360" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="str">
+        <v>YAM004D001</v>
+      </c>
+      <c r="B361" t="str">
+        <v>YAM004</v>
+      </c>
+      <c r="C361" t="str">
+        <v>YAM004D001</v>
+      </c>
+      <c r="D361" t="str">
+        <v/>
+      </c>
+      <c r="E361" t="str">
+        <v/>
+      </c>
+      <c r="F361" t="str">
+        <v/>
+      </c>
+      <c r="G361" t="str">
+        <v/>
+      </c>
+      <c r="H361" t="str">
+        <v/>
+      </c>
+      <c r="I361" t="str">
+        <v>2026-04-10T10:18:20.464Z</v>
+      </c>
+      <c r="J361" t="str">
+        <v>2026-04-10T10:18:20.464Z</v>
+      </c>
+      <c r="K361" t="str">
+        <v/>
+      </c>
+      <c r="L361" t="str">
+        <v/>
+      </c>
+      <c r="M361" t="str">
+        <v/>
+      </c>
+      <c r="N361" t="str">
+        <v/>
+      </c>
+      <c r="O361" t="str">
+        <v/>
+      </c>
+      <c r="P361" t="str">
+        <v/>
+      </c>
+      <c r="Q361" t="str">
+        <v/>
+      </c>
+      <c r="R361" t="str">
+        <v/>
+      </c>
+      <c r="S361" t="str">
+        <v/>
+      </c>
+      <c r="T361" t="str">
+        <v>17.997.999.997.99</v>
+      </c>
+      <c r="U361" t="str">
+        <v/>
+      </c>
+      <c r="V361" t="str">
+        <v/>
+      </c>
+      <c r="W361" t="str">
+        <v/>
+      </c>
+      <c r="X361" t="str">
+        <v/>
+      </c>
+      <c r="Y361" t="str">
+        <v/>
+      </c>
+      <c r="Z361" t="str">
+        <v/>
+      </c>
+      <c r="AA361" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="str">
+        <v>YAM005D001</v>
+      </c>
+      <c r="B362" t="str">
+        <v>YAM005</v>
+      </c>
+      <c r="C362" t="str">
+        <v>SENKO5</v>
+      </c>
+      <c r="D362" t="str">
+        <v/>
+      </c>
+      <c r="E362" t="str">
+        <v/>
+      </c>
+      <c r="F362" t="str">
+        <v/>
+      </c>
+      <c r="G362" t="str">
+        <v/>
+      </c>
+      <c r="H362" t="str">
+        <v/>
+      </c>
+      <c r="I362" t="str">
+        <v>2026-04-10T10:18:23.621Z</v>
+      </c>
+      <c r="J362" t="str">
+        <v>2026-04-10T10:18:23.621Z</v>
+      </c>
+      <c r="K362" t="str">
+        <v/>
+      </c>
+      <c r="L362" t="str">
+        <v/>
+      </c>
+      <c r="M362" t="str">
+        <v/>
+      </c>
+      <c r="N362" t="str">
+        <v/>
+      </c>
+      <c r="O362" t="str">
+        <v/>
+      </c>
+      <c r="P362" t="str">
+        <v/>
+      </c>
+      <c r="Q362" t="str">
+        <v/>
+      </c>
+      <c r="R362" t="str">
+        <v/>
+      </c>
+      <c r="S362" t="str">
+        <v/>
+      </c>
+      <c r="T362">
+        <v>87.99</v>
+      </c>
+      <c r="U362" t="str">
+        <v>100</v>
+      </c>
+      <c r="V362" t="str">
+        <v/>
+      </c>
+      <c r="W362" t="str">
+        <v/>
+      </c>
+      <c r="X362" t="str">
+        <v/>
+      </c>
+      <c r="Y362" t="str">
+        <v/>
+      </c>
+      <c r="Z362" t="str">
+        <v/>
+      </c>
+      <c r="AA362" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="str">
+        <v>YAM006D001</v>
+      </c>
+      <c r="B363" t="str">
+        <v>YAM006</v>
+      </c>
+      <c r="C363" t="str">
+        <v>SENKO4</v>
+      </c>
+      <c r="D363" t="str">
+        <v/>
+      </c>
+      <c r="E363" t="str">
+        <v/>
+      </c>
+      <c r="F363" t="str">
+        <v/>
+      </c>
+      <c r="G363" t="str">
+        <v/>
+      </c>
+      <c r="H363" t="str">
+        <v/>
+      </c>
+      <c r="I363" t="str">
+        <v>2026-04-10T10:18:25.835Z</v>
+      </c>
+      <c r="J363" t="str">
+        <v>2026-04-10T10:18:25.835Z</v>
+      </c>
+      <c r="K363" t="str">
+        <v/>
+      </c>
+      <c r="L363" t="str">
+        <v/>
+      </c>
+      <c r="M363" t="str">
+        <v/>
+      </c>
+      <c r="N363" t="str">
+        <v/>
+      </c>
+      <c r="O363" t="str">
+        <v/>
+      </c>
+      <c r="P363" t="str">
+        <v/>
+      </c>
+      <c r="Q363" t="str">
+        <v/>
+      </c>
+      <c r="R363" t="str">
+        <v/>
+      </c>
+      <c r="S363" t="str">
+        <v/>
+      </c>
+      <c r="T363">
+        <v>114.99</v>
+      </c>
+      <c r="U363" t="str">
+        <v>160</v>
+      </c>
+      <c r="V363" t="str">
+        <v/>
+      </c>
+      <c r="W363" t="str">
+        <v/>
+      </c>
+      <c r="X363" t="str">
+        <v/>
+      </c>
+      <c r="Y363" t="str">
+        <v/>
+      </c>
+      <c r="Z363" t="str">
+        <v/>
+      </c>
+      <c r="AA363" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="str">
+        <v>YAM007D001</v>
+      </c>
+      <c r="B364" t="str">
+        <v>YAM007</v>
+      </c>
+      <c r="C364" t="str">
+        <v>YAM-SENKO3</v>
+      </c>
+      <c r="D364" t="str">
+        <v/>
+      </c>
+      <c r="E364" t="str">
+        <v/>
+      </c>
+      <c r="F364" t="str">
+        <v/>
+      </c>
+      <c r="G364" t="str">
+        <v/>
+      </c>
+      <c r="H364" t="str">
+        <v/>
+      </c>
+      <c r="I364" t="str">
+        <v>2026-04-10T10:18:27.985Z</v>
+      </c>
+      <c r="J364" t="str">
+        <v>2026-04-10T10:18:27.985Z</v>
+      </c>
+      <c r="K364" t="str">
+        <v/>
+      </c>
+      <c r="L364" t="str">
+        <v/>
+      </c>
+      <c r="M364" t="str">
+        <v/>
+      </c>
+      <c r="N364" t="str">
+        <v/>
+      </c>
+      <c r="O364" t="str">
+        <v/>
+      </c>
+      <c r="P364" t="str">
+        <v/>
+      </c>
+      <c r="Q364" t="str">
+        <v/>
+      </c>
+      <c r="R364" t="str">
+        <v/>
+      </c>
+      <c r="S364" t="str">
+        <v/>
+      </c>
+      <c r="T364">
+        <v>35.99</v>
+      </c>
+      <c r="U364" t="str">
+        <v>50</v>
+      </c>
+      <c r="V364" t="str">
+        <v/>
+      </c>
+      <c r="W364" t="str">
+        <v/>
+      </c>
+      <c r="X364" t="str">
+        <v/>
+      </c>
+      <c r="Y364" t="str">
+        <v/>
+      </c>
+      <c r="Z364" t="str">
+        <v/>
+      </c>
+      <c r="AA364" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="str">
+        <v>YAM008D001</v>
+      </c>
+      <c r="B365" t="str">
+        <v>YAM008</v>
+      </c>
+      <c r="C365" t="str">
+        <v>YAM-SENKO2</v>
+      </c>
+      <c r="D365" t="str">
+        <v/>
+      </c>
+      <c r="E365" t="str">
+        <v/>
+      </c>
+      <c r="F365" t="str">
+        <v/>
+      </c>
+      <c r="G365" t="str">
+        <v/>
+      </c>
+      <c r="H365" t="str">
+        <v/>
+      </c>
+      <c r="I365" t="str">
+        <v>2026-04-10T10:18:30.130Z</v>
+      </c>
+      <c r="J365" t="str">
+        <v>2026-04-10T10:18:30.130Z</v>
+      </c>
+      <c r="K365" t="str">
+        <v/>
+      </c>
+      <c r="L365" t="str">
+        <v/>
+      </c>
+      <c r="M365" t="str">
+        <v/>
+      </c>
+      <c r="N365" t="str">
+        <v/>
+      </c>
+      <c r="O365" t="str">
+        <v/>
+      </c>
+      <c r="P365" t="str">
+        <v/>
+      </c>
+      <c r="Q365" t="str">
+        <v/>
+      </c>
+      <c r="R365" t="str">
+        <v/>
+      </c>
+      <c r="S365" t="str">
+        <v/>
+      </c>
+      <c r="T365">
+        <v>35.99</v>
+      </c>
+      <c r="U365" t="str">
+        <v>50</v>
+      </c>
+      <c r="V365" t="str">
+        <v/>
+      </c>
+      <c r="W365" t="str">
+        <v/>
+      </c>
+      <c r="X365" t="str">
+        <v/>
+      </c>
+      <c r="Y365" t="str">
+        <v/>
+      </c>
+      <c r="Z365" t="str">
+        <v/>
+      </c>
+      <c r="AA365" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="str">
+        <v>YAM009D001</v>
+      </c>
+      <c r="B366" t="str">
+        <v>YAM009</v>
+      </c>
+      <c r="C366" t="str">
+        <v>YAM-SENKO1</v>
+      </c>
+      <c r="D366" t="str">
+        <v/>
+      </c>
+      <c r="E366" t="str">
+        <v/>
+      </c>
+      <c r="F366" t="str">
+        <v/>
+      </c>
+      <c r="G366" t="str">
+        <v/>
+      </c>
+      <c r="H366" t="str">
+        <v/>
+      </c>
+      <c r="I366" t="str">
+        <v>2026-04-10T10:18:33.272Z</v>
+      </c>
+      <c r="J366" t="str">
+        <v>2026-04-10T10:18:33.272Z</v>
+      </c>
+      <c r="K366" t="str">
+        <v/>
+      </c>
+      <c r="L366" t="str">
+        <v/>
+      </c>
+      <c r="M366" t="str">
+        <v/>
+      </c>
+      <c r="N366" t="str">
+        <v/>
+      </c>
+      <c r="O366" t="str">
+        <v/>
+      </c>
+      <c r="P366" t="str">
+        <v/>
+      </c>
+      <c r="Q366" t="str">
+        <v/>
+      </c>
+      <c r="R366" t="str">
+        <v/>
+      </c>
+      <c r="S366" t="str">
+        <v/>
+      </c>
+      <c r="T366">
+        <v>64.99</v>
+      </c>
+      <c r="U366" t="str">
+        <v>90</v>
+      </c>
+      <c r="V366" t="str">
+        <v/>
+      </c>
+      <c r="W366" t="str">
+        <v/>
+      </c>
+      <c r="X366" t="str">
+        <v/>
+      </c>
+      <c r="Y366" t="str">
+        <v/>
+      </c>
+      <c r="Z366" t="str">
+        <v/>
+      </c>
+      <c r="AA366" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="str">
+        <v>YAM010D001</v>
+      </c>
+      <c r="B367" t="str">
+        <v>YAM010</v>
+      </c>
+      <c r="C367" t="str">
+        <v>YAM-9C-10-020</v>
+      </c>
+      <c r="D367" t="str">
+        <v/>
+      </c>
+      <c r="E367" t="str">
+        <v/>
+      </c>
+      <c r="F367" t="str">
+        <v/>
+      </c>
+      <c r="G367" t="str">
+        <v/>
+      </c>
+      <c r="H367" t="str">
+        <v/>
+      </c>
+      <c r="I367" t="str">
+        <v>2026-04-10T10:18:35.432Z</v>
+      </c>
+      <c r="J367" t="str">
+        <v>2026-04-10T10:18:35.432Z</v>
+      </c>
+      <c r="K367" t="str">
+        <v/>
+      </c>
+      <c r="L367" t="str">
+        <v/>
+      </c>
+      <c r="M367" t="str">
+        <v/>
+      </c>
+      <c r="N367" t="str">
+        <v/>
+      </c>
+      <c r="O367" t="str">
+        <v/>
+      </c>
+      <c r="P367" t="str">
+        <v/>
+      </c>
+      <c r="Q367" t="str">
+        <v/>
+      </c>
+      <c r="R367" t="str">
+        <v/>
+      </c>
+      <c r="S367" t="str">
+        <v/>
+      </c>
+      <c r="T367">
+        <v>6.99</v>
+      </c>
+      <c r="U367" t="str">
+        <v>10</v>
+      </c>
+      <c r="V367" t="str">
+        <v/>
+      </c>
+      <c r="W367" t="str">
+        <v/>
+      </c>
+      <c r="X367" t="str">
+        <v/>
+      </c>
+      <c r="Y367" t="str">
+        <v/>
+      </c>
+      <c r="Z367" t="str">
+        <v/>
+      </c>
+      <c r="AA367" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="str">
+        <v>YAM011D001</v>
+      </c>
+      <c r="B368" t="str">
+        <v>YAM011</v>
+      </c>
+      <c r="C368" t="str">
+        <v>YAM-31-10-020</v>
+      </c>
+      <c r="D368" t="str">
+        <v/>
+      </c>
+      <c r="E368" t="str">
+        <v/>
+      </c>
+      <c r="F368" t="str">
+        <v/>
+      </c>
+      <c r="G368" t="str">
+        <v/>
+      </c>
+      <c r="H368" t="str">
+        <v/>
+      </c>
+      <c r="I368" t="str">
+        <v>2026-04-10T10:18:36.702Z</v>
+      </c>
+      <c r="J368" t="str">
+        <v>2026-04-10T10:18:36.702Z</v>
+      </c>
+      <c r="K368" t="str">
+        <v/>
+      </c>
+      <c r="L368" t="str">
+        <v/>
+      </c>
+      <c r="M368" t="str">
+        <v/>
+      </c>
+      <c r="N368" t="str">
+        <v/>
+      </c>
+      <c r="O368" t="str">
+        <v/>
+      </c>
+      <c r="P368" t="str">
+        <v/>
+      </c>
+      <c r="Q368" t="str">
+        <v/>
+      </c>
+      <c r="R368" t="str">
+        <v/>
+      </c>
+      <c r="S368" t="str">
+        <v/>
+      </c>
+      <c r="T368">
+        <v>8.99</v>
+      </c>
+      <c r="U368" t="str">
+        <v/>
+      </c>
+      <c r="V368" t="str">
+        <v/>
+      </c>
+      <c r="W368" t="str">
+        <v/>
+      </c>
+      <c r="X368" t="str">
+        <v/>
+      </c>
+      <c r="Y368" t="str">
+        <v/>
+      </c>
+      <c r="Z368" t="str">
+        <v/>
+      </c>
+      <c r="AA368" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="str">
+        <v>YAM012D001</v>
+      </c>
+      <c r="B369" t="str">
+        <v>YAM012</v>
+      </c>
+      <c r="C369" t="str">
+        <v>YAM-9-50-021</v>
+      </c>
+      <c r="D369" t="str">
+        <v/>
+      </c>
+      <c r="E369" t="str">
+        <v/>
+      </c>
+      <c r="F369" t="str">
+        <v/>
+      </c>
+      <c r="G369" t="str">
+        <v/>
+      </c>
+      <c r="H369" t="str">
+        <v/>
+      </c>
+      <c r="I369" t="str">
+        <v>2026-04-10T10:18:38.783Z</v>
+      </c>
+      <c r="J369" t="str">
+        <v>2026-04-10T10:18:38.783Z</v>
+      </c>
+      <c r="K369" t="str">
+        <v/>
+      </c>
+      <c r="L369" t="str">
+        <v/>
+      </c>
+      <c r="M369" t="str">
+        <v/>
+      </c>
+      <c r="N369" t="str">
+        <v/>
+      </c>
+      <c r="O369" t="str">
+        <v/>
+      </c>
+      <c r="P369" t="str">
+        <v/>
+      </c>
+      <c r="Q369" t="str">
+        <v/>
+      </c>
+      <c r="R369" t="str">
+        <v/>
+      </c>
+      <c r="S369" t="str">
+        <v/>
+      </c>
+      <c r="T369">
+        <v>34.99</v>
+      </c>
+      <c r="U369" t="str">
+        <v/>
+      </c>
+      <c r="V369" t="str">
+        <v/>
+      </c>
+      <c r="W369" t="str">
+        <v/>
+      </c>
+      <c r="X369" t="str">
+        <v/>
+      </c>
+      <c r="Y369" t="str">
+        <v/>
+      </c>
+      <c r="Z369" t="str">
+        <v/>
+      </c>
+      <c r="AA369" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="str">
+        <v>YAM013D001</v>
+      </c>
+      <c r="B370" t="str">
+        <v>YAM013</v>
+      </c>
+      <c r="C370" t="str">
+        <v>YAM-39-MEGA</v>
+      </c>
+      <c r="D370" t="str">
+        <v/>
+      </c>
+      <c r="E370" t="str">
+        <v/>
+      </c>
+      <c r="F370" t="str">
+        <v/>
+      </c>
+      <c r="G370" t="str">
+        <v/>
+      </c>
+      <c r="H370" t="str">
+        <v/>
+      </c>
+      <c r="I370" t="str">
+        <v>2026-04-10T10:18:40.908Z</v>
+      </c>
+      <c r="J370" t="str">
+        <v>2026-04-10T10:18:40.908Z</v>
+      </c>
+      <c r="K370" t="str">
+        <v/>
+      </c>
+      <c r="L370" t="str">
+        <v/>
+      </c>
+      <c r="M370" t="str">
+        <v/>
+      </c>
+      <c r="N370" t="str">
+        <v/>
+      </c>
+      <c r="O370" t="str">
+        <v/>
+      </c>
+      <c r="P370" t="str">
+        <v/>
+      </c>
+      <c r="Q370" t="str">
+        <v/>
+      </c>
+      <c r="R370" t="str">
+        <v/>
+      </c>
+      <c r="S370" t="str">
+        <v/>
+      </c>
+      <c r="T370">
+        <v>16.99</v>
+      </c>
+      <c r="U370" t="str">
+        <v/>
+      </c>
+      <c r="V370" t="str">
+        <v/>
+      </c>
+      <c r="W370" t="str">
+        <v/>
+      </c>
+      <c r="X370" t="str">
+        <v/>
+      </c>
+      <c r="Y370" t="str">
+        <v/>
+      </c>
+      <c r="Z370" t="str">
+        <v/>
+      </c>
+      <c r="AA370" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="str">
+        <v>YAM014D001</v>
+      </c>
+      <c r="B371" t="str">
+        <v>YAM014</v>
+      </c>
+      <c r="C371" t="str">
+        <v>YAM-SPSEN7-021</v>
+      </c>
+      <c r="D371" t="str">
+        <v/>
+      </c>
+      <c r="E371" t="str">
+        <v/>
+      </c>
+      <c r="F371" t="str">
+        <v/>
+      </c>
+      <c r="G371" t="str">
+        <v/>
+      </c>
+      <c r="H371" t="str">
+        <v/>
+      </c>
+      <c r="I371" t="str">
+        <v>2026-04-10T10:18:43.146Z</v>
+      </c>
+      <c r="J371" t="str">
+        <v>2026-04-10T10:18:43.146Z</v>
+      </c>
+      <c r="K371" t="str">
+        <v/>
+      </c>
+      <c r="L371" t="str">
+        <v/>
+      </c>
+      <c r="M371" t="str">
+        <v/>
+      </c>
+      <c r="N371" t="str">
+        <v/>
+      </c>
+      <c r="O371" t="str">
+        <v/>
+      </c>
+      <c r="P371" t="str">
+        <v/>
+      </c>
+      <c r="Q371" t="str">
+        <v/>
+      </c>
+      <c r="R371" t="str">
+        <v/>
+      </c>
+      <c r="S371" t="str">
+        <v/>
+      </c>
+      <c r="T371">
+        <v>7.99</v>
+      </c>
+      <c r="U371" t="str">
+        <v>7</v>
+      </c>
+      <c r="V371" t="str">
+        <v/>
+      </c>
+      <c r="W371" t="str">
+        <v/>
+      </c>
+      <c r="X371" t="str">
+        <v/>
+      </c>
+      <c r="Y371" t="str">
+        <v/>
+      </c>
+      <c r="Z371" t="str">
+        <v/>
+      </c>
+      <c r="AA371" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="str">
+        <v>YAM015D001</v>
+      </c>
+      <c r="B372" t="str">
+        <v>YAM015</v>
+      </c>
+      <c r="C372" t="str">
+        <v>YAM-9N3-10-021</v>
+      </c>
+      <c r="D372" t="str">
+        <v/>
+      </c>
+      <c r="E372" t="str">
+        <v/>
+      </c>
+      <c r="F372" t="str">
+        <v/>
+      </c>
+      <c r="G372" t="str">
+        <v/>
+      </c>
+      <c r="H372" t="str">
+        <v/>
+      </c>
+      <c r="I372" t="str">
+        <v>2026-04-10T10:18:45.238Z</v>
+      </c>
+      <c r="J372" t="str">
+        <v>2026-04-10T10:18:45.238Z</v>
+      </c>
+      <c r="K372" t="str">
+        <v/>
+      </c>
+      <c r="L372" t="str">
+        <v/>
+      </c>
+      <c r="M372" t="str">
+        <v/>
+      </c>
+      <c r="N372" t="str">
+        <v/>
+      </c>
+      <c r="O372" t="str">
+        <v/>
+      </c>
+      <c r="P372" t="str">
+        <v/>
+      </c>
+      <c r="Q372" t="str">
+        <v/>
+      </c>
+      <c r="R372" t="str">
+        <v/>
+      </c>
+      <c r="S372" t="str">
+        <v/>
+      </c>
+      <c r="T372">
+        <v>5.99</v>
+      </c>
+      <c r="U372" t="str">
+        <v>10</v>
+      </c>
+      <c r="V372" t="str">
+        <v/>
+      </c>
+      <c r="W372" t="str">
+        <v/>
+      </c>
+      <c r="X372" t="str">
+        <v/>
+      </c>
+      <c r="Y372" t="str">
+        <v/>
+      </c>
+      <c r="Z372" t="str">
+        <v/>
+      </c>
+      <c r="AA372" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="str">
+        <v>YAM016D001</v>
+      </c>
+      <c r="B373" t="str">
+        <v>YAM016</v>
+      </c>
+      <c r="C373" t="str">
+        <v>YAM-9B-10-009</v>
+      </c>
+      <c r="D373" t="str">
+        <v/>
+      </c>
+      <c r="E373" t="str">
+        <v/>
+      </c>
+      <c r="F373" t="str">
+        <v/>
+      </c>
+      <c r="G373" t="str">
+        <v/>
+      </c>
+      <c r="H373" t="str">
+        <v/>
+      </c>
+      <c r="I373" t="str">
+        <v>2026-04-10T10:18:47.330Z</v>
+      </c>
+      <c r="J373" t="str">
+        <v>2026-04-10T10:18:47.330Z</v>
+      </c>
+      <c r="K373" t="str">
+        <v/>
+      </c>
+      <c r="L373" t="str">
+        <v/>
+      </c>
+      <c r="M373" t="str">
+        <v/>
+      </c>
+      <c r="N373" t="str">
+        <v/>
+      </c>
+      <c r="O373" t="str">
+        <v/>
+      </c>
+      <c r="P373" t="str">
+        <v/>
+      </c>
+      <c r="Q373" t="str">
+        <v/>
+      </c>
+      <c r="R373" t="str">
+        <v/>
+      </c>
+      <c r="S373" t="str">
+        <v/>
+      </c>
+      <c r="T373">
+        <v>5.99</v>
+      </c>
+      <c r="U373" t="str">
+        <v>10</v>
+      </c>
+      <c r="V373" t="str">
+        <v/>
+      </c>
+      <c r="W373" t="str">
+        <v/>
+      </c>
+      <c r="X373" t="str">
+        <v/>
+      </c>
+      <c r="Y373" t="str">
+        <v/>
+      </c>
+      <c r="Z373" t="str">
+        <v/>
+      </c>
+      <c r="AA373" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="str">
+        <v>YAM017D001</v>
+      </c>
+      <c r="B374" t="str">
+        <v>YAM017</v>
+      </c>
+      <c r="C374" t="str">
+        <v>YAM-9P-10-021</v>
+      </c>
+      <c r="D374" t="str">
+        <v/>
+      </c>
+      <c r="E374" t="str">
+        <v/>
+      </c>
+      <c r="F374" t="str">
+        <v/>
+      </c>
+      <c r="G374" t="str">
+        <v/>
+      </c>
+      <c r="H374" t="str">
+        <v/>
+      </c>
+      <c r="I374" t="str">
+        <v>2026-04-10T10:18:49.421Z</v>
+      </c>
+      <c r="J374" t="str">
+        <v>2026-04-10T10:18:49.421Z</v>
+      </c>
+      <c r="K374" t="str">
+        <v/>
+      </c>
+      <c r="L374" t="str">
+        <v/>
+      </c>
+      <c r="M374" t="str">
+        <v/>
+      </c>
+      <c r="N374" t="str">
+        <v/>
+      </c>
+      <c r="O374" t="str">
+        <v/>
+      </c>
+      <c r="P374" t="str">
+        <v/>
+      </c>
+      <c r="Q374" t="str">
+        <v/>
+      </c>
+      <c r="R374" t="str">
+        <v/>
+      </c>
+      <c r="S374" t="str">
+        <v/>
+      </c>
+      <c r="T374">
+        <v>7.99</v>
+      </c>
+      <c r="U374" t="str">
+        <v>10</v>
+      </c>
+      <c r="V374" t="str">
+        <v/>
+      </c>
+      <c r="W374" t="str">
+        <v/>
+      </c>
+      <c r="X374" t="str">
+        <v/>
+      </c>
+      <c r="Y374" t="str">
+        <v/>
+      </c>
+      <c r="Z374" t="str">
+        <v/>
+      </c>
+      <c r="AA374" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="str">
+        <v>YAM018D001</v>
+      </c>
+      <c r="B375" t="str">
+        <v>YAM018</v>
+      </c>
+      <c r="C375" t="str">
+        <v>YAM-9M-10-157</v>
+      </c>
+      <c r="D375" t="str">
+        <v/>
+      </c>
+      <c r="E375" t="str">
+        <v/>
+      </c>
+      <c r="F375" t="str">
+        <v/>
+      </c>
+      <c r="G375" t="str">
+        <v/>
+      </c>
+      <c r="H375" t="str">
+        <v/>
+      </c>
+      <c r="I375" t="str">
+        <v>2026-04-10T10:18:51.127Z</v>
+      </c>
+      <c r="J375" t="str">
+        <v>2026-04-10T10:18:51.127Z</v>
+      </c>
+      <c r="K375" t="str">
+        <v/>
+      </c>
+      <c r="L375" t="str">
+        <v/>
+      </c>
+      <c r="M375" t="str">
+        <v/>
+      </c>
+      <c r="N375" t="str">
+        <v/>
+      </c>
+      <c r="O375" t="str">
+        <v/>
+      </c>
+      <c r="P375" t="str">
+        <v/>
+      </c>
+      <c r="Q375" t="str">
+        <v/>
+      </c>
+      <c r="R375" t="str">
+        <v/>
+      </c>
+      <c r="S375" t="str">
+        <v/>
+      </c>
+      <c r="T375">
+        <v>7.99</v>
+      </c>
+      <c r="U375" t="str">
+        <v>10</v>
+      </c>
+      <c r="V375" t="str">
+        <v/>
+      </c>
+      <c r="W375" t="str">
+        <v/>
+      </c>
+      <c r="X375" t="str">
+        <v/>
+      </c>
+      <c r="Y375" t="str">
+        <v/>
+      </c>
+      <c r="Z375" t="str">
+        <v/>
+      </c>
+      <c r="AA375" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="str">
+        <v>YAM019D001</v>
+      </c>
+      <c r="B376" t="str">
+        <v>YAM019</v>
+      </c>
+      <c r="C376" t="str">
+        <v>YAM-9X-05-021</v>
+      </c>
+      <c r="D376" t="str">
+        <v/>
+      </c>
+      <c r="E376" t="str">
+        <v/>
+      </c>
+      <c r="F376" t="str">
+        <v/>
+      </c>
+      <c r="G376" t="str">
+        <v/>
+      </c>
+      <c r="H376" t="str">
+        <v/>
+      </c>
+      <c r="I376" t="str">
+        <v>2026-04-10T10:18:53.263Z</v>
+      </c>
+      <c r="J376" t="str">
+        <v>2026-04-10T10:18:53.263Z</v>
+      </c>
+      <c r="K376" t="str">
+        <v/>
+      </c>
+      <c r="L376" t="str">
+        <v/>
+      </c>
+      <c r="M376" t="str">
+        <v/>
+      </c>
+      <c r="N376" t="str">
+        <v/>
+      </c>
+      <c r="O376" t="str">
+        <v/>
+      </c>
+      <c r="P376" t="str">
+        <v/>
+      </c>
+      <c r="Q376" t="str">
+        <v/>
+      </c>
+      <c r="R376" t="str">
+        <v/>
+      </c>
+      <c r="S376" t="str">
+        <v/>
+      </c>
+      <c r="T376">
+        <v>6.99</v>
+      </c>
+      <c r="U376" t="str">
+        <v>5</v>
+      </c>
+      <c r="V376" t="str">
+        <v/>
+      </c>
+      <c r="W376" t="str">
+        <v/>
+      </c>
+      <c r="X376" t="str">
+        <v/>
+      </c>
+      <c r="Y376" t="str">
+        <v/>
+      </c>
+      <c r="Z376" t="str">
+        <v/>
+      </c>
+      <c r="AA376" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="str">
+        <v>YAM020D001</v>
+      </c>
+      <c r="B377" t="str">
+        <v>YAM020</v>
+      </c>
+      <c r="C377" t="str">
+        <v>YAM-9L-05-020</v>
+      </c>
+      <c r="D377" t="str">
+        <v/>
+      </c>
+      <c r="E377" t="str">
+        <v/>
+      </c>
+      <c r="F377" t="str">
+        <v/>
+      </c>
+      <c r="G377" t="str">
+        <v/>
+      </c>
+      <c r="H377" t="str">
+        <v/>
+      </c>
+      <c r="I377" t="str">
+        <v>2026-04-10T10:18:55.387Z</v>
+      </c>
+      <c r="J377" t="str">
+        <v>2026-04-10T10:18:55.387Z</v>
+      </c>
+      <c r="K377" t="str">
+        <v/>
+      </c>
+      <c r="L377" t="str">
+        <v/>
+      </c>
+      <c r="M377" t="str">
+        <v/>
+      </c>
+      <c r="N377" t="str">
+        <v/>
+      </c>
+      <c r="O377" t="str">
+        <v/>
+      </c>
+      <c r="P377" t="str">
+        <v/>
+      </c>
+      <c r="Q377" t="str">
+        <v/>
+      </c>
+      <c r="R377" t="str">
+        <v/>
+      </c>
+      <c r="S377" t="str">
+        <v/>
+      </c>
+      <c r="T377">
+        <v>6.99</v>
+      </c>
+      <c r="U377" t="str">
+        <v>5</v>
+      </c>
+      <c r="V377" t="str">
+        <v/>
+      </c>
+      <c r="W377" t="str">
+        <v/>
+      </c>
+      <c r="X377" t="str">
+        <v/>
+      </c>
+      <c r="Y377" t="str">
+        <v/>
+      </c>
+      <c r="Z377" t="str">
+        <v/>
+      </c>
+      <c r="AA377" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="str">
+        <v>YAM021D001</v>
+      </c>
+      <c r="B378" t="str">
+        <v>YAM021</v>
+      </c>
+      <c r="C378" t="str">
+        <v>YAM-9S-10-009</v>
+      </c>
+      <c r="D378" t="str">
+        <v/>
+      </c>
+      <c r="E378" t="str">
+        <v/>
+      </c>
+      <c r="F378" t="str">
+        <v/>
+      </c>
+      <c r="G378" t="str">
+        <v/>
+      </c>
+      <c r="H378" t="str">
+        <v/>
+      </c>
+      <c r="I378" t="str">
+        <v>2026-04-10T10:18:57.476Z</v>
+      </c>
+      <c r="J378" t="str">
+        <v>2026-04-10T10:18:57.476Z</v>
+      </c>
+      <c r="K378" t="str">
+        <v/>
+      </c>
+      <c r="L378" t="str">
+        <v/>
+      </c>
+      <c r="M378" t="str">
+        <v/>
+      </c>
+      <c r="N378" t="str">
+        <v/>
+      </c>
+      <c r="O378" t="str">
+        <v/>
+      </c>
+      <c r="P378" t="str">
+        <v/>
+      </c>
+      <c r="Q378" t="str">
+        <v/>
+      </c>
+      <c r="R378" t="str">
+        <v/>
+      </c>
+      <c r="S378" t="str">
+        <v/>
+      </c>
+      <c r="T378">
+        <v>7.99</v>
+      </c>
+      <c r="U378" t="str">
+        <v>10</v>
+      </c>
+      <c r="V378" t="str">
+        <v/>
+      </c>
+      <c r="W378" t="str">
+        <v/>
+      </c>
+      <c r="X378" t="str">
+        <v/>
+      </c>
+      <c r="Y378" t="str">
+        <v/>
+      </c>
+      <c r="Z378" t="str">
+        <v/>
+      </c>
+      <c r="AA378" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="str">
+        <v>YAM022D001</v>
+      </c>
+      <c r="B379" t="str">
+        <v>YAM022</v>
+      </c>
+      <c r="C379" t="str">
+        <v>YAM-9-10-002</v>
+      </c>
+      <c r="D379" t="str">
+        <v/>
+      </c>
+      <c r="E379" t="str">
+        <v/>
+      </c>
+      <c r="F379" t="str">
+        <v/>
+      </c>
+      <c r="G379" t="str">
+        <v/>
+      </c>
+      <c r="H379" t="str">
+        <v/>
+      </c>
+      <c r="I379" t="str">
+        <v>2026-04-10T10:18:59.215Z</v>
+      </c>
+      <c r="J379" t="str">
+        <v>2026-04-10T10:18:59.215Z</v>
+      </c>
+      <c r="K379" t="str">
+        <v/>
+      </c>
+      <c r="L379" t="str">
+        <v/>
+      </c>
+      <c r="M379" t="str">
+        <v/>
+      </c>
+      <c r="N379" t="str">
+        <v/>
+      </c>
+      <c r="O379" t="str">
+        <v/>
+      </c>
+      <c r="P379" t="str">
+        <v/>
+      </c>
+      <c r="Q379" t="str">
+        <v/>
+      </c>
+      <c r="R379" t="str">
+        <v/>
+      </c>
+      <c r="S379" t="str">
+        <v/>
+      </c>
+      <c r="T379">
+        <v>7.99</v>
+      </c>
+      <c r="U379" t="str">
+        <v>10</v>
+      </c>
+      <c r="V379" t="str">
+        <v/>
+      </c>
+      <c r="W379" t="str">
+        <v/>
+      </c>
+      <c r="X379" t="str">
+        <v/>
+      </c>
+      <c r="Y379" t="str">
+        <v/>
+      </c>
+      <c r="Z379" t="str">
+        <v/>
+      </c>
+      <c r="AA379" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="str">
+        <v>YAM023D001</v>
+      </c>
+      <c r="B380" t="str">
+        <v>YAM023</v>
+      </c>
+      <c r="C380" t="str">
+        <v>YAM-68F-8-9005</v>
+      </c>
+      <c r="D380" t="str">
+        <v/>
+      </c>
+      <c r="E380" t="str">
+        <v/>
+      </c>
+      <c r="F380" t="str">
+        <v/>
+      </c>
+      <c r="G380" t="str">
+        <v/>
+      </c>
+      <c r="H380" t="str">
+        <v/>
+      </c>
+      <c r="I380" t="str">
+        <v>2026-04-10T10:19:00.636Z</v>
+      </c>
+      <c r="J380" t="str">
+        <v>2026-04-10T10:19:00.636Z</v>
+      </c>
+      <c r="K380" t="str">
+        <v/>
+      </c>
+      <c r="L380" t="str">
+        <v/>
+      </c>
+      <c r="M380" t="str">
+        <v/>
+      </c>
+      <c r="N380" t="str">
+        <v/>
+      </c>
+      <c r="O380" t="str">
+        <v/>
+      </c>
+      <c r="P380" t="str">
+        <v/>
+      </c>
+      <c r="Q380" t="str">
+        <v/>
+      </c>
+      <c r="R380" t="str">
+        <v/>
+      </c>
+      <c r="S380" t="str">
+        <v/>
+      </c>
+      <c r="T380">
+        <v>6.99</v>
+      </c>
+      <c r="U380" t="str">
+        <v>8</v>
+      </c>
+      <c r="V380" t="str">
+        <v/>
+      </c>
+      <c r="W380" t="str">
+        <v/>
+      </c>
+      <c r="X380" t="str">
+        <v/>
+      </c>
+      <c r="Y380" t="str">
+        <v/>
+      </c>
+      <c r="Z380" t="str">
+        <v/>
+      </c>
+      <c r="AA380" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="str">
+        <v>YAM024D001</v>
+      </c>
+      <c r="B381" t="str">
+        <v>YAM024</v>
+      </c>
+      <c r="C381" t="str">
+        <v>YAM-68JR-10-031</v>
+      </c>
+      <c r="D381" t="str">
+        <v/>
+      </c>
+      <c r="E381" t="str">
+        <v/>
+      </c>
+      <c r="F381" t="str">
+        <v/>
+      </c>
+      <c r="G381" t="str">
+        <v/>
+      </c>
+      <c r="H381" t="str">
+        <v/>
+      </c>
+      <c r="I381" t="str">
+        <v>2026-04-10T10:19:02.734Z</v>
+      </c>
+      <c r="J381" t="str">
+        <v>2026-04-10T10:19:02.734Z</v>
+      </c>
+      <c r="K381" t="str">
+        <v/>
+      </c>
+      <c r="L381" t="str">
+        <v/>
+      </c>
+      <c r="M381" t="str">
+        <v/>
+      </c>
+      <c r="N381" t="str">
+        <v/>
+      </c>
+      <c r="O381" t="str">
+        <v/>
+      </c>
+      <c r="P381" t="str">
+        <v/>
+      </c>
+      <c r="Q381" t="str">
+        <v/>
+      </c>
+      <c r="R381" t="str">
+        <v/>
+      </c>
+      <c r="S381" t="str">
+        <v/>
+      </c>
+      <c r="T381">
+        <v>4.99</v>
+      </c>
+      <c r="U381" t="str">
+        <v>10</v>
+      </c>
+      <c r="V381" t="str">
+        <v/>
+      </c>
+      <c r="W381" t="str">
+        <v/>
+      </c>
+      <c r="X381" t="str">
+        <v/>
+      </c>
+      <c r="Y381" t="str">
+        <v/>
+      </c>
+      <c r="Z381" t="str">
+        <v/>
+      </c>
+      <c r="AA381" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="str">
+        <v>YAM025D001</v>
+      </c>
+      <c r="B382" t="str">
+        <v>YAM025</v>
+      </c>
+      <c r="C382" t="str">
+        <v>YAM-7-20-021</v>
+      </c>
+      <c r="D382" t="str">
+        <v/>
+      </c>
+      <c r="E382" t="str">
+        <v/>
+      </c>
+      <c r="F382" t="str">
+        <v/>
+      </c>
+      <c r="G382" t="str">
+        <v/>
+      </c>
+      <c r="H382" t="str">
+        <v/>
+      </c>
+      <c r="I382" t="str">
+        <v>2026-04-10T10:19:04.912Z</v>
+      </c>
+      <c r="J382" t="str">
+        <v>2026-04-10T10:19:04.912Z</v>
+      </c>
+      <c r="K382" t="str">
+        <v/>
+      </c>
+      <c r="L382" t="str">
+        <v/>
+      </c>
+      <c r="M382" t="str">
+        <v/>
+      </c>
+      <c r="N382" t="str">
+        <v/>
+      </c>
+      <c r="O382" t="str">
+        <v/>
+      </c>
+      <c r="P382" t="str">
+        <v/>
+      </c>
+      <c r="Q382" t="str">
+        <v/>
+      </c>
+      <c r="R382" t="str">
+        <v/>
+      </c>
+      <c r="S382" t="str">
+        <v/>
+      </c>
+      <c r="T382">
+        <v>8.99</v>
+      </c>
+      <c r="U382" t="str">
+        <v/>
+      </c>
+      <c r="V382" t="str">
+        <v/>
+      </c>
+      <c r="W382" t="str">
+        <v/>
+      </c>
+      <c r="X382" t="str">
+        <v/>
+      </c>
+      <c r="Y382" t="str">
+        <v/>
+      </c>
+      <c r="Z382" t="str">
+        <v/>
+      </c>
+      <c r="AA382" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="str">
+        <v>YAM026D001</v>
+      </c>
+      <c r="B383" t="str">
+        <v>YAM026</v>
+      </c>
+      <c r="C383" t="str">
+        <v>YAM-SENSEI65-10-297</v>
+      </c>
+      <c r="D383" t="str">
+        <v/>
+      </c>
+      <c r="E383" t="str">
+        <v/>
+      </c>
+      <c r="F383" t="str">
+        <v/>
+      </c>
+      <c r="G383" t="str">
+        <v/>
+      </c>
+      <c r="H383" t="str">
+        <v/>
+      </c>
+      <c r="I383" t="str">
+        <v>2026-04-10T10:19:07.068Z</v>
+      </c>
+      <c r="J383" t="str">
+        <v>2026-04-10T10:19:07.068Z</v>
+      </c>
+      <c r="K383" t="str">
+        <v/>
+      </c>
+      <c r="L383" t="str">
+        <v/>
+      </c>
+      <c r="M383" t="str">
+        <v/>
+      </c>
+      <c r="N383" t="str">
+        <v/>
+      </c>
+      <c r="O383" t="str">
+        <v/>
+      </c>
+      <c r="P383" t="str">
+        <v/>
+      </c>
+      <c r="Q383" t="str">
+        <v/>
+      </c>
+      <c r="R383" t="str">
+        <v/>
+      </c>
+      <c r="S383" t="str">
+        <v/>
+      </c>
+      <c r="T383">
+        <v>6.99</v>
+      </c>
+      <c r="U383" t="str">
+        <v>10</v>
+      </c>
+      <c r="V383" t="str">
+        <v/>
+      </c>
+      <c r="W383" t="str">
+        <v/>
+      </c>
+      <c r="X383" t="str">
+        <v/>
+      </c>
+      <c r="Y383" t="str">
+        <v/>
+      </c>
+      <c r="Z383" t="str">
+        <v/>
+      </c>
+      <c r="AA383" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="str">
+        <v>YAM027D001</v>
+      </c>
+      <c r="B384" t="str">
+        <v>YAM027</v>
+      </c>
+      <c r="C384" t="str">
+        <v>YAM-OKI-06-301</v>
+      </c>
+      <c r="D384" t="str">
+        <v/>
+      </c>
+      <c r="E384" t="str">
+        <v/>
+      </c>
+      <c r="F384" t="str">
+        <v/>
+      </c>
+      <c r="G384" t="str">
+        <v/>
+      </c>
+      <c r="H384" t="str">
+        <v/>
+      </c>
+      <c r="I384" t="str">
+        <v>2026-04-10T10:19:10.212Z</v>
+      </c>
+      <c r="J384" t="str">
+        <v>2026-04-10T10:19:10.212Z</v>
+      </c>
+      <c r="K384" t="str">
+        <v/>
+      </c>
+      <c r="L384" t="str">
+        <v/>
+      </c>
+      <c r="M384" t="str">
+        <v/>
+      </c>
+      <c r="N384" t="str">
+        <v/>
+      </c>
+      <c r="O384" t="str">
+        <v/>
+      </c>
+      <c r="P384" t="str">
+        <v/>
+      </c>
+      <c r="Q384" t="str">
+        <v/>
+      </c>
+      <c r="R384" t="str">
+        <v/>
+      </c>
+      <c r="S384" t="str">
+        <v/>
+      </c>
+      <c r="T384">
+        <v>7.49</v>
+      </c>
+      <c r="U384" t="str">
+        <v>6</v>
+      </c>
+      <c r="V384" t="str">
+        <v/>
+      </c>
+      <c r="W384" t="str">
+        <v/>
+      </c>
+      <c r="X384" t="str">
+        <v/>
+      </c>
+      <c r="Y384" t="str">
+        <v/>
+      </c>
+      <c r="Z384" t="str">
+        <v/>
+      </c>
+      <c r="AA384" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="str">
+        <v>YAM028D001</v>
+      </c>
+      <c r="B385" t="str">
+        <v>YAM028</v>
+      </c>
+      <c r="C385" t="str">
+        <v>YAM-ICHI-06-301</v>
+      </c>
+      <c r="D385" t="str">
+        <v/>
+      </c>
+      <c r="E385" t="str">
+        <v/>
+      </c>
+      <c r="F385" t="str">
+        <v/>
+      </c>
+      <c r="G385" t="str">
+        <v/>
+      </c>
+      <c r="H385" t="str">
+        <v/>
+      </c>
+      <c r="I385" t="str">
+        <v>2026-04-10T10:19:12.347Z</v>
+      </c>
+      <c r="J385" t="str">
+        <v>2026-04-10T10:19:12.347Z</v>
+      </c>
+      <c r="K385" t="str">
+        <v/>
+      </c>
+      <c r="L385" t="str">
+        <v/>
+      </c>
+      <c r="M385" t="str">
+        <v/>
+      </c>
+      <c r="N385" t="str">
+        <v/>
+      </c>
+      <c r="O385" t="str">
+        <v/>
+      </c>
+      <c r="P385" t="str">
+        <v/>
+      </c>
+      <c r="Q385" t="str">
+        <v/>
+      </c>
+      <c r="R385" t="str">
+        <v/>
+      </c>
+      <c r="S385" t="str">
+        <v/>
+      </c>
+      <c r="T385">
+        <v>7.49</v>
+      </c>
+      <c r="U385" t="str">
+        <v>6</v>
+      </c>
+      <c r="V385" t="str">
+        <v/>
+      </c>
+      <c r="W385" t="str">
+        <v/>
+      </c>
+      <c r="X385" t="str">
+        <v/>
+      </c>
+      <c r="Y385" t="str">
+        <v/>
+      </c>
+      <c r="Z385" t="str">
+        <v/>
+      </c>
+      <c r="AA385" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="str">
+        <v>YAM029D001</v>
+      </c>
+      <c r="B386" t="str">
+        <v>YAM029</v>
+      </c>
+      <c r="C386" t="str">
+        <v>YAM-SLNKO325-8-021</v>
+      </c>
+      <c r="D386" t="str">
+        <v/>
+      </c>
+      <c r="E386" t="str">
+        <v/>
+      </c>
+      <c r="F386" t="str">
+        <v/>
+      </c>
+      <c r="G386" t="str">
+        <v/>
+      </c>
+      <c r="H386" t="str">
+        <v/>
+      </c>
+      <c r="I386" t="str">
+        <v>2026-04-10T10:19:15.237Z</v>
+      </c>
+      <c r="J386" t="str">
+        <v>2026-04-10T10:19:15.237Z</v>
+      </c>
+      <c r="K386" t="str">
+        <v/>
+      </c>
+      <c r="L386" t="str">
+        <v/>
+      </c>
+      <c r="M386" t="str">
+        <v/>
+      </c>
+      <c r="N386" t="str">
+        <v/>
+      </c>
+      <c r="O386" t="str">
+        <v/>
+      </c>
+      <c r="P386" t="str">
+        <v/>
+      </c>
+      <c r="Q386" t="str">
+        <v/>
+      </c>
+      <c r="R386" t="str">
+        <v/>
+      </c>
+      <c r="S386" t="str">
+        <v>3.25</v>
+      </c>
+      <c r="T386">
+        <v>6.99</v>
+      </c>
+      <c r="U386" t="str">
+        <v>8</v>
+      </c>
+      <c r="V386" t="str">
+        <v/>
+      </c>
+      <c r="W386" t="str">
+        <v/>
+      </c>
+      <c r="X386" t="str">
+        <v/>
+      </c>
+      <c r="Y386" t="str">
+        <v/>
+      </c>
+      <c r="Z386" t="str">
+        <v/>
+      </c>
+      <c r="AA386" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="str">
+        <v>YAM029D002</v>
+      </c>
+      <c r="B387" t="str">
+        <v>YAM029</v>
+      </c>
+      <c r="C387" t="str">
+        <v>YAM-SLINKO5.5-021</v>
+      </c>
+      <c r="D387" t="str">
+        <v/>
+      </c>
+      <c r="E387" t="str">
+        <v/>
+      </c>
+      <c r="F387" t="str">
+        <v/>
+      </c>
+      <c r="G387" t="str">
+        <v/>
+      </c>
+      <c r="H387" t="str">
+        <v/>
+      </c>
+      <c r="I387" t="str">
+        <v>2026-04-10T10:19:15.237Z</v>
+      </c>
+      <c r="J387" t="str">
+        <v>2026-04-10T10:19:15.237Z</v>
+      </c>
+      <c r="K387" t="str">
+        <v/>
+      </c>
+      <c r="L387" t="str">
+        <v/>
+      </c>
+      <c r="M387" t="str">
+        <v/>
+      </c>
+      <c r="N387" t="str">
+        <v/>
+      </c>
+      <c r="O387" t="str">
+        <v/>
+      </c>
+      <c r="P387" t="str">
+        <v/>
+      </c>
+      <c r="Q387" t="str">
+        <v/>
+      </c>
+      <c r="R387" t="str">
+        <v/>
+      </c>
+      <c r="S387" t="str">
+        <v>5.5</v>
+      </c>
+      <c r="T387">
+        <v>7.99</v>
+      </c>
+      <c r="U387" t="str">
+        <v>7</v>
+      </c>
+      <c r="V387" t="str">
+        <v/>
+      </c>
+      <c r="W387" t="str">
+        <v/>
+      </c>
+      <c r="X387" t="str">
+        <v/>
+      </c>
+      <c r="Y387" t="str">
+        <v/>
+      </c>
+      <c r="Z387" t="str">
+        <v/>
+      </c>
+      <c r="AA387" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="str">
+        <v>YAM030D001</v>
+      </c>
+      <c r="B388" t="str">
+        <v>YAM030</v>
+      </c>
+      <c r="C388" t="str">
+        <v>YAM-68M-08-031</v>
+      </c>
+      <c r="D388" t="str">
+        <v/>
+      </c>
+      <c r="E388" t="str">
+        <v/>
+      </c>
+      <c r="F388" t="str">
+        <v/>
+      </c>
+      <c r="G388" t="str">
+        <v/>
+      </c>
+      <c r="H388" t="str">
+        <v/>
+      </c>
+      <c r="I388" t="str">
+        <v>2026-04-10T10:19:17.364Z</v>
+      </c>
+      <c r="J388" t="str">
+        <v>2026-04-10T10:19:17.364Z</v>
+      </c>
+      <c r="K388" t="str">
+        <v/>
+      </c>
+      <c r="L388" t="str">
+        <v/>
+      </c>
+      <c r="M388" t="str">
+        <v/>
+      </c>
+      <c r="N388" t="str">
+        <v/>
+      </c>
+      <c r="O388" t="str">
+        <v/>
+      </c>
+      <c r="P388" t="str">
+        <v/>
+      </c>
+      <c r="Q388" t="str">
+        <v/>
+      </c>
+      <c r="R388" t="str">
+        <v/>
+      </c>
+      <c r="S388" t="str">
+        <v/>
+      </c>
+      <c r="T388">
+        <v>5.99</v>
+      </c>
+      <c r="U388" t="str">
+        <v>8</v>
+      </c>
+      <c r="V388" t="str">
+        <v/>
+      </c>
+      <c r="W388" t="str">
+        <v/>
+      </c>
+      <c r="X388" t="str">
+        <v/>
+      </c>
+      <c r="Y388" t="str">
+        <v/>
+      </c>
+      <c r="Z388" t="str">
+        <v/>
+      </c>
+      <c r="AA388" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="str">
+        <v>YAM031D001</v>
+      </c>
+      <c r="B389" t="str">
+        <v>YAM031</v>
+      </c>
+      <c r="C389" t="str">
+        <v>YAM-SHINOBI35-8-297</v>
+      </c>
+      <c r="D389" t="str">
+        <v/>
+      </c>
+      <c r="E389" t="str">
+        <v/>
+      </c>
+      <c r="F389" t="str">
+        <v/>
+      </c>
+      <c r="G389" t="str">
+        <v/>
+      </c>
+      <c r="H389" t="str">
+        <v/>
+      </c>
+      <c r="I389" t="str">
+        <v>2026-04-10T10:19:20.468Z</v>
+      </c>
+      <c r="J389" t="str">
+        <v>2026-04-10T10:19:20.468Z</v>
+      </c>
+      <c r="K389" t="str">
+        <v/>
+      </c>
+      <c r="L389" t="str">
+        <v/>
+      </c>
+      <c r="M389" t="str">
+        <v/>
+      </c>
+      <c r="N389" t="str">
+        <v/>
+      </c>
+      <c r="O389" t="str">
+        <v/>
+      </c>
+      <c r="P389" t="str">
+        <v/>
+      </c>
+      <c r="Q389" t="str">
+        <v/>
+      </c>
+      <c r="R389" t="str">
+        <v/>
+      </c>
+      <c r="S389" t="str">
+        <v/>
+      </c>
+      <c r="T389">
+        <v>9.99</v>
+      </c>
+      <c r="U389" t="str">
+        <v>8</v>
+      </c>
+      <c r="V389" t="str">
+        <v/>
+      </c>
+      <c r="W389" t="str">
+        <v/>
+      </c>
+      <c r="X389" t="str">
+        <v/>
+      </c>
+      <c r="Y389" t="str">
+        <v/>
+      </c>
+      <c r="Z389" t="str">
+        <v/>
+      </c>
+      <c r="AA389" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="str">
+        <v>YAM032D001</v>
+      </c>
+      <c r="B390" t="str">
+        <v>YAM032</v>
+      </c>
+      <c r="C390" t="str">
+        <v>YAM-HULK1</v>
+      </c>
+      <c r="D390" t="str">
+        <v/>
+      </c>
+      <c r="E390" t="str">
+        <v/>
+      </c>
+      <c r="F390" t="str">
+        <v/>
+      </c>
+      <c r="G390" t="str">
+        <v/>
+      </c>
+      <c r="H390" t="str">
+        <v/>
+      </c>
+      <c r="I390" t="str">
+        <v>2026-04-10T10:19:23.545Z</v>
+      </c>
+      <c r="J390" t="str">
+        <v>2026-04-10T10:19:23.545Z</v>
+      </c>
+      <c r="K390" t="str">
+        <v/>
+      </c>
+      <c r="L390" t="str">
+        <v/>
+      </c>
+      <c r="M390" t="str">
+        <v/>
+      </c>
+      <c r="N390" t="str">
+        <v/>
+      </c>
+      <c r="O390" t="str">
+        <v/>
+      </c>
+      <c r="P390" t="str">
+        <v/>
+      </c>
+      <c r="Q390" t="str">
+        <v/>
+      </c>
+      <c r="R390" t="str">
+        <v/>
+      </c>
+      <c r="S390" t="str">
+        <v/>
+      </c>
+      <c r="T390">
+        <v>34.99</v>
+      </c>
+      <c r="U390" t="str">
+        <v>50</v>
+      </c>
+      <c r="V390" t="str">
+        <v/>
+      </c>
+      <c r="W390" t="str">
+        <v/>
+      </c>
+      <c r="X390" t="str">
+        <v/>
+      </c>
+      <c r="Y390" t="str">
+        <v/>
+      </c>
+      <c r="Z390" t="str">
+        <v/>
+      </c>
+      <c r="AA390" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="str">
+        <v>YAM033D001</v>
+      </c>
+      <c r="B391" t="str">
+        <v>YAM033</v>
+      </c>
+      <c r="C391" t="str">
+        <v>YAM-NUKI35-08-305</v>
+      </c>
+      <c r="D391" t="str">
+        <v/>
+      </c>
+      <c r="E391" t="str">
+        <v/>
+      </c>
+      <c r="F391" t="str">
+        <v/>
+      </c>
+      <c r="G391" t="str">
+        <v/>
+      </c>
+      <c r="H391" t="str">
+        <v/>
+      </c>
+      <c r="I391" t="str">
+        <v>2026-04-10T10:19:26.555Z</v>
+      </c>
+      <c r="J391" t="str">
+        <v>2026-04-10T10:19:26.555Z</v>
+      </c>
+      <c r="K391" t="str">
+        <v/>
+      </c>
+      <c r="L391" t="str">
+        <v/>
+      </c>
+      <c r="M391" t="str">
+        <v/>
+      </c>
+      <c r="N391" t="str">
+        <v/>
+      </c>
+      <c r="O391" t="str">
+        <v/>
+      </c>
+      <c r="P391" t="str">
+        <v/>
+      </c>
+      <c r="Q391" t="str">
+        <v/>
+      </c>
+      <c r="R391" t="str">
+        <v/>
+      </c>
+      <c r="S391" t="str">
+        <v/>
+      </c>
+      <c r="T391">
+        <v>7.99</v>
+      </c>
+      <c r="U391" t="str">
+        <v/>
+      </c>
+      <c r="V391" t="str">
+        <v/>
+      </c>
+      <c r="W391" t="str">
+        <v/>
+      </c>
+      <c r="X391" t="str">
+        <v/>
+      </c>
+      <c r="Y391" t="str">
+        <v/>
+      </c>
+      <c r="Z391" t="str">
+        <v/>
+      </c>
+      <c r="AA391" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="str">
+        <v>YAM034D001</v>
+      </c>
+      <c r="B392" t="str">
+        <v>YAM034</v>
+      </c>
+      <c r="C392" t="str">
+        <v>YAM-97-10-031</v>
+      </c>
+      <c r="D392" t="str">
+        <v/>
+      </c>
+      <c r="E392" t="str">
+        <v/>
+      </c>
+      <c r="F392" t="str">
+        <v/>
+      </c>
+      <c r="G392" t="str">
+        <v/>
+      </c>
+      <c r="H392" t="str">
+        <v/>
+      </c>
+      <c r="I392" t="str">
+        <v>2026-04-10T10:19:28.669Z</v>
+      </c>
+      <c r="J392" t="str">
+        <v>2026-04-10T10:19:28.669Z</v>
+      </c>
+      <c r="K392" t="str">
+        <v/>
+      </c>
+      <c r="L392" t="str">
+        <v/>
+      </c>
+      <c r="M392" t="str">
+        <v/>
+      </c>
+      <c r="N392" t="str">
+        <v/>
+      </c>
+      <c r="O392" t="str">
+        <v/>
+      </c>
+      <c r="P392" t="str">
+        <v/>
+      </c>
+      <c r="Q392" t="str">
+        <v/>
+      </c>
+      <c r="R392" t="str">
+        <v/>
+      </c>
+      <c r="S392" t="str">
+        <v/>
+      </c>
+      <c r="T392">
+        <v>7.99</v>
+      </c>
+      <c r="U392" t="str">
+        <v>10</v>
+      </c>
+      <c r="V392" t="str">
+        <v/>
+      </c>
+      <c r="W392" t="str">
+        <v/>
+      </c>
+      <c r="X392" t="str">
+        <v/>
+      </c>
+      <c r="Y392" t="str">
+        <v/>
+      </c>
+      <c r="Z392" t="str">
+        <v/>
+      </c>
+      <c r="AA392" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="str">
+        <v>YAM035D001</v>
+      </c>
+      <c r="B393" t="str">
+        <v>YAM035</v>
+      </c>
+      <c r="C393" t="str">
+        <v>YAM-15-20-021</v>
+      </c>
+      <c r="D393" t="str">
+        <v/>
+      </c>
+      <c r="E393" t="str">
+        <v/>
+      </c>
+      <c r="F393" t="str">
+        <v/>
+      </c>
+      <c r="G393" t="str">
+        <v/>
+      </c>
+      <c r="H393" t="str">
+        <v/>
+      </c>
+      <c r="I393" t="str">
+        <v>2026-04-10T10:19:30.873Z</v>
+      </c>
+      <c r="J393" t="str">
+        <v>2026-04-10T10:19:30.873Z</v>
+      </c>
+      <c r="K393" t="str">
+        <v/>
+      </c>
+      <c r="L393" t="str">
+        <v/>
+      </c>
+      <c r="M393" t="str">
+        <v/>
+      </c>
+      <c r="N393" t="str">
+        <v/>
+      </c>
+      <c r="O393" t="str">
+        <v/>
+      </c>
+      <c r="P393" t="str">
+        <v/>
+      </c>
+      <c r="Q393" t="str">
+        <v/>
+      </c>
+      <c r="R393" t="str">
+        <v/>
+      </c>
+      <c r="S393" t="str">
+        <v/>
+      </c>
+      <c r="T393">
+        <v>7.99</v>
+      </c>
+      <c r="U393" t="str">
+        <v>20</v>
+      </c>
+      <c r="V393" t="str">
+        <v/>
+      </c>
+      <c r="W393" t="str">
+        <v/>
+      </c>
+      <c r="X393" t="str">
+        <v/>
+      </c>
+      <c r="Y393" t="str">
+        <v/>
+      </c>
+      <c r="Z393" t="str">
+        <v/>
+      </c>
+      <c r="AA393" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="str">
+        <v>YAM036D001</v>
+      </c>
+      <c r="B394" t="str">
+        <v>YAM036</v>
+      </c>
+      <c r="C394" t="str">
+        <v>YAM-40-20-031</v>
+      </c>
+      <c r="D394" t="str">
+        <v/>
+      </c>
+      <c r="E394" t="str">
+        <v/>
+      </c>
+      <c r="F394" t="str">
+        <v/>
+      </c>
+      <c r="G394" t="str">
+        <v/>
+      </c>
+      <c r="H394" t="str">
+        <v/>
+      </c>
+      <c r="I394" t="str">
+        <v>2026-04-10T10:19:32.965Z</v>
+      </c>
+      <c r="J394" t="str">
+        <v>2026-04-10T10:19:32.965Z</v>
+      </c>
+      <c r="K394" t="str">
+        <v/>
+      </c>
+      <c r="L394" t="str">
+        <v/>
+      </c>
+      <c r="M394" t="str">
+        <v/>
+      </c>
+      <c r="N394" t="str">
+        <v/>
+      </c>
+      <c r="O394" t="str">
+        <v/>
+      </c>
+      <c r="P394" t="str">
+        <v/>
+      </c>
+      <c r="Q394" t="str">
+        <v/>
+      </c>
+      <c r="R394" t="str">
+        <v/>
+      </c>
+      <c r="S394" t="str">
+        <v/>
+      </c>
+      <c r="T394">
+        <v>7.99</v>
+      </c>
+      <c r="U394" t="str">
+        <v>20</v>
+      </c>
+      <c r="V394" t="str">
+        <v/>
+      </c>
+      <c r="W394" t="str">
+        <v/>
+      </c>
+      <c r="X394" t="str">
+        <v/>
+      </c>
+      <c r="Y394" t="str">
+        <v/>
+      </c>
+      <c r="Z394" t="str">
+        <v/>
+      </c>
+      <c r="AA394" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="str">
+        <v>YAM037D001</v>
+      </c>
+      <c r="B395" t="str">
+        <v>YAM037</v>
+      </c>
+      <c r="C395" t="str">
+        <v>YAM-SHIBO27-8-9005</v>
+      </c>
+      <c r="D395" t="str">
+        <v/>
+      </c>
+      <c r="E395" t="str">
+        <v/>
+      </c>
+      <c r="F395" t="str">
+        <v/>
+      </c>
+      <c r="G395" t="str">
+        <v/>
+      </c>
+      <c r="H395" t="str">
+        <v/>
+      </c>
+      <c r="I395" t="str">
+        <v>2026-04-10T10:19:37.985Z</v>
+      </c>
+      <c r="J395" t="str">
+        <v>2026-04-10T10:19:37.985Z</v>
+      </c>
+      <c r="K395" t="str">
+        <v/>
+      </c>
+      <c r="L395" t="str">
+        <v/>
+      </c>
+      <c r="M395" t="str">
+        <v/>
+      </c>
+      <c r="N395" t="str">
+        <v/>
+      </c>
+      <c r="O395" t="str">
+        <v/>
+      </c>
+      <c r="P395" t="str">
+        <v/>
+      </c>
+      <c r="Q395" t="str">
+        <v/>
+      </c>
+      <c r="R395" t="str">
+        <v/>
+      </c>
+      <c r="S395" t="str">
+        <v>2.7</v>
+      </c>
+      <c r="T395">
+        <v>7.99</v>
+      </c>
+      <c r="U395" t="str">
+        <v>8</v>
+      </c>
+      <c r="V395" t="str">
+        <v/>
+      </c>
+      <c r="W395" t="str">
+        <v/>
+      </c>
+      <c r="X395" t="str">
+        <v/>
+      </c>
+      <c r="Y395" t="str">
+        <v/>
+      </c>
+      <c r="Z395" t="str">
+        <v/>
+      </c>
+      <c r="AA395" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="str">
+        <v>YAM037D002</v>
+      </c>
+      <c r="B396" t="str">
+        <v>YAM037</v>
+      </c>
+      <c r="C396" t="str">
+        <v>YAM-SHIBO32-7-9005</v>
+      </c>
+      <c r="D396" t="str">
+        <v/>
+      </c>
+      <c r="E396" t="str">
+        <v/>
+      </c>
+      <c r="F396" t="str">
+        <v/>
+      </c>
+      <c r="G396" t="str">
+        <v/>
+      </c>
+      <c r="H396" t="str">
+        <v/>
+      </c>
+      <c r="I396" t="str">
+        <v>2026-04-10T10:19:37.985Z</v>
+      </c>
+      <c r="J396" t="str">
+        <v>2026-04-10T10:19:37.985Z</v>
+      </c>
+      <c r="K396" t="str">
+        <v/>
+      </c>
+      <c r="L396" t="str">
+        <v/>
+      </c>
+      <c r="M396" t="str">
+        <v/>
+      </c>
+      <c r="N396" t="str">
+        <v/>
+      </c>
+      <c r="O396" t="str">
+        <v/>
+      </c>
+      <c r="P396" t="str">
+        <v/>
+      </c>
+      <c r="Q396" t="str">
+        <v/>
+      </c>
+      <c r="R396" t="str">
+        <v/>
+      </c>
+      <c r="S396" t="str">
+        <v>3.2</v>
+      </c>
+      <c r="T396">
+        <v>7.99</v>
+      </c>
+      <c r="U396" t="str">
+        <v>7</v>
+      </c>
+      <c r="V396" t="str">
+        <v/>
+      </c>
+      <c r="W396" t="str">
+        <v/>
+      </c>
+      <c r="X396" t="str">
+        <v/>
+      </c>
+      <c r="Y396" t="str">
+        <v/>
+      </c>
+      <c r="Z396" t="str">
+        <v/>
+      </c>
+      <c r="AA396" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="str">
+        <v>YAM037D003</v>
+      </c>
+      <c r="B397" t="str">
+        <v>YAM037</v>
+      </c>
+      <c r="C397" t="str">
+        <v>YAM-SHIBO37-6-9005</v>
+      </c>
+      <c r="D397" t="str">
+        <v/>
+      </c>
+      <c r="E397" t="str">
+        <v/>
+      </c>
+      <c r="F397" t="str">
+        <v/>
+      </c>
+      <c r="G397" t="str">
+        <v/>
+      </c>
+      <c r="H397" t="str">
+        <v/>
+      </c>
+      <c r="I397" t="str">
+        <v>2026-04-10T10:19:37.985Z</v>
+      </c>
+      <c r="J397" t="str">
+        <v>2026-04-10T10:19:37.985Z</v>
+      </c>
+      <c r="K397" t="str">
+        <v/>
+      </c>
+      <c r="L397" t="str">
+        <v/>
+      </c>
+      <c r="M397" t="str">
+        <v/>
+      </c>
+      <c r="N397" t="str">
+        <v/>
+      </c>
+      <c r="O397" t="str">
+        <v/>
+      </c>
+      <c r="P397" t="str">
+        <v/>
+      </c>
+      <c r="Q397" t="str">
+        <v/>
+      </c>
+      <c r="R397" t="str">
+        <v/>
+      </c>
+      <c r="S397" t="str">
+        <v>3.7</v>
+      </c>
+      <c r="T397">
+        <v>7.99</v>
+      </c>
+      <c r="U397" t="str">
+        <v>6</v>
+      </c>
+      <c r="V397" t="str">
+        <v/>
+      </c>
+      <c r="W397" t="str">
+        <v/>
+      </c>
+      <c r="X397" t="str">
+        <v/>
+      </c>
+      <c r="Y397" t="str">
+        <v/>
+      </c>
+      <c r="Z397" t="str">
+        <v/>
+      </c>
+      <c r="AA397" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="str">
+        <v>YAM038D001</v>
+      </c>
+      <c r="B398" t="str">
+        <v>YAM038</v>
+      </c>
+      <c r="C398" t="str">
+        <v>YAM-HINGMIN35-7-9005</v>
+      </c>
+      <c r="D398" t="str">
+        <v/>
+      </c>
+      <c r="E398" t="str">
+        <v/>
+      </c>
+      <c r="F398" t="str">
+        <v/>
+      </c>
+      <c r="G398" t="str">
+        <v/>
+      </c>
+      <c r="H398" t="str">
+        <v/>
+      </c>
+      <c r="I398" t="str">
+        <v>2026-04-10T10:19:39.734Z</v>
+      </c>
+      <c r="J398" t="str">
+        <v>2026-04-10T10:19:39.734Z</v>
+      </c>
+      <c r="K398" t="str">
+        <v/>
+      </c>
+      <c r="L398" t="str">
+        <v/>
+      </c>
+      <c r="M398" t="str">
+        <v/>
+      </c>
+      <c r="N398" t="str">
+        <v/>
+      </c>
+      <c r="O398" t="str">
+        <v/>
+      </c>
+      <c r="P398" t="str">
+        <v/>
+      </c>
+      <c r="Q398" t="str">
+        <v/>
+      </c>
+      <c r="R398" t="str">
+        <v/>
+      </c>
+      <c r="S398" t="str">
+        <v>3.5</v>
+      </c>
+      <c r="T398">
+        <v>9.99</v>
+      </c>
+      <c r="U398" t="str">
+        <v>7</v>
+      </c>
+      <c r="V398" t="str">
+        <v/>
+      </c>
+      <c r="W398" t="str">
+        <v/>
+      </c>
+      <c r="X398" t="str">
+        <v/>
+      </c>
+      <c r="Y398" t="str">
+        <v/>
+      </c>
+      <c r="Z398" t="str">
+        <v/>
+      </c>
+      <c r="AA398" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="str">
+        <v>YAM038D002</v>
+      </c>
+      <c r="B399" t="str">
+        <v>YAM038</v>
+      </c>
+      <c r="C399" t="str">
+        <v>YAM-HINGMIN5-6-9005</v>
+      </c>
+      <c r="D399" t="str">
+        <v/>
+      </c>
+      <c r="E399" t="str">
+        <v/>
+      </c>
+      <c r="F399" t="str">
+        <v/>
+      </c>
+      <c r="G399" t="str">
+        <v/>
+      </c>
+      <c r="H399" t="str">
+        <v/>
+      </c>
+      <c r="I399" t="str">
+        <v>2026-04-10T10:19:39.734Z</v>
+      </c>
+      <c r="J399" t="str">
+        <v>2026-04-10T10:19:39.734Z</v>
+      </c>
+      <c r="K399" t="str">
+        <v/>
+      </c>
+      <c r="L399" t="str">
+        <v/>
+      </c>
+      <c r="M399" t="str">
+        <v/>
+      </c>
+      <c r="N399" t="str">
+        <v/>
+      </c>
+      <c r="O399" t="str">
+        <v/>
+      </c>
+      <c r="P399" t="str">
+        <v/>
+      </c>
+      <c r="Q399" t="str">
+        <v/>
+      </c>
+      <c r="R399" t="str">
+        <v/>
+      </c>
+      <c r="S399" t="str">
+        <v>5</v>
+      </c>
+      <c r="T399">
+        <v>9.99</v>
+      </c>
+      <c r="U399" t="str">
+        <v>6</v>
+      </c>
+      <c r="V399" t="str">
+        <v/>
+      </c>
+      <c r="W399" t="str">
+        <v/>
+      </c>
+      <c r="X399" t="str">
+        <v/>
+      </c>
+      <c r="Y399" t="str">
+        <v/>
+      </c>
+      <c r="Z399" t="str">
+        <v/>
+      </c>
+      <c r="AA399" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="str">
+        <v>YAM038D003</v>
+      </c>
+      <c r="B400" t="str">
+        <v>YAM038</v>
+      </c>
+      <c r="C400" t="str">
+        <v>YAM-HINGMIN6-5-9005</v>
+      </c>
+      <c r="D400" t="str">
+        <v/>
+      </c>
+      <c r="E400" t="str">
+        <v/>
+      </c>
+      <c r="F400" t="str">
+        <v/>
+      </c>
+      <c r="G400" t="str">
+        <v/>
+      </c>
+      <c r="H400" t="str">
+        <v/>
+      </c>
+      <c r="I400" t="str">
+        <v>2026-04-10T10:19:39.734Z</v>
+      </c>
+      <c r="J400" t="str">
+        <v>2026-04-10T10:19:39.734Z</v>
+      </c>
+      <c r="K400" t="str">
+        <v/>
+      </c>
+      <c r="L400" t="str">
+        <v/>
+      </c>
+      <c r="M400" t="str">
+        <v/>
+      </c>
+      <c r="N400" t="str">
+        <v/>
+      </c>
+      <c r="O400" t="str">
+        <v/>
+      </c>
+      <c r="P400" t="str">
+        <v/>
+      </c>
+      <c r="Q400" t="str">
+        <v/>
+      </c>
+      <c r="R400" t="str">
+        <v/>
+      </c>
+      <c r="S400" t="str">
+        <v>6</v>
+      </c>
+      <c r="T400">
+        <v>9.99</v>
+      </c>
+      <c r="U400" t="str">
+        <v>5</v>
+      </c>
+      <c r="V400" t="str">
+        <v/>
+      </c>
+      <c r="W400" t="str">
+        <v/>
+      </c>
+      <c r="X400" t="str">
+        <v/>
+      </c>
+      <c r="Y400" t="str">
+        <v/>
+      </c>
+      <c r="Z400" t="str">
+        <v/>
+      </c>
+      <c r="AA400" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="str">
+        <v>YAM038D004</v>
+      </c>
+      <c r="B401" t="str">
+        <v>YAM038</v>
+      </c>
+      <c r="C401" t="str">
+        <v>YAM-HINGMIN7-4-9005</v>
+      </c>
+      <c r="D401" t="str">
+        <v/>
+      </c>
+      <c r="E401" t="str">
+        <v/>
+      </c>
+      <c r="F401" t="str">
+        <v/>
+      </c>
+      <c r="G401" t="str">
+        <v/>
+      </c>
+      <c r="H401" t="str">
+        <v/>
+      </c>
+      <c r="I401" t="str">
+        <v>2026-04-10T10:19:39.734Z</v>
+      </c>
+      <c r="J401" t="str">
+        <v>2026-04-10T10:19:39.734Z</v>
+      </c>
+      <c r="K401" t="str">
+        <v/>
+      </c>
+      <c r="L401" t="str">
+        <v/>
+      </c>
+      <c r="M401" t="str">
+        <v/>
+      </c>
+      <c r="N401" t="str">
+        <v/>
+      </c>
+      <c r="O401" t="str">
+        <v/>
+      </c>
+      <c r="P401" t="str">
+        <v/>
+      </c>
+      <c r="Q401" t="str">
+        <v/>
+      </c>
+      <c r="R401" t="str">
+        <v/>
+      </c>
+      <c r="S401" t="str">
+        <v>7</v>
+      </c>
+      <c r="T401">
+        <v>9.99</v>
+      </c>
+      <c r="U401" t="str">
+        <v>4</v>
+      </c>
+      <c r="V401" t="str">
+        <v/>
+      </c>
+      <c r="W401" t="str">
+        <v/>
+      </c>
+      <c r="X401" t="str">
+        <v/>
+      </c>
+      <c r="Y401" t="str">
+        <v/>
+      </c>
+      <c r="Z401" t="str">
+        <v/>
+      </c>
+      <c r="AA401" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="str">
+        <v>YAM039D001</v>
+      </c>
+      <c r="B402" t="str">
+        <v>YAM039</v>
+      </c>
+      <c r="C402" t="str">
+        <v>BAITS-ZAKK1</v>
+      </c>
+      <c r="D402" t="str">
+        <v/>
+      </c>
+      <c r="E402" t="str">
+        <v/>
+      </c>
+      <c r="F402" t="str">
+        <v/>
+      </c>
+      <c r="G402" t="str">
+        <v/>
+      </c>
+      <c r="H402" t="str">
+        <v/>
+      </c>
+      <c r="I402" t="str">
+        <v>2026-04-10T10:19:41.850Z</v>
+      </c>
+      <c r="J402" t="str">
+        <v>2026-04-10T10:19:41.850Z</v>
+      </c>
+      <c r="K402" t="str">
+        <v/>
+      </c>
+      <c r="L402" t="str">
+        <v/>
+      </c>
+      <c r="M402" t="str">
+        <v/>
+      </c>
+      <c r="N402" t="str">
+        <v/>
+      </c>
+      <c r="O402" t="str">
+        <v/>
+      </c>
+      <c r="P402" t="str">
+        <v/>
+      </c>
+      <c r="Q402" t="str">
+        <v/>
+      </c>
+      <c r="R402" t="str">
+        <v/>
+      </c>
+      <c r="S402" t="str">
+        <v/>
+      </c>
+      <c r="T402">
+        <v>64.99</v>
+      </c>
+      <c r="U402" t="str">
+        <v>84</v>
+      </c>
+      <c r="V402" t="str">
+        <v/>
+      </c>
+      <c r="W402" t="str">
+        <v/>
+      </c>
+      <c r="X402" t="str">
+        <v/>
+      </c>
+      <c r="Y402" t="str">
+        <v/>
+      </c>
+      <c r="Z402" t="str">
+        <v/>
+      </c>
+      <c r="AA402" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="str">
+        <v>YAM040D001</v>
+      </c>
+      <c r="B403" t="str">
+        <v>YAM040</v>
+      </c>
+      <c r="C403" t="str">
+        <v>YAM-134S-6-021</v>
+      </c>
+      <c r="D403" t="str">
+        <v/>
+      </c>
+      <c r="E403" t="str">
+        <v/>
+      </c>
+      <c r="F403" t="str">
+        <v/>
+      </c>
+      <c r="G403" t="str">
+        <v/>
+      </c>
+      <c r="H403" t="str">
+        <v/>
+      </c>
+      <c r="I403" t="str">
+        <v>2026-04-10T10:19:43.096Z</v>
+      </c>
+      <c r="J403" t="str">
+        <v>2026-04-10T10:19:43.096Z</v>
+      </c>
+      <c r="K403" t="str">
+        <v/>
+      </c>
+      <c r="L403" t="str">
+        <v/>
+      </c>
+      <c r="M403" t="str">
+        <v/>
+      </c>
+      <c r="N403" t="str">
+        <v/>
+      </c>
+      <c r="O403" t="str">
+        <v/>
+      </c>
+      <c r="P403" t="str">
+        <v/>
+      </c>
+      <c r="Q403" t="str">
+        <v/>
+      </c>
+      <c r="R403" t="str">
+        <v/>
+      </c>
+      <c r="S403" t="str">
+        <v/>
+      </c>
+      <c r="T403">
+        <v>6.99</v>
+      </c>
+      <c r="U403" t="str">
+        <v>6</v>
+      </c>
+      <c r="V403" t="str">
+        <v/>
+      </c>
+      <c r="W403" t="str">
+        <v/>
+      </c>
+      <c r="X403" t="str">
+        <v/>
+      </c>
+      <c r="Y403" t="str">
+        <v/>
+      </c>
+      <c r="Z403" t="str">
+        <v/>
+      </c>
+      <c r="AA403" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="str">
+        <v>YAM041D001</v>
+      </c>
+      <c r="B404" t="str">
+        <v>YAM041</v>
+      </c>
+      <c r="C404" t="str">
+        <v>YAM-SSHAD3-10-305</v>
+      </c>
+      <c r="D404" t="str">
+        <v/>
+      </c>
+      <c r="E404" t="str">
+        <v/>
+      </c>
+      <c r="F404" t="str">
+        <v/>
+      </c>
+      <c r="G404" t="str">
+        <v/>
+      </c>
+      <c r="H404" t="str">
+        <v/>
+      </c>
+      <c r="I404" t="str">
+        <v>2026-04-10T10:19:45.246Z</v>
+      </c>
+      <c r="J404" t="str">
+        <v>2026-04-10T10:19:45.246Z</v>
+      </c>
+      <c r="K404" t="str">
+        <v/>
+      </c>
+      <c r="L404" t="str">
+        <v/>
+      </c>
+      <c r="M404" t="str">
+        <v/>
+      </c>
+      <c r="N404" t="str">
+        <v/>
+      </c>
+      <c r="O404" t="str">
+        <v/>
+      </c>
+      <c r="P404" t="str">
+        <v/>
+      </c>
+      <c r="Q404" t="str">
+        <v/>
+      </c>
+      <c r="R404" t="str">
+        <v/>
+      </c>
+      <c r="S404" t="str">
+        <v/>
+      </c>
+      <c r="T404">
+        <v>5.99</v>
+      </c>
+      <c r="U404" t="str">
+        <v/>
+      </c>
+      <c r="V404" t="str">
+        <v/>
+      </c>
+      <c r="W404" t="str">
+        <v/>
+      </c>
+      <c r="X404" t="str">
+        <v/>
+      </c>
+      <c r="Y404" t="str">
+        <v/>
+      </c>
+      <c r="Z404" t="str">
+        <v/>
+      </c>
+      <c r="AA404" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="str">
+        <v>YAM042D001</v>
+      </c>
+      <c r="B405" t="str">
+        <v>YAM042</v>
+      </c>
+      <c r="C405" t="str">
+        <v>YAM-SSSWIM32-8-297</v>
+      </c>
+      <c r="D405" t="str">
+        <v/>
+      </c>
+      <c r="E405" t="str">
+        <v/>
+      </c>
+      <c r="F405" t="str">
+        <v/>
+      </c>
+      <c r="G405" t="str">
+        <v/>
+      </c>
+      <c r="H405" t="str">
+        <v/>
+      </c>
+      <c r="I405" t="str">
+        <v>2026-04-10T10:19:48.508Z</v>
+      </c>
+      <c r="J405" t="str">
+        <v>2026-04-10T10:19:48.508Z</v>
+      </c>
+      <c r="K405" t="str">
+        <v/>
+      </c>
+      <c r="L405" t="str">
+        <v/>
+      </c>
+      <c r="M405" t="str">
+        <v/>
+      </c>
+      <c r="N405" t="str">
+        <v/>
+      </c>
+      <c r="O405" t="str">
+        <v/>
+      </c>
+      <c r="P405" t="str">
+        <v/>
+      </c>
+      <c r="Q405" t="str">
+        <v/>
+      </c>
+      <c r="R405" t="str">
+        <v/>
+      </c>
+      <c r="S405" t="str">
+        <v/>
+      </c>
+      <c r="T405">
+        <v>5.99</v>
+      </c>
+      <c r="U405" t="str">
+        <v>8</v>
+      </c>
+      <c r="V405" t="str">
+        <v/>
+      </c>
+      <c r="W405" t="str">
+        <v/>
+      </c>
+      <c r="X405" t="str">
+        <v/>
+      </c>
+      <c r="Y405" t="str">
+        <v/>
+      </c>
+      <c r="Z405" t="str">
+        <v/>
+      </c>
+      <c r="AA405" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="str">
+        <v>YAM043D001</v>
+      </c>
+      <c r="B406" t="str">
+        <v>YAM043</v>
+      </c>
+      <c r="C406" t="str">
+        <v>YAM-134-06-036</v>
+      </c>
+      <c r="D406" t="str">
+        <v/>
+      </c>
+      <c r="E406" t="str">
+        <v/>
+      </c>
+      <c r="F406" t="str">
+        <v/>
+      </c>
+      <c r="G406" t="str">
+        <v/>
+      </c>
+      <c r="H406" t="str">
+        <v/>
+      </c>
+      <c r="I406" t="str">
+        <v>2026-04-10T10:19:50.589Z</v>
+      </c>
+      <c r="J406" t="str">
+        <v>2026-04-10T10:19:50.589Z</v>
+      </c>
+      <c r="K406" t="str">
+        <v/>
+      </c>
+      <c r="L406" t="str">
+        <v/>
+      </c>
+      <c r="M406" t="str">
+        <v/>
+      </c>
+      <c r="N406" t="str">
+        <v/>
+      </c>
+      <c r="O406" t="str">
+        <v/>
+      </c>
+      <c r="P406" t="str">
+        <v/>
+      </c>
+      <c r="Q406" t="str">
+        <v/>
+      </c>
+      <c r="R406" t="str">
+        <v/>
+      </c>
+      <c r="S406" t="str">
+        <v/>
+      </c>
+      <c r="T406">
+        <v>6.99</v>
+      </c>
+      <c r="U406" t="str">
+        <v/>
+      </c>
+      <c r="V406" t="str">
+        <v/>
+      </c>
+      <c r="W406" t="str">
+        <v/>
+      </c>
+      <c r="X406" t="str">
+        <v/>
+      </c>
+      <c r="Y406" t="str">
+        <v/>
+      </c>
+      <c r="Z406" t="str">
+        <v/>
+      </c>
+      <c r="AA406" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="str">
+        <v>YAM044D001</v>
+      </c>
+      <c r="B407" t="str">
+        <v>YAM044</v>
+      </c>
+      <c r="C407" t="str">
+        <v>YAM-134-BP-99-50</v>
+      </c>
+      <c r="D407" t="str">
+        <v/>
+      </c>
+      <c r="E407" t="str">
+        <v/>
+      </c>
+      <c r="F407" t="str">
+        <v/>
+      </c>
+      <c r="G407" t="str">
+        <v/>
+      </c>
+      <c r="H407" t="str">
+        <v/>
+      </c>
+      <c r="I407" t="str">
+        <v>2026-04-10T10:19:52.662Z</v>
+      </c>
+      <c r="J407" t="str">
+        <v>2026-04-10T10:19:52.662Z</v>
+      </c>
+      <c r="K407" t="str">
+        <v/>
+      </c>
+      <c r="L407" t="str">
+        <v/>
+      </c>
+      <c r="M407" t="str">
+        <v/>
+      </c>
+      <c r="N407" t="str">
+        <v/>
+      </c>
+      <c r="O407" t="str">
+        <v/>
+      </c>
+      <c r="P407" t="str">
+        <v/>
+      </c>
+      <c r="Q407" t="str">
+        <v/>
+      </c>
+      <c r="R407" t="str">
+        <v/>
+      </c>
+      <c r="S407" t="str">
+        <v/>
+      </c>
+      <c r="T407">
+        <v>34.99</v>
+      </c>
+      <c r="U407" t="str">
+        <v/>
+      </c>
+      <c r="V407" t="str">
+        <v/>
+      </c>
+      <c r="W407" t="str">
+        <v/>
+      </c>
+      <c r="X407" t="str">
+        <v/>
+      </c>
+      <c r="Y407" t="str">
+        <v/>
+      </c>
+      <c r="Z407" t="str">
+        <v/>
+      </c>
+      <c r="AA407" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="str">
+        <v>YAM045D001</v>
+      </c>
+      <c r="B408" t="str">
+        <v>YAM045</v>
+      </c>
+      <c r="C408" t="str">
+        <v>YAM-134P-05-021</v>
+      </c>
+      <c r="D408" t="str">
+        <v/>
+      </c>
+      <c r="E408" t="str">
+        <v/>
+      </c>
+      <c r="F408" t="str">
+        <v/>
+      </c>
+      <c r="G408" t="str">
+        <v/>
+      </c>
+      <c r="H408" t="str">
+        <v/>
+      </c>
+      <c r="I408" t="str">
+        <v>2026-04-10T10:19:55.958Z</v>
+      </c>
+      <c r="J408" t="str">
+        <v>2026-04-10T10:19:55.958Z</v>
+      </c>
+      <c r="K408" t="str">
+        <v/>
+      </c>
+      <c r="L408" t="str">
+        <v/>
+      </c>
+      <c r="M408" t="str">
+        <v/>
+      </c>
+      <c r="N408" t="str">
+        <v/>
+      </c>
+      <c r="O408" t="str">
+        <v/>
+      </c>
+      <c r="P408" t="str">
+        <v/>
+      </c>
+      <c r="Q408" t="str">
+        <v/>
+      </c>
+      <c r="R408" t="str">
+        <v/>
+      </c>
+      <c r="S408" t="str">
+        <v/>
+      </c>
+      <c r="T408">
+        <v>6.99</v>
+      </c>
+      <c r="U408" t="str">
+        <v>5</v>
+      </c>
+      <c r="V408" t="str">
+        <v/>
+      </c>
+      <c r="W408" t="str">
+        <v/>
+      </c>
+      <c r="X408" t="str">
+        <v/>
+      </c>
+      <c r="Y408" t="str">
+        <v/>
+      </c>
+      <c r="Z408" t="str">
+        <v/>
+      </c>
+      <c r="AA408" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="str">
+        <v>YAM046D001</v>
+      </c>
+      <c r="B409" t="str">
+        <v>YAM046</v>
+      </c>
+      <c r="C409" t="str">
+        <v>YAM-121-07-208</v>
+      </c>
+      <c r="D409" t="str">
+        <v/>
+      </c>
+      <c r="E409" t="str">
+        <v/>
+      </c>
+      <c r="F409" t="str">
+        <v/>
+      </c>
+      <c r="G409" t="str">
+        <v/>
+      </c>
+      <c r="H409" t="str">
+        <v/>
+      </c>
+      <c r="I409" t="str">
+        <v>2026-04-10T10:19:57.724Z</v>
+      </c>
+      <c r="J409" t="str">
+        <v>2026-04-10T10:19:57.724Z</v>
+      </c>
+      <c r="K409" t="str">
+        <v/>
+      </c>
+      <c r="L409" t="str">
+        <v/>
+      </c>
+      <c r="M409" t="str">
+        <v/>
+      </c>
+      <c r="N409" t="str">
+        <v/>
+      </c>
+      <c r="O409" t="str">
+        <v/>
+      </c>
+      <c r="P409" t="str">
+        <v/>
+      </c>
+      <c r="Q409" t="str">
+        <v/>
+      </c>
+      <c r="R409" t="str">
+        <v/>
+      </c>
+      <c r="S409" t="str">
+        <v/>
+      </c>
+      <c r="T409">
+        <v>5.99</v>
+      </c>
+      <c r="U409" t="str">
+        <v>7</v>
+      </c>
+      <c r="V409" t="str">
+        <v/>
+      </c>
+      <c r="W409" t="str">
+        <v/>
+      </c>
+      <c r="X409" t="str">
+        <v/>
+      </c>
+      <c r="Y409" t="str">
+        <v/>
+      </c>
+      <c r="Z409" t="str">
+        <v/>
+      </c>
+      <c r="AA409" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R355"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AA409"/>
   </ignoredErrors>
 </worksheet>
 </file>